--- a/scripts/sources/海王祭アプリ2026マスターデータ.xlsx
+++ b/scripts/sources/海王祭アプリ2026マスターデータ.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="252">
   <si>
     <t>id</t>
   </si>
@@ -41,577 +41,619 @@
     <t>キャンパスマップ</t>
   </si>
   <si>
+    <t>campus-map.png</t>
+  </si>
+  <si>
     <t>1-1</t>
   </si>
   <si>
+    <t>1号館1F</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>1-1-map.png</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>1号館2F</t>
+  </si>
+  <si>
+    <t>1-2-map.png</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>2号館1F</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>2-1-map.png</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>2号館2F</t>
+  </si>
+  <si>
+    <t>2-2-map.png</t>
+  </si>
+  <si>
+    <t>ettyu-1</t>
+  </si>
+  <si>
+    <t>越中島会館1F</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>ettyu-1-map.png</t>
+  </si>
+  <si>
+    <t>ettyu-2</t>
+  </si>
+  <si>
+    <t>越中島会館2F</t>
+  </si>
+  <si>
+    <t>ettyu-2-map.png</t>
+  </si>
+  <si>
+    <t>exp-1-1</t>
+  </si>
+  <si>
+    <t>第1実験棟1F</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>exp-1-1-map.png</t>
+  </si>
+  <si>
+    <t>exp-1-3</t>
+  </si>
+  <si>
+    <t>第1実験棟3F</t>
+  </si>
+  <si>
+    <t>exp-1-3-map.png</t>
+  </si>
+  <si>
+    <t>exp-3-5</t>
+  </si>
+  <si>
+    <t>第3実験棟5F</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>exp-3-5-map.png</t>
+  </si>
+  <si>
+    <t>exp-3-6</t>
+  </si>
+  <si>
+    <t>第3実験棟6F</t>
+  </si>
+  <si>
+    <t>exp-3-6-map.png</t>
+  </si>
+  <si>
+    <t>exp-4-5</t>
+  </si>
+  <si>
+    <t>第4実験棟5F</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>exp-4-5-map.png</t>
+  </si>
+  <si>
+    <t>lat</t>
+  </si>
+  <si>
+    <t>lng</t>
+  </si>
+  <si>
+    <t>has_toilet</t>
+  </si>
+  <si>
+    <t>has_aed</t>
+  </si>
+  <si>
+    <t>has_fire_extinguisher</t>
+  </si>
+  <si>
+    <t>AR_00</t>
+  </si>
+  <si>
+    <t>正門</t>
+  </si>
+  <si>
+    <t>AR_01</t>
+  </si>
+  <si>
+    <t>体育館側地区入口</t>
+  </si>
+  <si>
+    <t>AR_02</t>
+  </si>
+  <si>
+    <t>本部</t>
+  </si>
+  <si>
+    <t>AR_03</t>
+  </si>
+  <si>
+    <t>避難場所(第2グランド)</t>
+  </si>
+  <si>
+    <t>AR_04</t>
+  </si>
+  <si>
+    <t>ステージ</t>
+  </si>
+  <si>
+    <t>AR_05</t>
+  </si>
+  <si>
+    <t>模擬店テントエリア</t>
+  </si>
+  <si>
+    <t>AR_06</t>
+  </si>
+  <si>
+    <t>明治丸前広場</t>
+  </si>
+  <si>
+    <t>AR_07</t>
+  </si>
+  <si>
+    <t>not_published</t>
+  </si>
+  <si>
+    <t>喫煙所</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>先端科学技術研究センター(非公開)</t>
+  </si>
+  <si>
+    <t>1号館</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>百周年記念会館</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>明治丸</t>
+  </si>
+  <si>
+    <t>第1実験棟</t>
+  </si>
+  <si>
+    <t>第3実験棟</t>
+  </si>
+  <si>
+    <t>2号館</t>
+  </si>
+  <si>
+    <t>越中島会館(講堂)</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>ワールドマリン・カフェ(休憩所)</t>
+  </si>
+  <si>
+    <t>第4実験棟(大教室)</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>ポンド(試乗会受付)</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>体育管理棟(非公開)</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>体育館</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>明治丸記念館</t>
+  </si>
+  <si>
+    <t>map</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>y_position</t>
+  </si>
+  <si>
+    <t>x_position</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>海王祭実行委員会ブース</t>
+  </si>
+  <si>
+    <t>ベビーカー置き場</t>
+  </si>
+  <si>
+    <t>試乗会集合場所</t>
+  </si>
+  <si>
+    <t>organization</t>
+  </si>
+  <si>
+    <t>mogi_01</t>
+  </si>
+  <si>
+    <t>publish</t>
+  </si>
+  <si>
+    <t>海洋会</t>
+  </si>
+  <si>
+    <t>素敵なオリジナルグッズや明治丸グッズを販売します。公式「明治丸　御船印」も登場、来場記念にどうぞ！</t>
+  </si>
+  <si>
+    <t>mogi_02</t>
+  </si>
+  <si>
+    <t>株式会社日本海事新聞社</t>
+  </si>
+  <si>
+    <t>学生の皆さんに電子版無料ログインID&amp;PWを配布するほか、来場者に発行日前の新聞(6月16日付)を無料配布いたします！</t>
+  </si>
+  <si>
+    <t>mogi_03</t>
+  </si>
+  <si>
+    <t>日本海洋塾</t>
+  </si>
+  <si>
+    <t>mogi_04</t>
+  </si>
+  <si>
+    <t>日本海事代理士会</t>
+  </si>
+  <si>
+    <t>ブースでは、海事代理士による無料法令相談を行います。 模擬店では、軽食提供等を行います。 どなたでもお気軽にお立ち寄りください。</t>
+  </si>
+  <si>
+    <t>mogi_05</t>
+  </si>
+  <si>
+    <t>ナカシマプロペラ株式会社</t>
+  </si>
+  <si>
+    <t>船を動かす“プロペラ”がキャンドルに！？ 世界にひとつだけのプロペラキャンドルをつくりませんか？ 楽しく体験しながら、本物のプロペラの“製造方法”も学べます。</t>
+  </si>
+  <si>
+    <t>mogi_06</t>
+  </si>
+  <si>
+    <t>今治造船株式会社</t>
+  </si>
+  <si>
+    <t>VRゴーグルを装着することで、まるで造船所にいるかのような没入感のある見学体験が可能です。普段はなかなか見ることができない建造中の船を歩いたり飛んだり･･･とご自身が操作することで、自由に体感することができます。</t>
+  </si>
+  <si>
+    <t>mogi_07</t>
+  </si>
+  <si>
+    <t>海王祭実行委員会</t>
+  </si>
+  <si>
+    <t>mogi_08</t>
+  </si>
+  <si>
+    <t>総合創作誌発行企画</t>
+  </si>
+  <si>
+    <t>創作誌の販売と活動紹介をいたします！ さまざまな作品をぜひご覧ください。</t>
+  </si>
+  <si>
+    <t>mogi_09</t>
+  </si>
+  <si>
+    <t>食飯とダンス公演</t>
+  </si>
+  <si>
+    <t>ダンス部EXSEAD</t>
+  </si>
+  <si>
+    <t>屋外ステージでダンス公演を行います！各ジャンルの発表に加え、さまざまな有志も見どころです   ぜひご覧ください！また、模擬店ブースではたこ焼きの販売も行います！</t>
+  </si>
+  <si>
+    <t>mogi_10</t>
+  </si>
+  <si>
+    <t>からあげ</t>
+  </si>
+  <si>
+    <t>軽音楽部</t>
+  </si>
+  <si>
+    <t>揚げ立てのからあげを販売いたします！ また、バンド発表も行います！</t>
+  </si>
+  <si>
+    <t>mogi_11</t>
+  </si>
+  <si>
+    <t>串だんご</t>
+  </si>
+  <si>
+    <t>東洋海洋大学合気道部</t>
+  </si>
+  <si>
+    <t>合気道部は屋外テントにてお団子を販売しています！お好きな生地のお団子とお好きな餡・たれを選んで、ぜひおいしい串団子を片手に海王祭をお楽しみください！！</t>
+  </si>
+  <si>
+    <t>mogi_12</t>
+  </si>
+  <si>
+    <t>ホットドッグ、フランクフルト</t>
+  </si>
+  <si>
+    <t>越中島硬式テニス部</t>
+  </si>
+  <si>
+    <t>パリッとジューシーなフランクフルトとそれをバンズでサンドして熱々に仕上げたホットドッグです！</t>
+  </si>
+  <si>
+    <t>mogi_13</t>
+  </si>
+  <si>
+    <t>チョコバナナ</t>
+  </si>
+  <si>
+    <t>男子バレーボール部</t>
+  </si>
+  <si>
+    <t>毎年人気のチョコバナナを今年も販売します！暑い日にぴったりなバナナスムージーも販売するのでぜひご賞味ください！</t>
+  </si>
+  <si>
+    <t>mogi_14</t>
+  </si>
+  <si>
+    <t>山名物！！ポテトフライ</t>
+  </si>
+  <si>
+    <t>山岳部</t>
+  </si>
+  <si>
+    <t>カリッカリに揚がってます！</t>
+  </si>
+  <si>
+    <t>mogi_15</t>
+  </si>
+  <si>
+    <t>チュロス</t>
+  </si>
+  <si>
+    <t>バスケットボール部</t>
+  </si>
+  <si>
+    <t>外はサクサク，中はもちっと。 海を感じる特別なチュロスにしました！</t>
+  </si>
+  <si>
+    <t>mogi_16</t>
+  </si>
+  <si>
+    <t>本格パエリア</t>
+  </si>
+  <si>
+    <t>木曜会</t>
+  </si>
+  <si>
+    <t>スペインの味を500円で楽しめる！海の幸や鶏肉の旨味が、お米一粒一粒に閉じ込められた贅沢パエリア♪</t>
+  </si>
+  <si>
+    <t>mogi_17</t>
+  </si>
+  <si>
+    <t>揚げアイス</t>
+  </si>
+  <si>
+    <t>ネットボール部</t>
+  </si>
+  <si>
+    <t>ネットボール部にかける思いのようにひんやりアイスをサクッと揚げます！ ぜひご賞味あれ！</t>
+  </si>
+  <si>
+    <t>mogi_18</t>
+  </si>
+  <si>
+    <t>特性スタミナ油そば</t>
+  </si>
+  <si>
+    <t>東京海洋大学・水泳部</t>
+  </si>
+  <si>
+    <t>いつもは大会等があり、参加を見送ることが多かった我々水泳部ですが、今回の海王祭りでは満を持して出店させていただきます。水泳部が一丸となって作った油そば食べてみたくなりませんか！？</t>
+  </si>
+  <si>
+    <t>mogi_19</t>
+  </si>
+  <si>
+    <t>輸血パックドリンク</t>
+  </si>
+  <si>
+    <t>お嬢様部&amp;ピューロランド部</t>
+  </si>
+  <si>
+    <t>お嬢様部とピューロランド部のコラボ！ワクワク満点の輸血パックドリンク！</t>
+  </si>
+  <si>
+    <t>mogi_20</t>
+  </si>
+  <si>
+    <t>空手部のお好み焼き</t>
+  </si>
+  <si>
+    <t>空手道部</t>
+  </si>
+  <si>
+    <t>広島出身の部員監修によるお好み焼きです！こだわった一品をぜひ。</t>
+  </si>
+  <si>
+    <t>mogi_21</t>
+  </si>
+  <si>
+    <t>最適解ワッフル</t>
+  </si>
+  <si>
+    <t>芝浦祭実行委員会</t>
+  </si>
+  <si>
+    <t>ミックスベリーを乗せた最適解ワッフルを 販売いたします！ ソースはチョコ、イチゴ、ブルーベリー、 メープルをご用意しております。</t>
+  </si>
+  <si>
+    <t>mogi_22</t>
+  </si>
+  <si>
+    <t>カニレース</t>
+  </si>
+  <si>
+    <t>ネクトンカフェ</t>
+  </si>
+  <si>
+    <t>mogi_23</t>
+  </si>
+  <si>
+    <t>魚介ラーメン</t>
+  </si>
+  <si>
+    <t>あさり会</t>
+  </si>
+  <si>
+    <t>品川キャンパスから来ました、あさり会です。品川キャンパスらしく魚介料理を提供します。品川キャンパス自治委員会委員長推奨のおいしい料理をぜひご賞味ください。</t>
+  </si>
+  <si>
+    <t>mogi_24</t>
+  </si>
+  <si>
+    <t>門仲晃一</t>
+  </si>
+  <si>
+    <t>クリームチーズが入ったライスコロッケ！！チキンライスとカレーピラフの２種類あります！！門仲晃一定番、特製唐揚げもご用意！！</t>
+  </si>
+  <si>
+    <t>mogi_25</t>
+  </si>
+  <si>
+    <t>クジラ肉の唐揚げ</t>
+  </si>
+  <si>
+    <t>剣道部</t>
+  </si>
+  <si>
+    <t>珍しいクジラ肉の唐揚げを販売いたします！ 香ばしく揚げた一品を、ぜひご賞味ください。</t>
+  </si>
+  <si>
+    <t>mogi_26</t>
+  </si>
+  <si>
+    <t>シェイク</t>
+  </si>
+  <si>
+    <t>カヌー部</t>
+  </si>
+  <si>
+    <t>カヌー部では、いちご・抹茶・キャラメル・ コーヒー・オレオから選べるシェイクを 販売しています。 ぜひお越しください！</t>
+  </si>
+  <si>
+    <t>mogi_27</t>
+  </si>
+  <si>
+    <t>海鮮焼そば</t>
+  </si>
+  <si>
+    <t>東京海洋大学ヨット部</t>
+  </si>
+  <si>
+    <t>海鮮のうまみがたっぷり入った焼きそばを 販売いたします！</t>
+  </si>
+  <si>
+    <t>mogi_28</t>
+  </si>
+  <si>
+    <t>焼きグソクムシ販売・アンサンブル他</t>
+  </si>
+  <si>
+    <t>東京海洋大学・共立薬科大学管弦楽団</t>
+  </si>
+  <si>
+    <t>オーケストラ部です！テントにて焼きグソクムシ、焼き鳥、ラムネの販売、ス ーパーボールすくい、教室にてアンサンブルおよびグッズ販売をいたしま す！ぜひお越しください！</t>
+  </si>
+  <si>
+    <t>mogi_29</t>
+  </si>
+  <si>
+    <t>生協学生委員会海王祭模擬店</t>
+  </si>
+  <si>
+    <t>東京海洋大学越中島生協学生委員会</t>
+  </si>
+  <si>
+    <t>生協学生委員会では、海洋大グッズ、瓶飲料の販売と水風船釣りを行います！ぜひ一度覗いてみてください！！</t>
+  </si>
+  <si>
+    <t>mogi_30</t>
+  </si>
+  <si>
+    <t>ベビーカステラ</t>
+  </si>
+  <si>
+    <t>海事普及会</t>
+  </si>
+  <si>
+    <t>ふんわり甘いベビーカステラを販売します。 食べ歩きにぜひどうぞ！ トッピングもございます！</t>
+  </si>
+  <si>
+    <t>mogi_31</t>
+  </si>
+  <si>
     <t>wip</t>
-  </si>
-  <si>
-    <t>1号館1F</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>1号館2F</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>2号館1F</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>2号館2F</t>
-  </si>
-  <si>
-    <t>ettyu-1</t>
-  </si>
-  <si>
-    <t>越中島会館1F</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>ettyu-2</t>
-  </si>
-  <si>
-    <t>越中島会館2F</t>
-  </si>
-  <si>
-    <t>exp-1-1</t>
-  </si>
-  <si>
-    <t>第1実験棟1F</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>exp-1-3</t>
-  </si>
-  <si>
-    <t>第1実験棟3F</t>
-  </si>
-  <si>
-    <t>exp-3-5</t>
-  </si>
-  <si>
-    <t>第3実験棟5F</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>exp-4-5</t>
-  </si>
-  <si>
-    <t>第4実験棟5F</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>lat</t>
-  </si>
-  <si>
-    <t>lng</t>
-  </si>
-  <si>
-    <t>has_toilet</t>
-  </si>
-  <si>
-    <t>has_aed</t>
-  </si>
-  <si>
-    <t>has_fire_extinguisher</t>
-  </si>
-  <si>
-    <t>AR_00</t>
-  </si>
-  <si>
-    <t>正門</t>
-  </si>
-  <si>
-    <t>AR_01</t>
-  </si>
-  <si>
-    <t>体育館側地区入口</t>
-  </si>
-  <si>
-    <t>AR_02</t>
-  </si>
-  <si>
-    <t>本部</t>
-  </si>
-  <si>
-    <t>AR_03</t>
-  </si>
-  <si>
-    <t>避難場所(第2グランド)</t>
-  </si>
-  <si>
-    <t>AR_04</t>
-  </si>
-  <si>
-    <t>ステージ</t>
-  </si>
-  <si>
-    <t>AR_05</t>
-  </si>
-  <si>
-    <t>模擬店テントエリア</t>
-  </si>
-  <si>
-    <t>AR_06</t>
-  </si>
-  <si>
-    <t>明治丸前広場</t>
-  </si>
-  <si>
-    <t>AR_07</t>
-  </si>
-  <si>
-    <t>喫煙所</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>先端科学技術研究センター(非公開)</t>
-  </si>
-  <si>
-    <t>1号館</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>百周年記念会館</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>明治丸</t>
-  </si>
-  <si>
-    <t>第1実験棟</t>
-  </si>
-  <si>
-    <t>第3実験棟</t>
-  </si>
-  <si>
-    <t>2号館</t>
-  </si>
-  <si>
-    <t>越中島会館(講堂)</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>ワールドマリン・カフェ(休憩所)</t>
-  </si>
-  <si>
-    <t>第4実験棟(大教室)</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>ポンド(試乗会受付)</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>体育管理棟(非公開)</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>体育館</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>明治丸記念館</t>
-  </si>
-  <si>
-    <t>map</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>y_position</t>
-  </si>
-  <si>
-    <t>x_position</t>
-  </si>
-  <si>
-    <t>00</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>海王祭実行委員会ブース</t>
-  </si>
-  <si>
-    <t>ベビーカー置き場</t>
-  </si>
-  <si>
-    <t>試乗会集合場所</t>
-  </si>
-  <si>
-    <t>organization</t>
-  </si>
-  <si>
-    <t>mogi_01</t>
-  </si>
-  <si>
-    <t>publish</t>
-  </si>
-  <si>
-    <t>海洋会</t>
-  </si>
-  <si>
-    <t>素敵なオリジナルグッズや明治丸グッズを販売します。公式「明治丸　御船印」も登場、来場記念にどうぞ！</t>
-  </si>
-  <si>
-    <t>mogi_02</t>
-  </si>
-  <si>
-    <t>株式会社日本海事新聞社</t>
-  </si>
-  <si>
-    <t>学生の皆さんに電子版無料ログインID&amp;PWを配布するほか、来場者に発行日前の新聞(6月16日付)を無料配布いたします！</t>
-  </si>
-  <si>
-    <t>mogi_03</t>
-  </si>
-  <si>
-    <t>日本海洋塾</t>
-  </si>
-  <si>
-    <t>mogi_04</t>
-  </si>
-  <si>
-    <t>日本海事代理士会</t>
-  </si>
-  <si>
-    <t>ブースでは、海事代理士による無料法令相談を行います。 模擬店では、軽食提供等を行います。 どなたでもお気軽にお立ち寄りください。</t>
-  </si>
-  <si>
-    <t>mogi_05</t>
-  </si>
-  <si>
-    <t>ナカシマプロペラ株式会社</t>
-  </si>
-  <si>
-    <t>船を動かす“プロペラ”がキャンドルに！？ 世界にひとつだけのプロペラキャンドルをつくりませんか？ 楽しく体験しながら、本物のプロペラの“製造方法”も学べます。</t>
-  </si>
-  <si>
-    <t>mogi_06</t>
-  </si>
-  <si>
-    <t>今治造船株式会社</t>
-  </si>
-  <si>
-    <t>VRゴーグルを装着することで、まるで造船所にいるかのような没入感のある見学体験が可能です。普段はなかなか見ることができない建造中の船を歩いたり飛んだり･･･とご自身が操作することで、自由に体感することができます。</t>
-  </si>
-  <si>
-    <t>mogi_07</t>
-  </si>
-  <si>
-    <t>not_published</t>
-  </si>
-  <si>
-    <t>海王祭実行委員会</t>
-  </si>
-  <si>
-    <t>mogi_08</t>
-  </si>
-  <si>
-    <t>総合創作誌発行企画</t>
-  </si>
-  <si>
-    <t>創作誌の販売と活動紹介をいたします！ さまざまな作品をぜひご覧ください。</t>
-  </si>
-  <si>
-    <t>mogi_09</t>
-  </si>
-  <si>
-    <t>食飯とダンス公演</t>
-  </si>
-  <si>
-    <t>ダンス部EXSEAD</t>
-  </si>
-  <si>
-    <t>屋外ステージでダンス公演を行います！各ジャンルの発表に加え、さまざまな有志も見どころです   ぜひご覧ください！また、模擬店ブースではたこ焼きの販売も行います！</t>
-  </si>
-  <si>
-    <t>mogi_10</t>
-  </si>
-  <si>
-    <t>からあげ</t>
-  </si>
-  <si>
-    <t>軽音楽部</t>
-  </si>
-  <si>
-    <t>揚げ立てのからあげを販売いたします！ また、バンド発表も行います！</t>
-  </si>
-  <si>
-    <t>mogi_11</t>
-  </si>
-  <si>
-    <t>串だんご</t>
-  </si>
-  <si>
-    <t>東洋海洋大学合気道部</t>
-  </si>
-  <si>
-    <t>合気道部は屋外テントにてお団子を販売しています！お好きな生地のお団子とお好きな餡・たれを選んで、ぜひおいしい串団子を片手に海王祭をお楽しみください！！</t>
-  </si>
-  <si>
-    <t>mogi_12</t>
-  </si>
-  <si>
-    <t>ホットドッグ、フランクフルト</t>
-  </si>
-  <si>
-    <t>越中島硬式テニス部</t>
-  </si>
-  <si>
-    <t>パリッとジューシーなフランクフルトとそれをバンズでサンドして熱々に仕上げたホットドッグです！</t>
-  </si>
-  <si>
-    <t>mogi_13</t>
-  </si>
-  <si>
-    <t>チョコバナナ</t>
-  </si>
-  <si>
-    <t>男子バレーボール部</t>
-  </si>
-  <si>
-    <t>毎年人気のチョコバナナを今年も販売します！暑い日にぴったりなバナナスムージーも販売するのでぜひご賞味ください！</t>
-  </si>
-  <si>
-    <t>mogi_14</t>
-  </si>
-  <si>
-    <t>山名物！！ポテトフライ</t>
-  </si>
-  <si>
-    <t>山岳部</t>
-  </si>
-  <si>
-    <t>カリッカリに揚がってます！</t>
-  </si>
-  <si>
-    <t>mogi_15</t>
-  </si>
-  <si>
-    <t>チュロス</t>
-  </si>
-  <si>
-    <t>バスケットボール部</t>
-  </si>
-  <si>
-    <t>外はサクサク，中はもちっと。 海を感じる特別なチュロスにしました！</t>
-  </si>
-  <si>
-    <t>mogi_16</t>
-  </si>
-  <si>
-    <t>本格パエリア</t>
-  </si>
-  <si>
-    <t>木曜会</t>
-  </si>
-  <si>
-    <t>スペインの味を500円で楽しめる！海の幸や鶏肉の旨味が、お米一粒一粒に閉じ込められた贅沢パエリア♪</t>
-  </si>
-  <si>
-    <t>mogi_17</t>
-  </si>
-  <si>
-    <t>揚げアイス</t>
-  </si>
-  <si>
-    <t>ネットボール部</t>
-  </si>
-  <si>
-    <t>ネットボール部にかける思いのようにひんやりアイスをサクッと揚げます！ ぜひご賞味あれ！</t>
-  </si>
-  <si>
-    <t>mogi_18</t>
-  </si>
-  <si>
-    <t>特性スタミナ油そば</t>
-  </si>
-  <si>
-    <t>東京海洋大学・水泳部</t>
-  </si>
-  <si>
-    <t>いつもは大会等があり、参加を見送ることが多かった我々水泳部ですが、今回の海王祭りでは満を持して出店させていただきます。水泳部が一丸となって作った油そば食べてみたくなりませんか！？</t>
-  </si>
-  <si>
-    <t>mogi_19</t>
-  </si>
-  <si>
-    <t>輸血パックドリンク</t>
-  </si>
-  <si>
-    <t>お嬢様部&amp;ピューロランド部</t>
-  </si>
-  <si>
-    <t>お嬢様部とピューロランド部のコラボ！ワクワク満点の輸血パックドリンク！</t>
-  </si>
-  <si>
-    <t>mogi_20</t>
-  </si>
-  <si>
-    <t>空手部のお好み焼き</t>
-  </si>
-  <si>
-    <t>空手道部</t>
-  </si>
-  <si>
-    <t>広島出身の部員監修によるお好み焼きです！こだわった一品をぜひ。</t>
-  </si>
-  <si>
-    <t>mogi_21</t>
-  </si>
-  <si>
-    <t>最適解ワッフル</t>
-  </si>
-  <si>
-    <t>芝浦祭実行委員会</t>
-  </si>
-  <si>
-    <t>ミックスベリーを乗せた最適解ワッフルを 販売いたします！ ソースはチョコ、イチゴ、ブルーベリー、 メープルをご用意しております。</t>
-  </si>
-  <si>
-    <t>mogi_22</t>
-  </si>
-  <si>
-    <t>カニレース</t>
-  </si>
-  <si>
-    <t>ネクトンカフェ</t>
-  </si>
-  <si>
-    <t>mogi_23</t>
-  </si>
-  <si>
-    <t>魚介ラーメン</t>
-  </si>
-  <si>
-    <t>あさり会</t>
-  </si>
-  <si>
-    <t>品川キャンパスから来ました、あさり会です。品川キャンパスらしく魚介料理を提供します。品川キャンパス自治委員会委員長推奨のおいしい料理をぜひご賞味ください。</t>
-  </si>
-  <si>
-    <t>mogi_24</t>
-  </si>
-  <si>
-    <t>門仲晃一</t>
-  </si>
-  <si>
-    <t>クリームチーズが入ったライスコロッケ！！チキンライスとカレーピラフの２種類あります！！門仲晃一定番、特製唐揚げもご用意！！</t>
-  </si>
-  <si>
-    <t>mogi_25</t>
-  </si>
-  <si>
-    <t>クジラ肉の唐揚げ</t>
-  </si>
-  <si>
-    <t>剣道部</t>
-  </si>
-  <si>
-    <t>珍しいクジラ肉の唐揚げを販売いたします！ 香ばしく揚げた一品を、ぜひご賞味ください。</t>
-  </si>
-  <si>
-    <t>mogi_26</t>
-  </si>
-  <si>
-    <t>シェイク</t>
-  </si>
-  <si>
-    <t>カヌー部</t>
-  </si>
-  <si>
-    <t>カヌー部では、いちご・抹茶・キャラメル・ コーヒー・オレオから選べるシェイクを 販売しています。 ぜひお越しください！</t>
-  </si>
-  <si>
-    <t>mogi_27</t>
-  </si>
-  <si>
-    <t>海鮮焼そば</t>
-  </si>
-  <si>
-    <t>東京海洋大学ヨット部</t>
-  </si>
-  <si>
-    <t>海鮮のうまみがたっぷり入った焼きそばを 販売いたします！</t>
-  </si>
-  <si>
-    <t>mogi_28</t>
-  </si>
-  <si>
-    <t>焼きグソクムシ販売・アンサンブル他</t>
-  </si>
-  <si>
-    <t>東京海洋大学・共立薬科大学管弦楽団</t>
-  </si>
-  <si>
-    <t>オーケストラ部です！テントにて焼きグソクムシ、焼き鳥、ラムネの販売、ス ーパーボールすくい、教室にてアンサンブルおよびグッズ販売をいたしま す！ぜひお越しください！</t>
-  </si>
-  <si>
-    <t>mogi_29</t>
-  </si>
-  <si>
-    <t>生協学生委員会海王祭模擬店</t>
-  </si>
-  <si>
-    <t>東京海洋大学越中島生協学生委員会</t>
-  </si>
-  <si>
-    <t>生協学生委員会では、海洋大グッズ、瓶飲料の販売と水風船釣りを行います！ぜひ一度覗いてみてください！！</t>
-  </si>
-  <si>
-    <t>mogi_30</t>
-  </si>
-  <si>
-    <t>ベビーカステラ</t>
-  </si>
-  <si>
-    <t>海事普及会</t>
-  </si>
-  <si>
-    <t>ふんわり甘いベビーカステラを販売します。 食べ歩きにぜひどうぞ！ トッピングもございます！</t>
-  </si>
-  <si>
-    <t>mogi_31</t>
   </si>
   <si>
     <t>防衛省自衛隊</t>
@@ -1029,6 +1071,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="14.38"/>
+    <col customWidth="1" min="5" max="5" width="13.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1059,13 +1102,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="3"/>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
@@ -1073,136 +1119,179 @@
       <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="A13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3"/>
@@ -5147,6 +5236,10 @@
     <row r="999">
       <c r="A999" s="3"/>
       <c r="D999" s="3"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="3"/>
+      <c r="D1000" s="3"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -5176,30 +5269,30 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2">
         <v>35.668622</v>
@@ -5210,13 +5303,13 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D3" s="2">
         <v>35.6682315</v>
@@ -5227,13 +5320,13 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2">
         <v>35.66742024</v>
@@ -5244,13 +5337,13 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2">
         <v>35.6656558</v>
@@ -5261,13 +5354,13 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D6" s="2">
         <v>35.6673204</v>
@@ -5278,13 +5371,13 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D7" s="2">
         <v>35.66718218</v>
@@ -5295,13 +5388,13 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D8" s="2">
         <v>35.6675603</v>
@@ -5312,13 +5405,13 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D9" s="2">
         <v>35.6681137</v>
@@ -5329,13 +5422,13 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="D10" s="2">
         <v>35.6683382</v>
@@ -5355,7 +5448,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="D11" s="2">
         <v>35.66821282</v>
@@ -5369,13 +5462,13 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D12" s="2">
         <v>35.6677954</v>
@@ -5392,13 +5485,13 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D13" s="2">
         <v>35.6674469</v>
@@ -5409,13 +5502,13 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D14" s="2">
         <v>35.6679242</v>
@@ -5429,13 +5522,13 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D15" s="2">
         <v>35.6672573</v>
@@ -5446,13 +5539,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D16" s="2">
         <v>35.667034</v>
@@ -5469,13 +5562,13 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D17" s="2">
         <v>35.6665416</v>
@@ -5495,13 +5588,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D18" s="2">
         <v>35.6661886</v>
@@ -5512,13 +5605,13 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="D19" s="2">
         <v>35.66636313</v>
@@ -5535,13 +5628,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2">
         <v>35.6661613</v>
@@ -5552,13 +5645,13 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D21" s="2">
         <v>35.6655048</v>
@@ -5572,13 +5665,13 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D22" s="2">
         <v>35.6679591</v>
@@ -5589,13 +5682,13 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D23" s="2">
         <v>35.6679567</v>
@@ -8573,33 +8666,33 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F2" s="2">
         <v>35.66742024</v>
@@ -8610,10 +8703,10 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F3" s="2">
         <v>35.66738266</v>
@@ -8624,10 +8717,10 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F4" s="2">
         <v>35.66733145</v>
@@ -8641,7 +8734,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F5" s="2">
         <v>35.6673204</v>
@@ -8652,10 +8745,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F6" s="2">
         <v>35.6661613</v>
@@ -11670,48 +11763,48 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="G2" s="2">
         <v>35.66776362</v>
@@ -11722,22 +11815,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="G3" s="2">
         <v>35.6677205</v>
@@ -11748,19 +11841,19 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="G4" s="2">
         <v>35.667776</v>
@@ -11771,22 +11864,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="G5" s="2">
         <v>35.6677303</v>
@@ -11797,22 +11890,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="G6" s="2">
         <v>35.6676801</v>
@@ -11823,22 +11916,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="G7" s="2">
         <v>35.6676289</v>
@@ -11849,19 +11942,19 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2">
@@ -11873,22 +11966,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="G9" s="2">
         <v>35.6676327</v>
@@ -11899,22 +11992,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G10" s="2">
         <v>35.6675843</v>
@@ -11925,22 +12018,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="G11" s="2">
         <v>35.6675385</v>
@@ -11951,22 +12044,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="G12" s="2">
         <v>35.6674927</v>
@@ -11977,22 +12070,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="G13" s="2">
         <v>35.6673587</v>
@@ -12003,22 +12096,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G14" s="2">
         <v>35.6673293</v>
@@ -12029,22 +12122,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="G15" s="2">
         <v>35.6673015</v>
@@ -12055,22 +12148,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="G16" s="2">
         <v>35.6672748</v>
@@ -12081,22 +12174,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="G17" s="2">
         <v>35.6672481</v>
@@ -12107,22 +12200,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="G18" s="2">
         <v>35.6672182</v>
@@ -12133,22 +12226,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="G19" s="2">
         <v>35.6671822</v>
@@ -12159,22 +12252,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="G20" s="2">
         <v>35.6671501</v>
@@ -12185,22 +12278,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="G21" s="2">
         <v>35.6669785</v>
@@ -12211,22 +12304,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="G22" s="2">
         <v>35.6671114</v>
@@ -12237,19 +12330,19 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="G23" s="2">
         <v>35.6670814</v>
@@ -12260,22 +12353,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="G24" s="2">
         <v>35.6670433</v>
@@ -12286,22 +12379,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="G25" s="2">
         <v>35.6670123</v>
@@ -12312,22 +12405,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="G26" s="2">
         <v>35.6669469</v>
@@ -12338,22 +12431,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="G27" s="2">
         <v>35.6669082</v>
@@ -12364,22 +12457,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="G28" s="2">
         <v>35.666875</v>
@@ -12390,22 +12483,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="G29" s="2">
         <v>35.6668396</v>
@@ -12416,22 +12509,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="G30" s="2">
         <v>35.6669616</v>
@@ -12442,22 +12535,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="G31" s="2">
         <v>35.66690034</v>
@@ -12468,39 +12561,39 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="I33" s="2">
         <v>0.5</v>
@@ -15434,25 +15527,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>4</v>
@@ -15460,7 +15553,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
@@ -15469,7 +15562,7 @@
         <v>46158.0</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="G2" s="8">
         <v>0.3645833333333333</v>
@@ -15480,7 +15573,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -15489,7 +15582,7 @@
         <v>46158.0</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="G3" s="8">
         <v>0.375</v>
@@ -15500,7 +15593,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -15509,7 +15602,7 @@
         <v>46158.0</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="G4" s="8">
         <v>0.4305555555555556</v>
@@ -15520,7 +15613,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>6</v>
@@ -15529,10 +15622,10 @@
         <v>46158.0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="G5" s="8">
         <v>0.4930555555555556</v>
@@ -15543,7 +15636,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -15552,7 +15645,7 @@
         <v>46158.0</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="G6" s="8">
         <v>0.5625</v>
@@ -15563,7 +15656,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>6</v>
@@ -15572,7 +15665,7 @@
         <v>46158.0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="G7" s="8">
         <v>0.5833333333333334</v>
@@ -15586,7 +15679,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
@@ -15595,7 +15688,7 @@
         <v>46158.0</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="G8" s="8">
         <v>0.6180555555555556</v>
@@ -15606,7 +15699,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
@@ -15615,7 +15708,7 @@
         <v>46158.0</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="G9" s="8">
         <v>0.7083333333333334</v>
@@ -15626,7 +15719,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>6</v>
@@ -15635,7 +15728,7 @@
         <v>46159.0</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G10" s="8">
         <v>0.3958333333333333</v>
@@ -15646,7 +15739,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>6</v>
@@ -15655,7 +15748,7 @@
         <v>46159.0</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="G11" s="8">
         <v>0.4375</v>
@@ -15666,7 +15759,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>6</v>
@@ -15675,7 +15768,7 @@
         <v>46159.0</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="G12" s="8">
         <v>0.4791666666666667</v>
@@ -15689,7 +15782,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>6</v>
@@ -15698,7 +15791,7 @@
         <v>46159.0</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="G13" s="8">
         <v>0.5138888888888888</v>
@@ -15709,7 +15802,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>6</v>
@@ -15718,7 +15811,7 @@
         <v>46159.0</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="G14" s="8">
         <v>0.5694444444444444</v>
@@ -15732,7 +15825,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>6</v>
@@ -15741,7 +15834,7 @@
         <v>46159.0</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G15" s="8">
         <v>0.6388888888888888</v>
@@ -15752,7 +15845,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>6</v>
@@ -15761,7 +15854,7 @@
         <v>46159.0</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="G16" s="8">
         <v>0.6736111111111112</v>
@@ -15775,7 +15868,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>6</v>
@@ -15784,7 +15877,7 @@
         <v>46159.0</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="G17" s="8">
         <v>0.7083333333333334</v>

--- a/scripts/sources/海王祭アプリ2026マスターデータ.xlsx
+++ b/scripts/sources/海王祭アプリ2026マスターデータ.xlsx
@@ -1457,7 +1457,7 @@
         <v>mogi_06</v>
       </c>
       <c r="B7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="str">
         <v>campus</v>

--- a/scripts/sources/海王祭アプリ2026マスターデータ.xlsx
+++ b/scripts/sources/海王祭アプリ2026マスターデータ.xlsx
@@ -1457,7 +1457,7 @@
         <v>mogi_06</v>
       </c>
       <c r="B7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="str">
         <v>campus</v>
@@ -2458,10 +2458,10 @@
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>0.177207</v>
+        <v>0.112847</v>
       </c>
       <c r="J35" t="str">
-        <v>0.416992</v>
+        <v>0.419954</v>
       </c>
       <c r="K35" t="str">
         <v>25-郵船クルーズ株式会社.png</v>
@@ -2528,10 +2528,10 @@
         <v/>
       </c>
       <c r="I37" t="str">
-        <v>0.179287</v>
+        <v>0.116998</v>
       </c>
       <c r="J37" t="str">
-        <v>0.704231</v>
+        <v>0.709166</v>
       </c>
       <c r="K37" t="str">
         <v>25-ブラスバンド部.png</v>
@@ -2808,10 +2808,10 @@
         <v/>
       </c>
       <c r="I45" t="str">
-        <v>0.758295</v>
+        <v>0.675296</v>
       </c>
       <c r="J45" t="str">
-        <v>0.470085</v>
+        <v>0.477203</v>
       </c>
       <c r="K45" t="str">
         <v>39-茶道部.png</v>
@@ -2878,10 +2878,10 @@
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>0.577776</v>
+        <v>0.415865</v>
       </c>
       <c r="J47" t="str">
-        <v>0.472933</v>
+        <v>0.470085</v>
       </c>
       <c r="K47" t="str">
         <v>39-今治造船株式会社.png</v>
@@ -3053,10 +3053,10 @@
         <v/>
       </c>
       <c r="I52" t="str">
-        <v>0.378622</v>
+        <v>0.374462</v>
       </c>
       <c r="J52" t="str">
-        <v>0.440182</v>
+        <v>0.461934</v>
       </c>
       <c r="K52" t="str">
         <v>41-KillerWhaleLab.png</v>
@@ -3158,10 +3158,10 @@
         <v/>
       </c>
       <c r="I55" t="str">
-        <v>0.484454</v>
+        <v>0.486531</v>
       </c>
       <c r="J55" t="str">
-        <v>0.440182</v>
+        <v>0.421538</v>
       </c>
       <c r="K55" t="str">
         <v>41-ロボット研究会.png</v>
@@ -3298,10 +3298,10 @@
         <v/>
       </c>
       <c r="I59" t="str">
-        <v>0.611040</v>
+        <v>0.631808</v>
       </c>
       <c r="J59" t="str">
-        <v>0.440182</v>
+        <v>0.443290</v>
       </c>
       <c r="K59" t="str">
         <v>41-プログラミングサークルNePP.png</v>

--- a/scripts/sources/海王祭アプリ2026マスターデータ.xlsx
+++ b/scripts/sources/海王祭アプリ2026マスターデータ.xlsx
@@ -36,10 +36,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="H:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy/MM/dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -1082,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J999"/>
+  <dimension ref="A1:J1000"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1162,7 +1160,7 @@
         <v>27-受付.png</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>03</v>
       </c>
@@ -1172,8 +1170,9 @@
       <c r="D4" t="str">
         <v>ベビーカー置き場</v>
       </c>
-      <c r="E4" t="str">
-        <v>ベビーカー置き場をご用意しています。ご自由にご利用ください。</v>
+      <c r="E4" t="str" xml:space="preserve">
+        <v xml:space="preserve">ベビーカー置き場をご用意しています。ご自由にご利用ください。
+※置場内の盗難及び事故発生等は責任を負いかねますので、ご了承ください。</v>
       </c>
       <c r="F4">
         <v>35.66733145</v>
@@ -1231,16 +1230,156 @@
         <v>49-試乗会.png</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>06</v>
+      </c>
+      <c r="B7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" t="str">
+        <v>ゴミステーション</v>
+      </c>
+      <c r="F7">
+        <v>35.6661613</v>
+      </c>
+      <c r="G7">
+        <v>139.7919166</v>
+      </c>
+      <c r="J7" t="str">
+        <v>27-本部.png</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>07</v>
+      </c>
+      <c r="B8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>ゴミステーション</v>
+      </c>
+      <c r="F8">
+        <v>35.6661613</v>
+      </c>
+      <c r="G8">
+        <v>139.7919166</v>
+      </c>
+      <c r="J8" t="str">
+        <v>27-本部.png</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>08</v>
+      </c>
+      <c r="B9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>ゴミステーション</v>
+      </c>
+      <c r="F9">
+        <v>35.6661613</v>
+      </c>
+      <c r="G9">
+        <v>139.7919166</v>
+      </c>
+      <c r="J9" t="str">
+        <v>27-本部.png</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>09</v>
+      </c>
+      <c r="B10" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>ゴミステーション</v>
+      </c>
+      <c r="F10">
+        <v>35.6661613</v>
+      </c>
+      <c r="G10">
+        <v>139.7919166</v>
+      </c>
+      <c r="J10" t="str">
+        <v>27-本部.png</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>10</v>
+      </c>
+      <c r="B11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>プラネタリウム受付</v>
+      </c>
+      <c r="F11">
+        <v>35.6661613</v>
+      </c>
+      <c r="G11">
+        <v>139.7919166</v>
+      </c>
+      <c r="J11" t="str">
+        <v>27-本部.png</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>11</v>
+      </c>
+      <c r="B12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" t="str">
+        <v>チョークの落書きコーナー</v>
+      </c>
+      <c r="F12" t="str">
+        <v>35.6666626</v>
+      </c>
+      <c r="G12" t="str">
+        <v>139.7920990</v>
+      </c>
+      <c r="J12" t="str">
+        <v>27-本部.png</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>12</v>
+      </c>
+      <c r="B13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" t="str">
+        <v>寄せ書きボード</v>
+      </c>
+      <c r="F13" t="str">
+        <v>35.6677689</v>
+      </c>
+      <c r="G13" t="str">
+        <v>139.7910838</v>
+      </c>
+      <c r="J13" t="str">
+        <v>27-本部.png</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J999"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J1000"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K985"/>
+  <dimension ref="A1:K1000"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1329,7 +1468,7 @@
         <v>株式会社日本海事新聞社</v>
       </c>
       <c r="F3" t="str">
-        <v>学生の皆さんに電子版無料ログインID&amp;PWを配布するほか、来場者に発行日前の新聞(6月16日付)を無料配布いたします！</v>
+        <v>学生の皆さんに電子版無料ログインID&amp;PWを配布するほか、来場者に発行日前の新聞(5月18日付)を無料配布いたします！</v>
       </c>
       <c r="G3">
         <v>35.6677205</v>
@@ -1454,7 +1593,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>mogi_06</v>
+        <v>mogi_07</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
@@ -1463,19 +1602,19 @@
         <v>campus</v>
       </c>
       <c r="D7" t="str">
-        <v>今治造船株式会社</v>
+        <v>海王祭実行委員会ブース</v>
       </c>
       <c r="E7" t="str">
-        <v>今治造船株式会社</v>
+        <v>海王祭実行委員会</v>
       </c>
       <c r="F7" t="str">
-        <v>VRゴーグルを装着することで、まるで造船所にいるかのような没入感のある見学体験が可能です。普段はなかなか見ることができない建造中の船を歩いたり飛んだり･･･とご自身が操作することで、自由に体感することができます。</v>
-      </c>
-      <c r="G7">
-        <v>35.6676289</v>
-      </c>
-      <c r="H7">
-        <v>139.790538</v>
+        <v>海王祭実行委員会の模擬店では ノンアルコールビール、海王祭グッズ、 船舶模型、ビンゴカードを販売いたします！射的もあるよ！</v>
+      </c>
+      <c r="G7" t="str">
+        <v>35.6673762</v>
+      </c>
+      <c r="H7" t="str">
+        <v>139.7910771</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -1484,12 +1623,12 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>39-今治造船株式会社.png</v>
+        <v>27-海王祭実行委員会.png</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>mogi_07</v>
+        <v>mogi_08</v>
       </c>
       <c r="B8" t="b">
         <v>1</v>
@@ -1498,19 +1637,19 @@
         <v>campus</v>
       </c>
       <c r="D8" t="str">
-        <v>海王祭実行委員会ブース</v>
+        <v>総合創作誌発行企画</v>
       </c>
       <c r="E8" t="str">
-        <v>海王祭実行委員会</v>
+        <v>総合創作誌発行企画</v>
       </c>
       <c r="F8" t="str">
-        <v>海王祭実行委員会の模擬店では ノンアルコールビール、海王祭グッズ、 船舶模型、ビンゴカードを 販売いたします！</v>
-      </c>
-      <c r="G8" t="str">
-        <v>35.6673762</v>
-      </c>
-      <c r="H8" t="str">
-        <v>139.7910771</v>
+        <v>創作誌の販売と活動紹介をいたします！ さまざまな作品をぜひご覧ください。</v>
+      </c>
+      <c r="G8">
+        <v>35.6676327</v>
+      </c>
+      <c r="H8">
+        <v>139.7910938</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -1519,12 +1658,12 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>27-海王祭実行委員会.png</v>
+        <v>29-総合創作誌発行企画.png</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>mogi_08</v>
+        <v>mogi_09</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -1533,19 +1672,19 @@
         <v>campus</v>
       </c>
       <c r="D9" t="str">
-        <v>総合創作誌発行企画</v>
+        <v>たこやき</v>
       </c>
       <c r="E9" t="str">
-        <v>総合創作誌発行企画</v>
+        <v>ダンス部EXSEAD</v>
       </c>
       <c r="F9" t="str">
-        <v>創作誌の販売と活動紹介をいたします！ さまざまな作品をぜひご覧ください。</v>
+        <v>たこ焼きの販売を行います！また、屋外ステージでダンス公演を行います！各ジャンルの発表に加え、さまざまな有志も見どころです   ぜひご覧ください！</v>
       </c>
       <c r="G9">
-        <v>35.6676327</v>
+        <v>35.6675843</v>
       </c>
       <c r="H9">
-        <v>139.7910938</v>
+        <v>139.7911495</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -1554,12 +1693,12 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>29-総合創作誌発行企画.png</v>
+        <v>29-ダンス部EXSEAD.png</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>mogi_09</v>
+        <v>mogi_10</v>
       </c>
       <c r="B10" t="b">
         <v>1</v>
@@ -1568,19 +1707,19 @@
         <v>campus</v>
       </c>
       <c r="D10" t="str">
-        <v>食飯とダンス公演</v>
+        <v>からあげ</v>
       </c>
       <c r="E10" t="str">
-        <v>ダンス部EXSEAD</v>
+        <v>軽音楽部</v>
       </c>
       <c r="F10" t="str">
-        <v>屋外ステージでダンス公演を行います！各ジャンルの発表に加え、さまざまな有志も見どころです   ぜひご覧ください！また、模擬店ブースではたこ焼きの販売も行います！</v>
+        <v>揚げ立てのからあげを販売いたします！ また、バンド発表も行います！</v>
       </c>
       <c r="G10">
-        <v>35.6675843</v>
+        <v>35.6675385</v>
       </c>
       <c r="H10">
-        <v>139.7911495</v>
+        <v>139.7912031</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -1589,12 +1728,12 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>29-ダンス部EXSEAD.png</v>
+        <v>29-越中島軽音部.png</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>mogi_10</v>
+        <v>mogi_11</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
@@ -1603,19 +1742,19 @@
         <v>campus</v>
       </c>
       <c r="D11" t="str">
-        <v>からあげ</v>
+        <v>串だんご</v>
       </c>
       <c r="E11" t="str">
-        <v>軽音楽部</v>
+        <v>東京海洋大学合気道部</v>
       </c>
       <c r="F11" t="str">
-        <v>揚げ立てのからあげを販売いたします！ また、バンド発表も行います！</v>
+        <v>屋外テントにてお団子を販売しています！お好きな生地のお団子とお好きな餡・たれを選んで、ぜひおいしい串団子を片手に海王祭をお楽しみください！！</v>
       </c>
       <c r="G11">
-        <v>35.6675385</v>
+        <v>35.6674927</v>
       </c>
       <c r="H11">
-        <v>139.7912031</v>
+        <v>139.7912581</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -1624,12 +1763,12 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>29-越中島軽音部.png</v>
+        <v>31-合気道部.png</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>mogi_11</v>
+        <v>mogi_12</v>
       </c>
       <c r="B12" t="b">
         <v>1</v>
@@ -1638,19 +1777,19 @@
         <v>campus</v>
       </c>
       <c r="D12" t="str">
-        <v>串だんご</v>
+        <v>ホットドッグ、フランクフルト</v>
       </c>
       <c r="E12" t="str">
-        <v>東京海洋大学合気道部</v>
+        <v>越中島硬式テニス部</v>
       </c>
       <c r="F12" t="str">
-        <v>合気道部は屋外テントにてお団子を販売しています！お好きな生地のお団子とお好きな餡・たれを選んで、ぜひおいしい串団子を片手に海王祭をお楽しみください！！</v>
+        <v>パリッとジューシーなフランクフルトとそれをバンズでサンドして熱々に仕上げたホットドッグです！</v>
       </c>
       <c r="G12">
-        <v>35.6674927</v>
+        <v>35.6673587</v>
       </c>
       <c r="H12">
-        <v>139.7912581</v>
+        <v>139.7912568</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -1659,12 +1798,12 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>31-合気道部.png</v>
+        <v>31-越中島硬式テニス部.png</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>mogi_12</v>
+        <v>mogi_13</v>
       </c>
       <c r="B13" t="b">
         <v>1</v>
@@ -1673,19 +1812,19 @@
         <v>campus</v>
       </c>
       <c r="D13" t="str">
-        <v>ホットドッグ、フランクフルト</v>
+        <v>チョコバナナ</v>
       </c>
       <c r="E13" t="str">
-        <v>越中島硬式テニス部</v>
+        <v>男子バレーボール部</v>
       </c>
       <c r="F13" t="str">
-        <v>パリッとジューシーなフランクフルトとそれをバンズでサンドして熱々に仕上げたホットドッグです！</v>
+        <v>毎年人気のチョコバナナを今年も販売します！</v>
       </c>
       <c r="G13">
-        <v>35.6673587</v>
+        <v>35.6673293</v>
       </c>
       <c r="H13">
-        <v>139.7912568</v>
+        <v>139.7912923</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -1694,12 +1833,12 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>31-越中島硬式テニス部.png</v>
+        <v>31-男子バレー部.png</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>mogi_13</v>
+        <v>mogi_14</v>
       </c>
       <c r="B14" t="b">
         <v>1</v>
@@ -1708,19 +1847,19 @@
         <v>campus</v>
       </c>
       <c r="D14" t="str">
-        <v>チョコバナナ</v>
+        <v>山名物！！ポテトフライ</v>
       </c>
       <c r="E14" t="str">
-        <v>男子バレーボール部</v>
+        <v>山岳部</v>
       </c>
       <c r="F14" t="str">
-        <v>毎年人気のチョコバナナを今年も販売します！暑い日にぴったりなバナナスムージーも販売するのでぜひご賞味ください！</v>
+        <v>カリッカリに揚がってます！</v>
       </c>
       <c r="G14">
-        <v>35.6673293</v>
+        <v>35.6673015</v>
       </c>
       <c r="H14">
-        <v>139.7912923</v>
+        <v>139.7913285</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -1729,12 +1868,12 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>31-男子バレー部.png</v>
+        <v>31-山岳部.png</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>mogi_14</v>
+        <v>mogi_15</v>
       </c>
       <c r="B15" t="b">
         <v>1</v>
@@ -1743,19 +1882,19 @@
         <v>campus</v>
       </c>
       <c r="D15" t="str">
-        <v>山名物！！ポテトフライ</v>
+        <v>青いチュロス</v>
       </c>
       <c r="E15" t="str">
-        <v>山岳部</v>
+        <v>バスケットボール部</v>
       </c>
       <c r="F15" t="str">
-        <v>カリッカリに揚がってます！</v>
+        <v>外はサクサク，中はもちっと。 海を感じる特別なチュロスにしました！</v>
       </c>
       <c r="G15">
-        <v>35.6673015</v>
+        <v>35.6672748</v>
       </c>
       <c r="H15">
-        <v>139.7913285</v>
+        <v>139.791358</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -1764,12 +1903,12 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>31-山岳部.png</v>
+        <v>31-バスケットボール部.png</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>mogi_15</v>
+        <v>mogi_16</v>
       </c>
       <c r="B16" t="b">
         <v>1</v>
@@ -1778,19 +1917,19 @@
         <v>campus</v>
       </c>
       <c r="D16" t="str">
-        <v>チュロス</v>
+        <v>本格パエリア</v>
       </c>
       <c r="E16" t="str">
-        <v>バスケットボール部</v>
+        <v>木曜会</v>
       </c>
       <c r="F16" t="str">
-        <v>外はサクサク，中はもちっと。 海を感じる特別なチュロスにしました！</v>
+        <v>スペインの味を500円で楽しめる！海の幸や鶏肉の旨味が、お米一粒一粒に閉じ込められた贅沢パエリア♪</v>
       </c>
       <c r="G16">
-        <v>35.6672748</v>
+        <v>35.6672481</v>
       </c>
       <c r="H16">
-        <v>139.791358</v>
+        <v>139.7913929</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -1799,12 +1938,12 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>31-バスケットボール部.png</v>
+        <v>31-木曜会.png</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>mogi_16</v>
+        <v>mogi_17</v>
       </c>
       <c r="B17" t="b">
         <v>1</v>
@@ -1813,19 +1952,19 @@
         <v>campus</v>
       </c>
       <c r="D17" t="str">
-        <v>本格パエリア</v>
+        <v>揚げアイス</v>
       </c>
       <c r="E17" t="str">
-        <v>木曜会</v>
+        <v>ネットボール部</v>
       </c>
       <c r="F17" t="str">
-        <v>スペインの味を500円で楽しめる！海の幸や鶏肉の旨味が、お米一粒一粒に閉じ込められた贅沢パエリア♪</v>
+        <v>ネットボール部にかける思いのようにひんやりアイスをサクッと揚げます！ ぜひご賞味あれ！</v>
       </c>
       <c r="G17">
-        <v>35.6672481</v>
+        <v>35.6672182</v>
       </c>
       <c r="H17">
-        <v>139.7913929</v>
+        <v>139.7914325</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -1834,12 +1973,12 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>31-木曜会.png</v>
+        <v>33-ネットボール部.png</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>mogi_17</v>
+        <v>mogi_18</v>
       </c>
       <c r="B18" t="b">
         <v>1</v>
@@ -1848,19 +1987,19 @@
         <v>campus</v>
       </c>
       <c r="D18" t="str">
-        <v>揚げアイス</v>
+        <v>特製スタミナ油そば</v>
       </c>
       <c r="E18" t="str">
-        <v>ネットボール部</v>
+        <v>東京海洋大学・水泳部</v>
       </c>
       <c r="F18" t="str">
-        <v>ネットボール部にかける思いのようにひんやりアイスをサクッと揚げます！ ぜひご賞味あれ！</v>
+        <v>いつもは大会等があり、参加を見送ることが多かった我々水泳部ですが、今回の海王祭では満を持して出店させていただきます。水泳部が一丸となって作った油そば食べてみたくなりませんか！？</v>
       </c>
       <c r="G18">
-        <v>35.6672182</v>
+        <v>35.6671822</v>
       </c>
       <c r="H18">
-        <v>139.7914325</v>
+        <v>139.7914767</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1869,12 +2008,12 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>33-ネットボール部.png</v>
+        <v>33-水泳部.png</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>mogi_18</v>
+        <v>mogi_19</v>
       </c>
       <c r="B19" t="b">
         <v>1</v>
@@ -1883,19 +2022,19 @@
         <v>campus</v>
       </c>
       <c r="D19" t="str">
-        <v>特製スタミナ油そば</v>
+        <v>輸血パックドリンク</v>
       </c>
       <c r="E19" t="str">
-        <v>東京海洋大学・水泳部</v>
+        <v>お嬢様部&amp;ピューロランド部</v>
       </c>
       <c r="F19" t="str">
-        <v>いつもは大会等があり、参加を見送ることが多かった我々水泳部ですが、今回の海王祭りでは満を持して出店させていただきます。水泳部が一丸となって作った油そば食べてみたくなりませんか！？</v>
+        <v>お嬢様部とピューロランド部のコラボ！ワクワク満点の輸血パックドリンク！</v>
       </c>
       <c r="G19">
-        <v>35.6671822</v>
+        <v>35.6671501</v>
       </c>
       <c r="H19">
-        <v>139.7914767</v>
+        <v>139.7915176</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1904,12 +2043,12 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>33-水泳部.png</v>
+        <v>33-お嬢様_ピューロランド部.png</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>mogi_19</v>
+        <v>mogi_20</v>
       </c>
       <c r="B20" t="b">
         <v>1</v>
@@ -1918,19 +2057,19 @@
         <v>campus</v>
       </c>
       <c r="D20" t="str">
-        <v>輸血パックドリンク</v>
+        <v>空手部のお好み焼き</v>
       </c>
       <c r="E20" t="str">
-        <v>お嬢様部&amp;ピューロランド部</v>
+        <v>空手道部</v>
       </c>
       <c r="F20" t="str">
-        <v>お嬢様部とピューロランド部のコラボ！ワクワク満点の輸血パックドリンク！</v>
-      </c>
-      <c r="G20">
-        <v>35.6671501</v>
-      </c>
-      <c r="H20">
-        <v>139.7915176</v>
+        <v>広島出身の部員監修によるお好み焼きです！こだわった一品をぜひ。</v>
+      </c>
+      <c r="G20" t="str">
+        <v>35.6671239</v>
+      </c>
+      <c r="H20" t="str">
+        <v>139.7915538</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1939,12 +2078,12 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>33-お嬢様_ピューロランド部.png</v>
+        <v>33-空手道部.png</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mogi_20</v>
+        <v>mogi_21</v>
       </c>
       <c r="B21" t="b">
         <v>1</v>
@@ -1953,19 +2092,19 @@
         <v>campus</v>
       </c>
       <c r="D21" t="str">
-        <v>空手部のお好み焼き</v>
+        <v>最適解ワッフル</v>
       </c>
       <c r="E21" t="str">
-        <v>空手道部</v>
+        <v>芝浦祭実行委員会</v>
       </c>
       <c r="F21" t="str">
-        <v>広島出身の部員監修によるお好み焼きです！こだわった一品をぜひ。</v>
+        <v>ミックスベリーを乗せた最適解ワッフルを販売いたします！ ソースはチョコ、イチゴ、ブルーベリー、 メープルをご用意しております。</v>
       </c>
       <c r="G21" t="str">
-        <v>35.6671239</v>
+        <v>35.6670940</v>
       </c>
       <c r="H21" t="str">
-        <v>139.7915538</v>
+        <v>139.7915914</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1974,12 +2113,12 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>33-空手道部.png</v>
+        <v>33-芝浦祭実行委員会.png</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>mogi_21</v>
+        <v>mogi_22</v>
       </c>
       <c r="B22" t="b">
         <v>1</v>
@@ -1988,19 +2127,19 @@
         <v>campus</v>
       </c>
       <c r="D22" t="str">
-        <v>最適解ワッフル</v>
+        <v>カニレース</v>
       </c>
       <c r="E22" t="str">
-        <v>芝浦祭実行委員会</v>
+        <v>ネクトンカフェ</v>
       </c>
       <c r="F22" t="str">
-        <v>ミックスベリーを乗せた最適解ワッフルを 販売いたします！ ソースはチョコ、イチゴ、ブルーベリー、 メープルをご用意しております。</v>
+        <v>サワガニ釣りとサワガニレースをします。 一位の方には景品をプレゼント！</v>
       </c>
       <c r="G22" t="str">
-        <v>35.6670940</v>
+        <v>35.6670624</v>
       </c>
       <c r="H22" t="str">
-        <v>139.7915914</v>
+        <v>139.7916276</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -2009,12 +2148,12 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>33-芝浦祭実行委員会.png</v>
+        <v>33-ネクトンカフェ.png</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>mogi_22</v>
+        <v>mogi_23</v>
       </c>
       <c r="B23" t="b">
         <v>1</v>
@@ -2023,19 +2162,19 @@
         <v>campus</v>
       </c>
       <c r="D23" t="str">
-        <v>カニレース</v>
+        <v>魚介ラーメン</v>
       </c>
       <c r="E23" t="str">
-        <v>ネクトンカフェ</v>
+        <v>あさり会</v>
       </c>
       <c r="F23" t="str">
-        <v>サワガニ釣りとサワガニレースをします。 一位の方には景品をプレゼント！</v>
+        <v>品川キャンパスから来ました、あさり会です。品川キャンパスらしく魚介料理を提供します。品川キャンパス自治委員会委員長推奨のおいしい料理をぜひご賞味ください。</v>
       </c>
       <c r="G23" t="str">
-        <v>35.6670624</v>
+        <v>35.6670275</v>
       </c>
       <c r="H23" t="str">
-        <v>139.7916276</v>
+        <v>139.7916739</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -2044,12 +2183,12 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>33-ネクトンカフェ.png</v>
+        <v>35-あさり会.png</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>mogi_23</v>
+        <v>mogi_24</v>
       </c>
       <c r="B24" t="b">
         <v>1</v>
@@ -2058,19 +2197,19 @@
         <v>campus</v>
       </c>
       <c r="D24" t="str">
-        <v>魚介ラーメン</v>
+        <v>門仲晃一</v>
       </c>
       <c r="E24" t="str">
-        <v>あさり会</v>
+        <v>門仲晃一</v>
       </c>
       <c r="F24" t="str">
-        <v>品川キャンパスから来ました、あさり会です。品川キャンパスらしく魚介料理を提供します。品川キャンパス自治委員会委員長推奨のおいしい料理をぜひご賞味ください。</v>
+        <v>クリームチーズが入ったライスコロッケ！！チキンライスとカレーピラフの２種類あります！！門仲晃一定番、特製唐揚げもご用意！！</v>
       </c>
       <c r="G24" t="str">
-        <v>35.6670275</v>
+        <v>35.6669894</v>
       </c>
       <c r="H24" t="str">
-        <v>139.7916739</v>
+        <v>139.7917195</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -2079,12 +2218,12 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>35-あさり会.png</v>
+        <v>35-門仲晃一.png</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>mogi_24</v>
+        <v>mogi_25</v>
       </c>
       <c r="B25" t="b">
         <v>1</v>
@@ -2093,19 +2232,19 @@
         <v>campus</v>
       </c>
       <c r="D25" t="str">
-        <v>門仲晃一</v>
+        <v>クジラ肉の竜田揚げ</v>
       </c>
       <c r="E25" t="str">
-        <v>門仲晃一</v>
+        <v>剣道部</v>
       </c>
       <c r="F25" t="str">
-        <v>クリームチーズが入ったライスコロッケ！！チキンライスとカレーピラフの２種類あります！！門仲晃一定番、特製唐揚げもご用意！！</v>
-      </c>
-      <c r="G25" t="str">
-        <v>35.6669894</v>
-      </c>
-      <c r="H25" t="str">
-        <v>139.7917195</v>
+        <v>珍しいクジラ肉の唐揚げを販売いたします！ 香ばしく揚げた一品を、ぜひご賞味ください。</v>
+      </c>
+      <c r="G25">
+        <v>35.6669469</v>
+      </c>
+      <c r="H25">
+        <v>139.7917631</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -2114,12 +2253,12 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>35-門仲晃一.png</v>
+        <v>35-剣道部.png</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>mogi_25</v>
+        <v>mogi_26</v>
       </c>
       <c r="B26" t="b">
         <v>1</v>
@@ -2128,19 +2267,19 @@
         <v>campus</v>
       </c>
       <c r="D26" t="str">
-        <v>クジラ肉の唐揚げ</v>
+        <v>シェイク</v>
       </c>
       <c r="E26" t="str">
-        <v>剣道部</v>
+        <v>カヌー部</v>
       </c>
       <c r="F26" t="str">
-        <v>珍しいクジラ肉の唐揚げを販売いたします！ 香ばしく揚げた一品を、ぜひご賞味ください。</v>
+        <v>カヌー部では、いちご・抹茶・キャラメル・ コーヒー・オレオから選べるシェイクを販売しています。 ぜひお越しください！</v>
       </c>
       <c r="G26">
-        <v>35.6669469</v>
+        <v>35.6669082</v>
       </c>
       <c r="H26">
-        <v>139.7917631</v>
+        <v>139.7918093</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -2149,12 +2288,12 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>35-剣道部.png</v>
+        <v>35-カヌー部.png</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>mogi_26</v>
+        <v>mogi_27</v>
       </c>
       <c r="B27" t="b">
         <v>1</v>
@@ -2163,19 +2302,19 @@
         <v>campus</v>
       </c>
       <c r="D27" t="str">
-        <v>シェイク</v>
+        <v>海鮮焼きそば</v>
       </c>
       <c r="E27" t="str">
-        <v>カヌー部</v>
+        <v>東京海洋大学ヨット部</v>
       </c>
       <c r="F27" t="str">
-        <v>カヌー部では、いちご・抹茶・キャラメル・ コーヒー・オレオから選べるシェイクを 販売しています。 ぜひお越しください！</v>
+        <v>海鮮のうまみがたっぷり入った焼きそばを販売いたします！</v>
       </c>
       <c r="G27">
-        <v>35.6669082</v>
+        <v>35.666875</v>
       </c>
       <c r="H27">
-        <v>139.7918093</v>
+        <v>139.7918502</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -2184,12 +2323,12 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>35-カヌー部.png</v>
+        <v>35-ヨット部.png</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>mogi_27</v>
+        <v>mogi_28</v>
       </c>
       <c r="B28" t="b">
         <v>1</v>
@@ -2198,19 +2337,19 @@
         <v>campus</v>
       </c>
       <c r="D28" t="str">
-        <v>海鮮焼そば</v>
+        <v>焼きグソクムシ</v>
       </c>
       <c r="E28" t="str">
-        <v>東京海洋大学ヨット部</v>
+        <v>オーケストラ部</v>
       </c>
       <c r="F28" t="str">
-        <v>海鮮のうまみがたっぷり入った焼きそばを 販売いたします！</v>
+        <v>オーケストラ部です！テントにて焼きグソクムシ、焼き鳥、ラムネの販売、ス ーパーボールすくいをいたしま す！ぜひお越しください！</v>
       </c>
       <c r="G28">
-        <v>35.666875</v>
+        <v>35.6668396</v>
       </c>
       <c r="H28">
-        <v>139.7918502</v>
+        <v>139.7918925</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -2219,12 +2358,12 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>35-ヨット部.png</v>
+        <v>35-オーケストラ部.png</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>mogi_28</v>
+        <v>mogi_29</v>
       </c>
       <c r="B29" t="b">
         <v>1</v>
@@ -2233,19 +2372,19 @@
         <v>campus</v>
       </c>
       <c r="D29" t="str">
-        <v>焼きグソクムシ販売・アンサンブル他</v>
+        <v>海洋大グッズ、瓶飲料、ヨーヨーつり</v>
       </c>
       <c r="E29" t="str">
-        <v>東京海洋大学・共立薬科大学管弦楽団</v>
+        <v>東京海洋大学越中島生協学生委員会</v>
       </c>
       <c r="F29" t="str">
-        <v>オーケストラ部です！テントにて焼きグソクムシ、焼き鳥、ラムネの販売、ス ーパーボールすくい、教室にてアンサンブルおよびグッズ販売をいたしま す！ぜひお越しください！</v>
+        <v>生協学生委員会では、海洋大グッズ、瓶飲料の販売と水風船釣りを行います！ぜひ一度覗いてみてください！！</v>
       </c>
       <c r="G29">
-        <v>35.6668396</v>
+        <v>35.6669616</v>
       </c>
       <c r="H29">
-        <v>139.7918925</v>
+        <v>139.7918931</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -2254,12 +2393,12 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>35-オーケストラ部.png</v>
+        <v>37-越中島生協学生委員会.png</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>mogi_29</v>
+        <v>mogi_30</v>
       </c>
       <c r="B30" t="b">
         <v>1</v>
@@ -2268,19 +2407,19 @@
         <v>campus</v>
       </c>
       <c r="D30" t="str">
-        <v>海洋大グッズ、瓶飲料、ヨーヨーつり</v>
+        <v>ベビーカステラ</v>
       </c>
       <c r="E30" t="str">
-        <v>東京海洋大学越中島生協学生委員会</v>
+        <v>海事普及会</v>
       </c>
       <c r="F30" t="str">
-        <v>生協学生委員会では、海洋大グッズ、瓶飲料の販売と水風船釣りを行います！ぜひ一度覗いてみてください！！</v>
-      </c>
-      <c r="G30">
-        <v>35.6669616</v>
-      </c>
-      <c r="H30">
-        <v>139.7918931</v>
+        <v>ふんわり甘いベビーカステラを販売します。 食べ歩きにぜひどうぞ！ トッピングもございます！</v>
+      </c>
+      <c r="G30" t="str">
+        <v>35.6669229</v>
+      </c>
+      <c r="H30" t="str">
+        <v>139.7919428</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -2289,12 +2428,12 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>37-越中島生協学生委員会.png</v>
+        <v>37-海事普及会.png</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>mogi_30</v>
+        <v>mogi_31</v>
       </c>
       <c r="B31" t="b">
         <v>1</v>
@@ -2303,19 +2442,19 @@
         <v>campus</v>
       </c>
       <c r="D31" t="str">
-        <v>ベビーカステラ</v>
+        <v>防衛省自衛隊 事業紹介</v>
       </c>
       <c r="E31" t="str">
-        <v>海事普及会</v>
+        <v>防衛省自衛隊 東京地方協力本部江東出張所</v>
       </c>
       <c r="F31" t="str">
-        <v>ふんわり甘いベビーカステラを販売します。 食べ歩きにぜひどうぞ！ トッピングもございます！</v>
+        <v>自衛隊の仕事や魅力をわかりやすく紹介するブースです。職業内容の説明に加え、VRによる臨場感ある体験や制服試着体験も実施し、実際の雰囲気を感じていただけます。少しでも興味のある方におすすめです。なお、16日のみ防衛装備庁も参加予定です。</v>
       </c>
       <c r="G31" t="str">
-        <v>35.6669229</v>
+        <v>35.6668842</v>
       </c>
       <c r="H31" t="str">
-        <v>139.7919428</v>
+        <v>139.7919837</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -2324,47 +2463,53 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>37-海事普及会.png</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>37-防衛省自衛隊東京地方協力本部江東出張所.png</v>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
       <c r="A32" t="str">
-        <v>mogi_31</v>
+        <v>mogi_32</v>
       </c>
       <c r="B32" t="b">
         <v>1</v>
       </c>
       <c r="C32" t="str">
-        <v>campus</v>
+        <v>1-1</v>
       </c>
       <c r="D32" t="str">
-        <v>防衛省自衛隊 事業紹介</v>
+        <v>志馬なにがし先生</v>
       </c>
       <c r="E32" t="str">
-        <v>防衛省自衛隊 東京地方協力本部江東出張所</v>
-      </c>
-      <c r="F32" t="str">
-        <v>自衛隊の仕事や魅力をわかりやすく紹介するブースです。職業内容の説明に加え、VRによる臨場感ある体験や制服試着体験も実施し、実際の雰囲気を感じていただけます。少しでも興味のある方におすすめです。なお、16日のみ防衛装備庁も参加予定です。</v>
+        <v>志馬なにがし先生</v>
+      </c>
+      <c r="F32" t="str" xml:space="preserve">
+        <v xml:space="preserve">・トークショー
+・サイン会
+・パネル展示
+本学出身作家志馬なにがし先生の作品に関連した企画です！！
+※本イベントの参加には模擬店テント1.海王祭実行委員会にて書籍の購入が必要です。
+パネル展示:5/16(土)15:00〜15:30
+トークショー:5/16(土)15:00〜16:00</v>
       </c>
       <c r="G32" t="str">
-        <v>35.6668842</v>
+        <v/>
       </c>
       <c r="H32" t="str">
-        <v>139.7919837</v>
+        <v/>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>0.195886</v>
       </c>
       <c r="J32" t="str">
-        <v/>
+        <v>0.099155</v>
       </c>
       <c r="K32" t="str">
-        <v>37-防衛省自衛隊東京地方協力本部江東出張所.png</v>
+        <v>25-志馬なにがし先生.png</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>mogi_32</v>
+        <v>mogi_33</v>
       </c>
       <c r="B33" t="b">
         <v>1</v>
@@ -2373,13 +2518,13 @@
         <v>1-1</v>
       </c>
       <c r="D33" t="str">
-        <v>志馬なにがし先生</v>
+        <v>日本造船工業会</v>
       </c>
       <c r="E33" t="str">
-        <v>志馬なにがし先生</v>
+        <v>一般社団法人 日本造船工業会</v>
       </c>
       <c r="F33" t="str">
-        <v>本学出身作家志馬なにがし先生の作品に関連した企画です！！</v>
+        <v>壁新聞の展示と造船動画の放映。</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2388,18 +2533,18 @@
         <v/>
       </c>
       <c r="I33" t="str">
-        <v>0.195886</v>
+        <v>0.210400</v>
       </c>
       <c r="J33" t="str">
-        <v>0.099155</v>
+        <v>0.327169</v>
       </c>
       <c r="K33" t="str">
-        <v>25-志馬なにがし先生.png</v>
+        <v>25-日本造船工業会.png</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>mogi_33</v>
+        <v>mogi_34</v>
       </c>
       <c r="B34" t="b">
         <v>1</v>
@@ -2408,13 +2553,13 @@
         <v>1-1</v>
       </c>
       <c r="D34" t="str">
-        <v>日本造船工業会</v>
+        <v>郵船クルーズ株式会社 企業紹介/就職相談</v>
       </c>
       <c r="E34" t="str">
-        <v>一般社団法人 日本造船工業会</v>
+        <v>郵船クルーズ株式会社客船「飛鳥II」「飛鳥Ⅲ」運航〜日本郵船グループ〜</v>
       </c>
       <c r="F34" t="str">
-        <v>壁新聞の展示と造船動画の放映。</v>
+        <v>日本船籍最大級の客船「飛鳥II」、「飛鳥Ⅲ」を運航。業界のリーディングカンパニーとして、日本船籍ならではの「和のおもてなし」と「最幸の時間」の提供を目指します。</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2423,18 +2568,18 @@
         <v/>
       </c>
       <c r="I34" t="str">
-        <v>0.179293</v>
+        <v>0.094180</v>
       </c>
       <c r="J34" t="str">
-        <v>0.331117</v>
+        <v>0.416992</v>
       </c>
       <c r="K34" t="str">
-        <v>25-日本造船工業会.png</v>
+        <v>25-郵船クルーズ株式会社.png</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>mogi_34</v>
+        <v>mogi_35</v>
       </c>
       <c r="B35" t="b">
         <v>1</v>
@@ -2443,13 +2588,13 @@
         <v>1-1</v>
       </c>
       <c r="D35" t="str">
-        <v>郵船クルーズ株式会社客船「飛鳥II」「飛鳥Ⅲ」運航〜日本郵船グループ〜</v>
+        <v>日本海事代理士会 関東支部</v>
       </c>
       <c r="E35" t="str">
-        <v>郵船クルーズ株式会社</v>
+        <v>日本海事代理士会 関東支部</v>
       </c>
       <c r="F35" t="str">
-        <v>日本船籍最大級の客船「飛鳥II」、「飛鳥Ⅲ」を運航。業界のリーディングカンパニーとして、日本船籍ならではの「和のおもてなし」と「最幸の時間」を提供を目指します。</v>
+        <v>ブースでは、海事代理士による無料法令相談を行います。模擬店では、軽食提供等を行います。どなたでもお気軽にお立ち寄りください。</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2458,18 +2603,18 @@
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>0.112847</v>
+        <v>0.208330</v>
       </c>
       <c r="J35" t="str">
-        <v>0.419954</v>
+        <v>0.616381</v>
       </c>
       <c r="K35" t="str">
-        <v>25-郵船クルーズ株式会社.png</v>
+        <v>25-日本海事代理士会_関東支部.png</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>mogi_35</v>
+        <v>mogi_36</v>
       </c>
       <c r="B36" t="b">
         <v>1</v>
@@ -2478,13 +2623,13 @@
         <v>1-1</v>
       </c>
       <c r="D36" t="str">
-        <v>日本海事代理士会 関東支部</v>
+        <v>じゃず喫茶</v>
       </c>
       <c r="E36" t="str">
-        <v>日本海事代理士会 関東支部</v>
+        <v>ブラスバンド部</v>
       </c>
       <c r="F36" t="str">
-        <v>ブースでは、海事代理士による無料法令相談を行います。模擬店では、軽食提供等を行います。どなたでもお気軽にお立ち寄りください。</v>
+        <v>珈琲やお茶菓子などを販売しています。飛び入りセッションも可能です。休憩所として、是非ご利用ください！</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2493,18 +2638,18 @@
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>0.180328</v>
+        <v>0.092104</v>
       </c>
       <c r="J36" t="str">
-        <v>0.617368</v>
+        <v>0.703244</v>
       </c>
       <c r="K36" t="str">
-        <v>25-日本海事代理士会_関東支部.png</v>
+        <v>25-ブラスバンド部.png</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>mogi_36</v>
+        <v>mogi_37</v>
       </c>
       <c r="B37" t="b">
         <v>1</v>
@@ -2513,13 +2658,13 @@
         <v>1-1</v>
       </c>
       <c r="D37" t="str">
-        <v>じゃず喫茶</v>
+        <v>戦没船を記録する会</v>
       </c>
       <c r="E37" t="str">
-        <v>ブラスバンド部</v>
+        <v>戦没船を記録する会</v>
       </c>
       <c r="F37" t="str">
-        <v>珈琲やお茶菓子などを販売しています。飛び入りセッションも可能です。休憩所として、是非ご利用ください！</v>
+        <v>当会のパネルを展示し、DVDを放映する。</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2528,68 +2673,79 @@
         <v/>
       </c>
       <c r="I37" t="str">
-        <v>0.116998</v>
+        <v>0.197947</v>
       </c>
       <c r="J37" t="str">
-        <v>0.709166</v>
+        <v>0.909542</v>
       </c>
       <c r="K37" t="str">
-        <v>25-ブラスバンド部.png</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>25-戦没船を記録する会.png</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
       <c r="A38" t="str">
-        <v>mogi_37</v>
+        <v>mogi_53</v>
       </c>
       <c r="B38" t="b">
         <v>1</v>
       </c>
       <c r="C38" t="str">
-        <v>1-1</v>
+        <v>campus</v>
       </c>
       <c r="D38" t="str">
-        <v>戦没船を記録する会</v>
+        <v>「帆船を語る」—岐路に立つ帆船と、その先の未来へ—</v>
       </c>
       <c r="E38" t="str">
-        <v>戦没船を記録する会</v>
-      </c>
-      <c r="F38" t="str">
-        <v>当会のパネルを展示し、DVDを放映する。</v>
+        <v>主催: 日本海洋塾</v>
+      </c>
+      <c r="F38" t="str" xml:space="preserve">
+        <v xml:space="preserve">【詳しくはこちら→】https://kaiyou-juku.org/event/index.html
+― 岐路に立つ帆船と、その先の未来へ ―
+商船大OB会組織「日本海洋塾」主催により、第66回海王祭にて特別講演を開催します。 日本の帆船運航・教育の第一線を担ってきたお二人をお迎えし、対面およびオンラインで実施します。
+■講演① 5月16日（土）午後1時～3時 小原朋尚 氏 元「みらいへ」船長／笹川平和財団 海洋政策研究所
+■講演② 5月17日（日）午後1時～3時 國枝佳明 氏 元 海王丸船長（航海訓練所）　元 東京海洋大学教授 現 富山高等専門学校 校長
+■会場 東京海洋大学 越中島キャンパス 明治丸ミュージアム・セミナー室（明治丸横、百周年記念館裏）
+■オンライン配信あり（全国から参加可能）　ZOOM招待QRコード添付
+▼日本海洋塾 公式掲載ページ
+https://www.kaioufes.com/event/indoor
+帆船は、単なる「懐かしい乗り物」ではありません。 大航海時代から積み上げられてきた、人類の知恵の結晶であり、機能美の極致です。 風を読み、海を感じ、自然と向き合いながら航海する—— そこには、現代の高度な技術社会においても失われてはならない、本質的な学びがあります。
+今、帆船は岐路に立っています。 しかしそれは終わりではなく、次の時代への出発点です。 これからの海事を担う学生たちには、帆船を通じて自然と対話する力を身につけ、 数年後の海洋分野における劇的・革新の先頭に立ってほしい—— その思いを込めた講演です。
+海事関係者、学生、そして海に関心のあるすべての方へ。 ぜひご参加ください。</v>
       </c>
       <c r="G38" t="str">
-        <v/>
+        <v>35.6678615</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>139.7903308</v>
       </c>
       <c r="I38" t="str">
-        <v>0.197947</v>
+        <v/>
       </c>
       <c r="J38" t="str">
-        <v>0.909542</v>
+        <v/>
       </c>
       <c r="K38" t="str">
-        <v>25-戦没船を記録する会.png</v>
+        <v>日本海洋塾_講演会.webp</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>mogi_48</v>
+        <v>mogi_58</v>
       </c>
       <c r="B39" t="b">
         <v>1</v>
       </c>
       <c r="C39" t="str">
-        <v>exp-1-3</v>
+        <v>2-1</v>
       </c>
       <c r="D39" t="str">
-        <v>航路論研究室</v>
+        <v>白鷗席</v>
       </c>
       <c r="E39" t="str">
-        <v>航路論研究室</v>
+        <v>茶道部</v>
       </c>
       <c r="F39" t="str">
-        <v>実際の船舶運航時に用いられる紙海図の展示・説明を行います。</v>
+        <v>お茶会を開催いたします。 ぜひお越しください。</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2598,33 +2754,33 @@
         <v/>
       </c>
       <c r="I39" t="str">
-        <v>0.935795</v>
+        <v>0.675296</v>
       </c>
       <c r="J39" t="str">
-        <v>0.880508</v>
+        <v>0.477203</v>
       </c>
       <c r="K39" t="str">
-        <v/>
+        <v>39-茶道部.png</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>mogi_49</v>
+        <v>mogi_59</v>
       </c>
       <c r="B40" t="b">
         <v>1</v>
       </c>
       <c r="C40" t="str">
-        <v>exp-4-5</v>
+        <v>2-1</v>
       </c>
       <c r="D40" t="str">
-        <v>情報通信工学研究室</v>
+        <v>アンサンブル</v>
       </c>
       <c r="E40" t="str">
-        <v>情報通信工学研究室</v>
+        <v>オーケストラ部</v>
       </c>
       <c r="F40" t="str">
-        <v>はじめての人でも楽しめる内容です！！GPS/GNSSを知りたい人・衛星に興味がある人はぜひ一度遊びに来てください～</v>
+        <v>オーケストラ部です！テントにて焼きグソクムシ、焼き鳥、ラムネの販売、スーパーボールすくい、教室にてアンサンブルおよびグッズ販売をいたします！ぜひお越しください！</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2633,33 +2789,33 @@
         <v/>
       </c>
       <c r="I40" t="str">
-        <v>0.926683</v>
+        <v>0.546643</v>
       </c>
       <c r="J40" t="str">
-        <v>0.224924</v>
+        <v>0.171122</v>
       </c>
       <c r="K40" t="str">
-        <v/>
+        <v>39-オーケストラ部.png</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>mogi_50</v>
+        <v>mogi_60</v>
       </c>
       <c r="B41" t="b">
         <v>1</v>
       </c>
       <c r="C41" t="str">
-        <v>campus</v>
+        <v>2-1</v>
       </c>
       <c r="D41" t="str">
-        <v>スタンプラリー</v>
+        <v>VRで体感！建造中の商船を見学してみよう！</v>
       </c>
       <c r="E41" t="str">
-        <v>海王祭実行委員</v>
+        <v>今治造船株式会社</v>
       </c>
       <c r="F41" t="str">
-        <v>台紙配布：正門受付　景品渡し：本部（明治丸前広場）研究室公開、学内敷地の展示物に配置してあるスタンプを５つ集めよう！</v>
+        <v>VRゴーグルを装着することで、まるで造船所にいるかのような没入感のある見学体験が可能です。</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2668,33 +2824,34 @@
         <v/>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>0.415865</v>
       </c>
       <c r="J41" t="str">
-        <v/>
+        <v>0.470085</v>
       </c>
       <c r="K41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42">
+        <v>39-今治造船株式会社.png</v>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
       <c r="A42" t="str">
-        <v>mogi_51</v>
+        <v>mogi_61</v>
       </c>
       <c r="B42" t="b">
         <v>1</v>
       </c>
       <c r="C42" t="str">
-        <v>exp-1-1</v>
+        <v>2-1</v>
       </c>
       <c r="D42" t="str">
-        <v>研究室公開！　垂直循環型回流水槽</v>
+        <v>海事教育のご案内と学校説明</v>
       </c>
       <c r="E42" t="str">
-        <v>垂直循環型回流水槽</v>
-      </c>
-      <c r="F42" t="str">
-        <v>実験水槽の公開を行います！</v>
+        <v>広島商船高等専門学校</v>
+      </c>
+      <c r="F42" t="str" xml:space="preserve">
+        <v xml:space="preserve">広島商船高等専門学校では、海事教育の魅力や本校の特色を紹介するブースを出展します。ブースでは、航海士・機関士をはじめとした海事分野の学びや、商船高専での学生生活について分かりやすく紹介したパンフレットを配布します。また、ご来場いただいた方には、広島商船高等専門学校オリジナルボールペンをプレゼントします。
+海や船、ものづくりに興味のある方はもちろん、進路を考えている中高生や保護者の皆さまも、ぜひお気軽にお立ち寄りください。</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2703,33 +2860,35 @@
         <v/>
       </c>
       <c r="I42" t="str">
-        <v>0.412840</v>
+        <v>0.843416</v>
       </c>
       <c r="J42" t="str">
-        <v>0.816487</v>
+        <v>0.178240</v>
       </c>
       <c r="K42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43">
+        <v>39-広島商船高等専門学校.png</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
       <c r="A43" t="str">
-        <v>mogi_52</v>
+        <v>mogi_76</v>
       </c>
       <c r="B43" t="b">
         <v>1</v>
       </c>
       <c r="C43" t="str">
-        <v>exp-3-6</v>
+        <v>2-1</v>
       </c>
       <c r="D43" t="str">
-        <v>電池推進船のペーパークラフトやってみない？</v>
+        <v>世界の海をかけて巡る船乗りを育てる　商船高専展</v>
       </c>
       <c r="E43" t="str">
-        <v>電気動力研究室</v>
-      </c>
-      <c r="F43" t="str">
-        <v>第3実験棟6階602 対象：小学生～　参加費無料 10:30～15:00</v>
+        <v>富山高等専門学校 広島商船高等専門学校</v>
+      </c>
+      <c r="F43" t="str" xml:space="preserve">
+        <v xml:space="preserve">ブースでは、海図の読み方とロープワークも学べる海図バッグの制作体験、
+令和 8 年 3 月に竣工した練習船「若潮丸」の紹介、質問コーナーを実施して
+います 。ぜひお立ち寄りください。</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2738,33 +2897,33 @@
         <v/>
       </c>
       <c r="I43" t="str">
-        <v>0.653470</v>
+        <v>0.843417</v>
       </c>
       <c r="J43" t="str">
-        <v>0.299943</v>
+        <v>0.178241</v>
       </c>
       <c r="K43" t="str">
-        <v/>
+        <v>39-富山高等専門学校・広島商船高等専門学校.png</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>mogi_53</v>
+        <v>mogi_62</v>
       </c>
       <c r="B44" t="b">
         <v>1</v>
       </c>
       <c r="C44" t="str">
-        <v>campus</v>
+        <v>2-2</v>
       </c>
       <c r="D44" t="str">
-        <v>「帆船を語る」—岐路に立つ帆船と、その先の未来へ—</v>
+        <v>魚拓体験</v>
       </c>
       <c r="E44" t="str">
-        <v>主催　日本海洋塾</v>
+        <v>igoan ユネスコクラブ</v>
       </c>
       <c r="F44" t="str">
-        <v>東京海洋大越中島キャンパスの前身、東京商船大OB会組織「日本海洋塾」主催により、第66回海王祭にて特別講演を開催します。</v>
+        <v>魚に関する授業と魚拓体験を行います！ 楽しみながら魚について学んでみませんか？</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2773,33 +2932,33 @@
         <v/>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>0.859998</v>
       </c>
       <c r="J44" t="str">
-        <v/>
+        <v>0.147567</v>
       </c>
       <c r="K44" t="str">
-        <v>27-日本海洋塾.png</v>
+        <v>39-igoanユネスコクラブ.png</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>mogi_58</v>
+        <v>mogi_63</v>
       </c>
       <c r="B45" t="b">
         <v>1</v>
       </c>
       <c r="C45" t="str">
-        <v>2-1</v>
+        <v>2-2</v>
       </c>
       <c r="D45" t="str">
-        <v>白鷗席</v>
+        <v>ボードゲームカフェ</v>
       </c>
       <c r="E45" t="str">
-        <v>茶道部</v>
+        <v>ボードゲームサークル</v>
       </c>
       <c r="F45" t="str">
-        <v>お茶会を開催いたします。 ぜひお越しください。</v>
+        <v>競りが体験できるカードゲーム「おさかな Marketer」販売中！</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2808,33 +2967,33 @@
         <v/>
       </c>
       <c r="I45" t="str">
-        <v>0.675296</v>
+        <v>0.853771</v>
       </c>
       <c r="J45" t="str">
-        <v>0.477203</v>
+        <v>0.450424</v>
       </c>
       <c r="K45" t="str">
-        <v>39-茶道部.png</v>
+        <v>39-ボードゲームサークル.png</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>mogi_59</v>
+        <v>mogi_64</v>
       </c>
       <c r="B46" t="b">
         <v>1</v>
       </c>
       <c r="C46" t="str">
-        <v>2-1</v>
+        <v>2-2</v>
       </c>
       <c r="D46" t="str">
-        <v>アンサンブル</v>
+        <v>出張うみがめ研究会</v>
       </c>
       <c r="E46" t="str">
-        <v>オーケストラ部</v>
+        <v>うみがめ研究会</v>
       </c>
       <c r="F46" t="str">
-        <v>オーケストラ部です！テントにて焼きグソクムシ、焼き鳥、ラムネの販売、スーパーボールすくい、教室にてアンサンブルおよびグッズ販売をいたします！ぜひお越しください！</v>
+        <v>ウミガメ展示やウミガメ教室を行います。 さらに亀卵クッキーを販売いたします！</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2843,33 +3002,33 @@
         <v/>
       </c>
       <c r="I46" t="str">
-        <v>0.546643</v>
+        <v>0.534194</v>
       </c>
       <c r="J46" t="str">
-        <v>0.171122</v>
+        <v>0.454554</v>
       </c>
       <c r="K46" t="str">
-        <v>39-オーケストラ部.png</v>
+        <v>40-うみがめ研究会.png</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>mogi_60</v>
+        <v>mogi_65</v>
       </c>
       <c r="B47" t="b">
         <v>1</v>
       </c>
       <c r="C47" t="str">
-        <v>2-1</v>
+        <v>ettyu-1</v>
       </c>
       <c r="D47" t="str">
-        <v>VRで体感！建造中の商船を見学してみよう！</v>
+        <v>缶バッジづくり</v>
       </c>
       <c r="E47" t="str">
-        <v>今治造船株式会社</v>
+        <v>Killer Whale Lab.</v>
       </c>
       <c r="F47" t="str">
-        <v>VRゴーグルを装着することで、まるで造船所にいるかのような没入感のある見学体験が可能です。</v>
+        <v>クジラに関する展示とシャチラボでしか 入手できないオリジナルグッズの販売、そして缶バッジづくりのコーナーを行っています！</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2878,33 +3037,33 @@
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>0.415865</v>
+        <v>0.374462</v>
       </c>
       <c r="J47" t="str">
-        <v>0.470085</v>
+        <v>0.461934</v>
       </c>
       <c r="K47" t="str">
-        <v>39-今治造船株式会社.png</v>
+        <v>41-KillerWhaleLab.png</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>mogi_61</v>
+        <v>mogi_67</v>
       </c>
       <c r="B48" t="b">
         <v>1</v>
       </c>
       <c r="C48" t="str">
-        <v>2-1</v>
+        <v>ettyu-1</v>
       </c>
       <c r="D48" t="str">
-        <v>世界の海をかけて巡る船乗りを育てる　商船高専展（富山）</v>
+        <v>休憩所</v>
       </c>
       <c r="E48" t="str">
-        <v>富山高等専門学校 広島商船高等専門学校</v>
+        <v>海王祭実行委員会</v>
       </c>
       <c r="F48" t="str">
-        <v>ブースでは、海図の読み方とロープワークも学べる海図バッグの制作体験、令和 8 年 3 月に竣工した練習船「若潮丸」の紹介、質問コーナーを実施しています。</v>
+        <v>休憩所として学生食堂(ワールドマリンカフェ)を開放しております。お食事や休憩にぜひご利用ください。</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2913,33 +3072,33 @@
         <v/>
       </c>
       <c r="I48" t="str">
-        <v>0.843416</v>
+        <v>0.641174</v>
       </c>
       <c r="J48" t="str">
-        <v>0.178240</v>
+        <v>0.800634</v>
       </c>
       <c r="K48" t="str">
-        <v>39-富山高等専門学校・広島商船高等専門学校.png</v>
+        <v>41-休憩所.png</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>mogi_62</v>
+        <v>mogi_68</v>
       </c>
       <c r="B49" t="b">
         <v>1</v>
       </c>
       <c r="C49" t="str">
-        <v>2-2</v>
+        <v>ettyu-1</v>
       </c>
       <c r="D49" t="str">
-        <v>魚拓体験</v>
+        <v>海王祭展</v>
       </c>
       <c r="E49" t="str">
-        <v>igoan ユネスコクラブ</v>
+        <v>越中島写真部</v>
       </c>
       <c r="F49" t="str">
-        <v>魚に関する授業と魚拓体験を行います！ 楽しみながら魚について学んでみませんか？</v>
+        <v>新体制となった後の初めての展示です。ぜひお越しください。</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2948,33 +3107,33 @@
         <v/>
       </c>
       <c r="I49" t="str">
-        <v>0.859998</v>
+        <v>0.638060</v>
       </c>
       <c r="J49" t="str">
-        <v>0.147567</v>
+        <v>0.933473</v>
       </c>
       <c r="K49" t="str">
-        <v>39-igoanユネスコクラブ.png</v>
+        <v>41-越中島写真部.png</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>mogi_63</v>
+        <v>mogi_69</v>
       </c>
       <c r="B50" t="b">
         <v>1</v>
       </c>
       <c r="C50" t="str">
-        <v>2-2</v>
+        <v>ettyu-1</v>
       </c>
       <c r="D50" t="str">
-        <v>ボードゲームカフェ</v>
+        <v>ロボット展示</v>
       </c>
       <c r="E50" t="str">
-        <v>ボードゲームサークル</v>
+        <v>ロボット研究会</v>
       </c>
       <c r="F50" t="str">
-        <v>競りが体験できるカードゲーム「おさかな Marketer」販売中！</v>
+        <v>当サークルで製作したロボットの展示・紹介及び一部機体の飛行展示を行います。</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2983,88 +3142,88 @@
         <v/>
       </c>
       <c r="I50" t="str">
-        <v>0.853771</v>
+        <v>0.486531</v>
       </c>
       <c r="J50" t="str">
-        <v>0.450424</v>
+        <v>0.421538</v>
       </c>
       <c r="K50" t="str">
-        <v>39-ボードゲームサークル.png</v>
+        <v>41-ロボット研究会.png</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>mogi_64</v>
+        <v>mogi_70</v>
       </c>
       <c r="B51" t="b">
         <v>1</v>
       </c>
       <c r="C51" t="str">
-        <v>2-2</v>
+        <v>campus</v>
       </c>
       <c r="D51" t="str">
-        <v>出張うみがめ研究会</v>
+        <v>飛行展示</v>
       </c>
       <c r="E51" t="str">
-        <v>うみがめ研究会</v>
+        <v>ロボット研究会</v>
       </c>
       <c r="F51" t="str">
-        <v>ウミガメ展示やウミガメ教室を行います。 さらに亀卵クッキーを販売いたします！</v>
+        <v>当サークルで製作したロボットの展示・紹介及び一部機体の飛行展示を行います。</v>
       </c>
       <c r="G51" t="str">
-        <v/>
+        <v>35.6678512</v>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>139.7931585</v>
       </c>
       <c r="I51" t="str">
-        <v>0.534194</v>
+        <v/>
       </c>
       <c r="J51" t="str">
-        <v>0.454554</v>
+        <v/>
       </c>
       <c r="K51" t="str">
-        <v>40-うみがめ研究会.png</v>
+        <v>41-ロボット研究会.png</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>mogi_65</v>
+        <v>mogi_71</v>
       </c>
       <c r="B52" t="b">
         <v>1</v>
       </c>
       <c r="C52" t="str">
-        <v>ettyu-1</v>
+        <v>campus</v>
       </c>
       <c r="D52" t="str">
-        <v>缶バッジづくり</v>
+        <v>ラジコン展示</v>
       </c>
       <c r="E52" t="str">
-        <v>Killer Whale Lab.</v>
+        <v>ロボット研究会</v>
       </c>
       <c r="F52" t="str">
-        <v>クジラに関する展示とシャチラボでしか 入手できないオリジナルグッズの販売、そして缶バッジづくりのコーナーを行っています！</v>
+        <v>当サークルで製作したロボットの展示・紹介及び一部機体の飛行展示を行います。</v>
       </c>
       <c r="G52" t="str">
-        <v/>
+        <v>35.6676175</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>139.7899894</v>
       </c>
       <c r="I52" t="str">
-        <v>0.374462</v>
+        <v/>
       </c>
       <c r="J52" t="str">
-        <v>0.461934</v>
+        <v/>
       </c>
       <c r="K52" t="str">
-        <v>41-KillerWhaleLab.png</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>41-ロボット研究会.png</v>
+      </c>
+    </row>
+    <row r="53" xml:space="preserve">
       <c r="A53" t="str">
-        <v>mogi_67</v>
+        <v>mogi_72</v>
       </c>
       <c r="B53" t="b">
         <v>1</v>
@@ -3073,19 +3232,20 @@
         <v>campus</v>
       </c>
       <c r="D53" t="str">
-        <v>休憩所</v>
+        <v>試乗会</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
-      <c r="F53" t="str">
-        <v>休憩所として学生食堂(ワールドマリンカフェ)を開放しております。お食事や休憩にぜひご利用ください。</v>
+      <c r="F53" t="str" xml:space="preserve">
+        <v xml:space="preserve">越中島キャンパスの訓練用船舶に乗船できる試乗会を実施します。
+事前抽選制で、当日抽選は実施しません。</v>
       </c>
       <c r="G53" t="str">
-        <v/>
+        <v>35.6661243</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>139.7921808</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -3094,27 +3254,27 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>41-休憩所.png</v>
+        <v>49-試乗会.png</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>mogi_68</v>
+        <v>mogi_73</v>
       </c>
       <c r="B54" t="b">
         <v>1</v>
       </c>
       <c r="C54" t="str">
-        <v>campus</v>
+        <v>ettyu-1</v>
       </c>
       <c r="D54" t="str">
-        <v>海王祭展</v>
+        <v>NePPパネル展示</v>
       </c>
       <c r="E54" t="str">
-        <v>越中島写真部</v>
+        <v>東京海洋大学プログラミングサークルNePP</v>
       </c>
       <c r="F54" t="str">
-        <v>新体制となった後の初めての展示です。ぜひお越しください。</v>
+        <v>プログラミングサークルNePPのパネル展示です。実行委員会屋内本部に併設予定。</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3123,33 +3283,33 @@
         <v/>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>0.631808</v>
       </c>
       <c r="J54" t="str">
-        <v/>
+        <v>0.443290</v>
       </c>
       <c r="K54" t="str">
-        <v>41-越中島写真部.png</v>
+        <v>41-プログラミングサークルNePP.png</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>mogi_69</v>
+        <v>lab_01</v>
       </c>
       <c r="B55" t="b">
         <v>1</v>
       </c>
       <c r="C55" t="str">
-        <v>ettyu-1</v>
+        <v>exp-3-5</v>
       </c>
       <c r="D55" t="str">
-        <v>ロボット展示</v>
+        <v>電気動力研究室 研究室公開</v>
       </c>
       <c r="E55" t="str">
-        <v>ロボット研究会</v>
+        <v/>
       </c>
       <c r="F55" t="str">
-        <v>当サークルで製作したロボットの展示・紹介及び一部機体の飛行展示を行います。</v>
+        <v>船の省エネや陸電導入、陸上の電気設備まで！電気が好きなら来るしかない！</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3158,33 +3318,33 @@
         <v/>
       </c>
       <c r="I55" t="str">
-        <v>0.486531</v>
+        <v>0.601611</v>
       </c>
       <c r="J55" t="str">
-        <v>0.421538</v>
+        <v>0.680813</v>
       </c>
       <c r="K55" t="str">
-        <v>41-ロボット研究会.png</v>
+        <v>電気動力研究室.webp</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>mogi_70</v>
+        <v>lab_02</v>
       </c>
       <c r="B56" t="b">
         <v>1</v>
       </c>
       <c r="C56" t="str">
-        <v>campus</v>
+        <v>exp-1-3</v>
       </c>
       <c r="D56" t="str">
-        <v>飛行展示</v>
+        <v>航路論研究室</v>
       </c>
       <c r="E56" t="str">
-        <v>ロボット研究会</v>
+        <v>航路論研究室</v>
       </c>
       <c r="F56" t="str">
-        <v>当サークルで製作したロボットの展示・紹介及び一部機体の飛行展示を行います。</v>
+        <v>実際の船舶運航時に用いられる紙海図の展示・説明を行います。</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3193,33 +3353,33 @@
         <v/>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>0.935795</v>
       </c>
       <c r="J56" t="str">
-        <v/>
+        <v>0.880508</v>
       </c>
       <c r="K56" t="str">
-        <v>41-ロボット研究会.png</v>
+        <v>航路論研究室.webp</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>mogi_71</v>
+        <v>lab_03</v>
       </c>
       <c r="B57" t="b">
         <v>1</v>
       </c>
       <c r="C57" t="str">
-        <v>campus</v>
+        <v>exp-4-5</v>
       </c>
       <c r="D57" t="str">
-        <v>ラジコン展示</v>
+        <v>情報通信工学研究室</v>
       </c>
       <c r="E57" t="str">
-        <v>ロボット研究会</v>
+        <v>情報通信工学研究室</v>
       </c>
       <c r="F57" t="str">
-        <v>当サークルで製作したロボットの展示・紹介及び一部機体の飛行展示を行います。</v>
+        <v>はじめての人でも楽しめる内容です！！GPS/GNSSを知りたい人・衛星に興味がある人はぜひ一度遊びに来てください～</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3228,33 +3388,33 @@
         <v/>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>0.617480</v>
       </c>
       <c r="J57" t="str">
-        <v/>
+        <v>0.230658</v>
       </c>
       <c r="K57" t="str">
-        <v>41-ロボット研究会.png</v>
+        <v>情報通信工学研究室.webp</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mogi_72</v>
+        <v>lab_04</v>
       </c>
       <c r="B58" t="b">
         <v>1</v>
       </c>
       <c r="C58" t="str">
-        <v>campus</v>
+        <v>exp-1-1</v>
       </c>
       <c r="D58" t="str">
-        <v>試乗会</v>
+        <v>研究室公開！　垂直循環型回流水槽</v>
       </c>
       <c r="E58" t="str">
-        <v>女子カッター部、男子カッター部、海王祭実行委員会</v>
+        <v>垂直循環型回流水槽</v>
       </c>
       <c r="F58" t="str">
-        <v>越中島キャンパスの訓練用船舶に乗船できる試乗会を実施します。</v>
+        <v>実験水槽の公開を行います！</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3263,33 +3423,33 @@
         <v/>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>0.412840</v>
       </c>
       <c r="J58" t="str">
-        <v/>
+        <v>0.816487</v>
       </c>
       <c r="K58" t="str">
-        <v>49-試乗会.png</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>mogi_73</v>
+        <v>lab_05</v>
       </c>
       <c r="B59" t="b">
         <v>1</v>
       </c>
       <c r="C59" t="str">
-        <v>ettyu-1</v>
+        <v>exp-3-6</v>
       </c>
       <c r="D59" t="str">
-        <v>NePPパネル展示</v>
+        <v>電池推進船のペーパークラフトやってみない？</v>
       </c>
       <c r="E59" t="str">
-        <v>東京海洋大学プログラミングサークルNePP</v>
+        <v>電気動力研究室</v>
       </c>
       <c r="F59" t="str">
-        <v>プログラミングサークルNePPのパネル展示です。実行委員会屋内本部に併設予定。</v>
+        <v>第3実験棟6階602 対象：小学生～　参加費無料 10:30～15:00</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3298,13 +3458,13 @@
         <v/>
       </c>
       <c r="I59" t="str">
-        <v>0.631808</v>
+        <v>0.653470</v>
       </c>
       <c r="J59" t="str">
-        <v>0.443290</v>
+        <v>0.299943</v>
       </c>
       <c r="K59" t="str">
-        <v>41-プログラミングサークルNePP.png</v>
+        <v>電気動力研究室_ペーパークラフト.webp</v>
       </c>
     </row>
     <row r="60">
@@ -35717,16 +35877,541 @@
         <v/>
       </c>
     </row>
+    <row r="986">
+      <c r="A986" t="str">
+        <v/>
+      </c>
+      <c r="B986" t="str">
+        <v/>
+      </c>
+      <c r="C986" t="str">
+        <v/>
+      </c>
+      <c r="D986" t="str">
+        <v/>
+      </c>
+      <c r="E986" t="str">
+        <v/>
+      </c>
+      <c r="F986" t="str">
+        <v/>
+      </c>
+      <c r="G986" t="str">
+        <v/>
+      </c>
+      <c r="H986" t="str">
+        <v/>
+      </c>
+      <c r="I986" t="str">
+        <v/>
+      </c>
+      <c r="J986" t="str">
+        <v/>
+      </c>
+      <c r="K986" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="str">
+        <v/>
+      </c>
+      <c r="B987" t="str">
+        <v/>
+      </c>
+      <c r="C987" t="str">
+        <v/>
+      </c>
+      <c r="D987" t="str">
+        <v/>
+      </c>
+      <c r="E987" t="str">
+        <v/>
+      </c>
+      <c r="F987" t="str">
+        <v/>
+      </c>
+      <c r="G987" t="str">
+        <v/>
+      </c>
+      <c r="H987" t="str">
+        <v/>
+      </c>
+      <c r="I987" t="str">
+        <v/>
+      </c>
+      <c r="J987" t="str">
+        <v/>
+      </c>
+      <c r="K987" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="str">
+        <v/>
+      </c>
+      <c r="B988" t="str">
+        <v/>
+      </c>
+      <c r="C988" t="str">
+        <v/>
+      </c>
+      <c r="D988" t="str">
+        <v/>
+      </c>
+      <c r="E988" t="str">
+        <v/>
+      </c>
+      <c r="F988" t="str">
+        <v/>
+      </c>
+      <c r="G988" t="str">
+        <v/>
+      </c>
+      <c r="H988" t="str">
+        <v/>
+      </c>
+      <c r="I988" t="str">
+        <v/>
+      </c>
+      <c r="J988" t="str">
+        <v/>
+      </c>
+      <c r="K988" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="str">
+        <v/>
+      </c>
+      <c r="B989" t="str">
+        <v/>
+      </c>
+      <c r="C989" t="str">
+        <v/>
+      </c>
+      <c r="D989" t="str">
+        <v/>
+      </c>
+      <c r="E989" t="str">
+        <v/>
+      </c>
+      <c r="F989" t="str">
+        <v/>
+      </c>
+      <c r="G989" t="str">
+        <v/>
+      </c>
+      <c r="H989" t="str">
+        <v/>
+      </c>
+      <c r="I989" t="str">
+        <v/>
+      </c>
+      <c r="J989" t="str">
+        <v/>
+      </c>
+      <c r="K989" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="str">
+        <v/>
+      </c>
+      <c r="B990" t="str">
+        <v/>
+      </c>
+      <c r="C990" t="str">
+        <v/>
+      </c>
+      <c r="D990" t="str">
+        <v/>
+      </c>
+      <c r="E990" t="str">
+        <v/>
+      </c>
+      <c r="F990" t="str">
+        <v/>
+      </c>
+      <c r="G990" t="str">
+        <v/>
+      </c>
+      <c r="H990" t="str">
+        <v/>
+      </c>
+      <c r="I990" t="str">
+        <v/>
+      </c>
+      <c r="J990" t="str">
+        <v/>
+      </c>
+      <c r="K990" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="str">
+        <v/>
+      </c>
+      <c r="B991" t="str">
+        <v/>
+      </c>
+      <c r="C991" t="str">
+        <v/>
+      </c>
+      <c r="D991" t="str">
+        <v/>
+      </c>
+      <c r="E991" t="str">
+        <v/>
+      </c>
+      <c r="F991" t="str">
+        <v/>
+      </c>
+      <c r="G991" t="str">
+        <v/>
+      </c>
+      <c r="H991" t="str">
+        <v/>
+      </c>
+      <c r="I991" t="str">
+        <v/>
+      </c>
+      <c r="J991" t="str">
+        <v/>
+      </c>
+      <c r="K991" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="str">
+        <v/>
+      </c>
+      <c r="B992" t="str">
+        <v/>
+      </c>
+      <c r="C992" t="str">
+        <v/>
+      </c>
+      <c r="D992" t="str">
+        <v/>
+      </c>
+      <c r="E992" t="str">
+        <v/>
+      </c>
+      <c r="F992" t="str">
+        <v/>
+      </c>
+      <c r="G992" t="str">
+        <v/>
+      </c>
+      <c r="H992" t="str">
+        <v/>
+      </c>
+      <c r="I992" t="str">
+        <v/>
+      </c>
+      <c r="J992" t="str">
+        <v/>
+      </c>
+      <c r="K992" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="str">
+        <v/>
+      </c>
+      <c r="B993" t="str">
+        <v/>
+      </c>
+      <c r="C993" t="str">
+        <v/>
+      </c>
+      <c r="D993" t="str">
+        <v/>
+      </c>
+      <c r="E993" t="str">
+        <v/>
+      </c>
+      <c r="F993" t="str">
+        <v/>
+      </c>
+      <c r="G993" t="str">
+        <v/>
+      </c>
+      <c r="H993" t="str">
+        <v/>
+      </c>
+      <c r="I993" t="str">
+        <v/>
+      </c>
+      <c r="J993" t="str">
+        <v/>
+      </c>
+      <c r="K993" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="str">
+        <v/>
+      </c>
+      <c r="B994" t="str">
+        <v/>
+      </c>
+      <c r="C994" t="str">
+        <v/>
+      </c>
+      <c r="D994" t="str">
+        <v/>
+      </c>
+      <c r="E994" t="str">
+        <v/>
+      </c>
+      <c r="F994" t="str">
+        <v/>
+      </c>
+      <c r="G994" t="str">
+        <v/>
+      </c>
+      <c r="H994" t="str">
+        <v/>
+      </c>
+      <c r="I994" t="str">
+        <v/>
+      </c>
+      <c r="J994" t="str">
+        <v/>
+      </c>
+      <c r="K994" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="str">
+        <v/>
+      </c>
+      <c r="B995" t="str">
+        <v/>
+      </c>
+      <c r="C995" t="str">
+        <v/>
+      </c>
+      <c r="D995" t="str">
+        <v/>
+      </c>
+      <c r="E995" t="str">
+        <v/>
+      </c>
+      <c r="F995" t="str">
+        <v/>
+      </c>
+      <c r="G995" t="str">
+        <v/>
+      </c>
+      <c r="H995" t="str">
+        <v/>
+      </c>
+      <c r="I995" t="str">
+        <v/>
+      </c>
+      <c r="J995" t="str">
+        <v/>
+      </c>
+      <c r="K995" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="str">
+        <v/>
+      </c>
+      <c r="B996" t="str">
+        <v/>
+      </c>
+      <c r="C996" t="str">
+        <v/>
+      </c>
+      <c r="D996" t="str">
+        <v/>
+      </c>
+      <c r="E996" t="str">
+        <v/>
+      </c>
+      <c r="F996" t="str">
+        <v/>
+      </c>
+      <c r="G996" t="str">
+        <v/>
+      </c>
+      <c r="H996" t="str">
+        <v/>
+      </c>
+      <c r="I996" t="str">
+        <v/>
+      </c>
+      <c r="J996" t="str">
+        <v/>
+      </c>
+      <c r="K996" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="str">
+        <v/>
+      </c>
+      <c r="B997" t="str">
+        <v/>
+      </c>
+      <c r="C997" t="str">
+        <v/>
+      </c>
+      <c r="D997" t="str">
+        <v/>
+      </c>
+      <c r="E997" t="str">
+        <v/>
+      </c>
+      <c r="F997" t="str">
+        <v/>
+      </c>
+      <c r="G997" t="str">
+        <v/>
+      </c>
+      <c r="H997" t="str">
+        <v/>
+      </c>
+      <c r="I997" t="str">
+        <v/>
+      </c>
+      <c r="J997" t="str">
+        <v/>
+      </c>
+      <c r="K997" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="str">
+        <v/>
+      </c>
+      <c r="B998" t="str">
+        <v/>
+      </c>
+      <c r="C998" t="str">
+        <v/>
+      </c>
+      <c r="D998" t="str">
+        <v/>
+      </c>
+      <c r="E998" t="str">
+        <v/>
+      </c>
+      <c r="F998" t="str">
+        <v/>
+      </c>
+      <c r="G998" t="str">
+        <v/>
+      </c>
+      <c r="H998" t="str">
+        <v/>
+      </c>
+      <c r="I998" t="str">
+        <v/>
+      </c>
+      <c r="J998" t="str">
+        <v/>
+      </c>
+      <c r="K998" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="str">
+        <v/>
+      </c>
+      <c r="B999" t="str">
+        <v/>
+      </c>
+      <c r="C999" t="str">
+        <v/>
+      </c>
+      <c r="D999" t="str">
+        <v/>
+      </c>
+      <c r="E999" t="str">
+        <v/>
+      </c>
+      <c r="F999" t="str">
+        <v/>
+      </c>
+      <c r="G999" t="str">
+        <v/>
+      </c>
+      <c r="H999" t="str">
+        <v/>
+      </c>
+      <c r="I999" t="str">
+        <v/>
+      </c>
+      <c r="J999" t="str">
+        <v/>
+      </c>
+      <c r="K999" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="str">
+        <v/>
+      </c>
+      <c r="B1000" t="str">
+        <v/>
+      </c>
+      <c r="C1000" t="str">
+        <v/>
+      </c>
+      <c r="D1000" t="str">
+        <v/>
+      </c>
+      <c r="E1000" t="str">
+        <v/>
+      </c>
+      <c r="F1000" t="str">
+        <v/>
+      </c>
+      <c r="G1000" t="str">
+        <v/>
+      </c>
+      <c r="H1000" t="str">
+        <v/>
+      </c>
+      <c r="I1000" t="str">
+        <v/>
+      </c>
+      <c r="J1000" t="str">
+        <v/>
+      </c>
+      <c r="K1000" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K985"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1000"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:L1000"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -35748,21 +36433,27 @@
         <v>description</v>
       </c>
       <c r="G1" t="str">
+        <v>sunny_loc</v>
+      </c>
+      <c r="H1" t="str">
+        <v>rainy_loc</v>
+      </c>
+      <c r="I1" t="str">
         <v>start_time</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>end_time</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>need_ticket_when_rainy</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>img_name</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1-01</v>
+        <v>01</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
@@ -35776,19 +36467,25 @@
       <c r="E2" t="str">
         <v>海王祭実行委員会</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H2" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I2">
         <v>0.3645833333333333</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>0.375</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>実行委員会.png</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>1-02</v>
+        <v>02</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
@@ -35806,19 +36503,25 @@
         <v xml:space="preserve">海王祭のオープニングを飾るのは、東京海洋大学のダンス部 EXSEAD。
 鍛え上げられたパフォーマンスで、明治丸前ステージを一気に祭りモードへ切り替えます。</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H3" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I3">
         <v>0.375</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>0.4166666666666667</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>ダンス部ステージ.png</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>1-03</v>
+        <v>03</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
@@ -35836,19 +36539,25 @@
         <v xml:space="preserve">陸上自衛隊 第1師団 第1音楽隊による、迫力の演奏ステージ。
 金管楽器を中心としたアンサンブル演奏を、ぜひ会場でお聞きください！</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H4" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I4">
         <v>0.4305555555555556</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>0.4722222222222222</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
         <v>自衛隊音楽隊ステージ.png</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>1-04</v>
+        <v>04</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
@@ -35870,19 +36579,25 @@
 - 第二部「船のエンジンを動かす 機関士の世界をのぞいて、しってみよう」（川崎汽船株式会社）
 - 第三部「船を操縦する人 航海士の世界をのぞいて、しってみよう」（日本郵船株式会社）</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H5" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I5">
         <v>0.4930555555555556</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>0.5625</v>
       </c>
-      <c r="J5" t="str">
+      <c r="L5" t="str">
         <v>実行委員会.png</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1-05</v>
+        <v>05</v>
       </c>
       <c r="B6" t="b">
         <v>0</v>
@@ -35893,16 +36608,22 @@
       <c r="D6" t="str">
         <v>さかなクン準備</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H6" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I6">
         <v>0.5625</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>1-06</v>
+        <v>06</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
@@ -35921,22 +36642,28 @@
 目の前で描き上がる迫力満点のイラストと、ギョギョっと驚くお話をお見逃しなく！
 雨天時: 現時点では整理券による先着案内となる予定です。整理券は当日5/16(土)午前9時30分より整列開始、午前10時30分より配布開始いたします。混雑状況により時間は前後する可能性がございます。</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H7" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I7">
         <v>0.5833333333333334</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>0.6041666666666666</v>
       </c>
-      <c r="I7" t="b">
+      <c r="K7" t="b">
         <v>1</v>
       </c>
-      <c r="J7" t="str">
+      <c r="L7" t="str">
         <v>さかなクンステージ.png</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
       <c r="A8" t="str">
-        <v>1-07</v>
+        <v>07</v>
       </c>
       <c r="B8" t="b">
         <v>1</v>
@@ -35954,19 +36681,25 @@
         <v xml:space="preserve">越中島キャンパス唯一の軽音楽部による、約2時間のロングステージ。
 バンドサウンドが明治丸の前を駆け抜ける、海王祭1日目のクライマックスです。</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H8" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I8">
         <v>0.6180555555555556</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>0.7013888888888888</v>
       </c>
-      <c r="J8" t="str">
+      <c r="L8" t="str">
         <v>軽音楽部ステージ.png</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>1-08</v>
+        <v>08</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -35985,19 +36718,25 @@
 ビンゴカードは10:00から本部テントにて100円で販売中（売り切れ次第終了／お一人様 MAX 5枚まで）。
 協賛企業からの豪華景品を狙って、ぜひご参加ください！</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H9" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I9">
         <v>0.7083333333333334</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>0.75</v>
       </c>
-      <c r="J9" t="str">
+      <c r="L9" t="str">
         <v>実行委員会.png</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2-01</v>
+        <v>09</v>
       </c>
       <c r="B10" t="b">
         <v>1</v>
@@ -36014,19 +36753,25 @@
       <c r="F10" t="str">
         <v>「授業や学校生活、寮生活 編」</v>
       </c>
-      <c r="G10">
-        <v>0.3958333333333333</v>
-      </c>
-      <c r="H10">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="J10" t="str">
+      <c r="G10" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H10" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I10">
+        <v>0.4027777777777778</v>
+      </c>
+      <c r="J10">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="L10" t="str">
         <v>トークショーステージ.png</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
       <c r="A11" t="str">
-        <v>2-02</v>
+        <v>10</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
@@ -36046,19 +36791,25 @@
 業界のリーディングカンパニーとして、日本船籍ならではの「和のおもてなし」と「最幸の時間」の提供を目指す同社が、豪華客船の魅力とクルーズ業界の最新トレンドをお届けします。
 </v>
       </c>
-      <c r="G11">
+      <c r="G11" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H11" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I11">
         <v>0.4375</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>0.4583333333333333</v>
       </c>
-      <c r="J11" t="str">
+      <c r="L11" t="str">
         <v>あすかステージ.png</v>
       </c>
     </row>
     <row r="12" xml:space="preserve">
       <c r="A12" t="str">
-        <v>2-03</v>
+        <v>11</v>
       </c>
       <c r="B12" t="b">
         <v>1</v>
@@ -36070,29 +36821,62 @@
         <v>ポムポムプリンスペシャルステージ「ぱぴぷぺ Pom!」 ショー①</v>
       </c>
       <c r="F12" t="str" xml:space="preserve">
-        <v xml:space="preserve">雨天時: 整理券による先着案内となります
+        <v xml:space="preserve">晴天時：整理券不要。どなたでもご観覧いただけます。
+雨天時：整理券による先着案内となります。
 POMPOMPURIN 30th ANNIVERSARY スペシャルステージ「ぱぴぷぺ Pom!」が、海王祭にやってくる！
 こげ茶色のベレー帽がトレードマークの、ゴールデンレトリバーの男のコ・ポムポムプリンと一緒に、楽しいひとときをお過ごしください。
 ※ショーは1日2回公演（11:30 / 16:10）。公演内容は同じです。
 ※キャラクターの衣装は予告なく変更になる可能性がございます。
-© 2026 SANRIO CO., LTD. APPROVAL NO. P170206-1</v>
-      </c>
-      <c r="G12">
+■注意事項：
+【雨天時のリストバンドの配布について】
+・イベント当日朝10:30より、「越中島会館 NYKgroupラウンジ」にて全ての回の「入場用リストバンド」を配布いたします。ご希望の回をお選びください。
+・当日列の混雑状況によりリストバンド配布時間が前後する場合がございます。あらかじめご了承ください。
+・ショーとグリーティング共通の配布列となります。
+・リストバンドの配布は1グループにつき5枚までの配布となります。代表者様のみお並びすることも可能です。列に割って入る横入り行為はご遠慮ください。お連れ様との途中合流もお控えください。
+・一度に両方のショーのリストバンドを受け取ることはできません。あらかじめご了承ください。
+・リストバンドは1枚につき1名までのご入場とさせていただきます。
+【ショー・グリーティングの観覧について】
+・ショー・グリーティングは両方とも「越中島会館 2階 講堂」にて開催されます。
+・開演前に、リストバンドを着用されていないお客様には退場していただきます。
+・開演前にリストバンドをスタッフが確認いたします。確認できない場合観覧をお断り致します。リストバンドの再発行は致しかねますので、リストバンドは慎重に保管をお願いいたします。
+・座席は全席ブロック制の自由席です。リストバンドの表示と同じエリア内の座席に自由に座ることが出来ます。
+・他のブロックではご観覧できませんのでご了承ください。
+・ブロック内は自由席となります。空席を作らないよう、詰めてご利用ください。
+・荷物を置くことによる過剰な席取り（およそ20分以上）はご遠慮ください。
+・過剰な席取り行為が確認された場合、スタッフの判断により荷物などを会場外へ移動させていただく場合があります。
+・リストバンドの転売、譲渡⾏為を固く禁じます。
+・開演10分前までにお席にお越しください。
+【その他注意事項】
+・リストバンドは先着数に到達次第、配布を終了いたします。
+・晴天時のイベント観覧方式は『芝生上での立見席』となります。芝生エリアの最前列はお子様優先とさせていただいております。
+・芝生内へベビーカー等大型荷物のお持ち込みはできませんので、本部テント隣接のベビーカー置き場をご利用ください。
+・場所によってはステージが見えにくい、また混雑状況によっては入場を制限させていただくなど、確実にご観覧いただけるとは限りませんので、あらかじめご了承ください。
+・スタッフが記録用に写真撮影を行う場合がございます。あらかじめご了承ください。
+・諸般の事情により、時間・内容が変更・中止となる場合がございます。あらかじめ了承ください。
+・皆様に気持ちよくご参加いただけるよう、ご理解とご協力をお願いいたします。</v>
+      </c>
+      <c r="G12" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H12" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I12">
         <v>0.4791666666666667</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>0.5</v>
       </c>
-      <c r="I12" t="b">
+      <c r="K12" t="b">
         <v>1</v>
       </c>
-      <c r="J12" t="str">
+      <c r="L12" t="str">
         <v>ポムポムプリンステージ.png</v>
       </c>
     </row>
     <row r="13" xml:space="preserve">
       <c r="A13" t="str">
-        <v>2-04</v>
+        <v>12</v>
       </c>
       <c r="B13" t="b">
         <v>1</v>
@@ -36112,19 +36896,25 @@
 ※写真・動画を含む撮影はご遠慮いただいております。
 画像出典：防衛省</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H13" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I13">
         <v>0.5138888888888888</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>0.5416666666666666</v>
       </c>
-      <c r="J13" t="str">
+      <c r="L13" t="str">
         <v>自衛隊トークショーステージ.png</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
       <c r="A14" t="str">
-        <v>2-05</v>
+        <v>13</v>
       </c>
       <c r="B14" t="b">
         <v>1</v>
@@ -36136,87 +36926,161 @@
         <v>ポムポムプリンスペシャルステージ「ぱぴぷぺ Pom!」 グリーティング</v>
       </c>
       <c r="F14" t="str" xml:space="preserve">
-        <v xml:space="preserve">ポムポムプリンと直接ふれあえる、特別なグリーティングタイム！
-ぜひ会いに来てください。
-雨天時: 整理券による先着案内となります
-© 2026 SANRIO CO., LTD. APPROVAL NO. P170206-1</v>
-      </c>
-      <c r="G14">
-        <v>0.5694444444444444</v>
-      </c>
-      <c r="H14">
-        <v>0.5902777777777778</v>
-      </c>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="str">
-        <v>ポムポムプリンステージ.png</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>2-06</v>
-      </c>
-      <c r="B15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>46159</v>
-      </c>
-      <c r="D15" t="str">
-        <v>海洋大生トークショー ②（受験・実習編）</v>
-      </c>
-      <c r="F15" t="str">
-        <v>2回目のトークショーは、入試対策と海洋大ならではの「乗船実習」がテーマ。受験を控える高校生・中学生はぜひお越しください！</v>
-      </c>
-      <c r="G15">
-        <v>0.6388888888888888</v>
-      </c>
-      <c r="H15">
-        <v>0.6527777777777778</v>
-      </c>
-      <c r="J15" t="str">
-        <v>トークショーステージ.png</v>
-      </c>
-    </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16" t="str">
-        <v>2-07</v>
-      </c>
-      <c r="B16" t="b">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>46159</v>
-      </c>
-      <c r="D16" t="str">
-        <v>ポムポムプリンスペシャルステージ「ぱぴぷぺ Pom!」 ショー②</v>
-      </c>
-      <c r="F16" t="str" xml:space="preserve">
-        <v xml:space="preserve">POMPOMPURIN 30th ANNIVERSARY スペシャルステージ「ぱぴぷぺ Pom!」が、海王祭にやってくる！
+        <v xml:space="preserve">晴天時：整理券不要。どなたでもご観覧いただけます。
+雨天時：整理券による先着案内となります。
+POMPOMPURIN 30th ANNIVERSARY スペシャルステージ「ぱぴぷぺ Pom!」が、海王祭にやってくる！
 こげ茶色のベレー帽がトレードマークの、ゴールデンレトリバーの男のコ・ポムポムプリンと一緒に、楽しいひとときをお過ごしください。
 ※ショーは1日2回公演（11:30 / 16:10）。公演内容は同じです。
 ※キャラクターの衣装は予告なく変更になる可能性がございます。
-雨天時: 整理券による先着案内となります
-© 2026 SANRIO CO., LTD. APPROVAL NO. P170206-1</v>
-      </c>
-      <c r="G16">
+■注意事項：
+【雨天時のリストバンドの配布について】
+・イベント当日朝10:30より、「越中島会館 NYKgroupラウンジ」にて全ての回の「入場用リストバンド」を配布いたします。ご希望の回をお選びください。
+・当日列の混雑状況によりリストバンド配布時間が前後する場合がございます。あらかじめご了承ください。
+・ショーとグリーティング共通の配布列となります。
+・リストバンドの配布は1グループにつき5枚までの配布となります。代表者様のみお並びすることも可能です。列に割って入る横入り行為はご遠慮ください。お連れ様との途中合流もお控えください。
+・一度に両方のショーのリストバンドを受け取ることはできません。あらかじめご了承ください。
+・リストバンドは1枚につき1名までのご入場とさせていただきます。
+【ショー・グリーティングの観覧について】
+・ショー・グリーティングは両方とも「越中島会館 2階 講堂」にて開催されます。
+・開演前に、リストバンドを着用されていないお客様には退場していただきます。
+・開演前にリストバンドをスタッフが確認いたします。確認できない場合観覧をお断り致します。リストバンドの再発行は致しかねますので、リストバンドは慎重に保管をお願いいたします。
+・座席は全席ブロック制の自由席です。リストバンドの表示と同じエリア内の座席に自由に座ることが出来ます。
+・他のブロックではご観覧できませんのでご了承ください。
+・ブロック内は自由席となります。空席を作らないよう、詰めてご利用ください。
+・荷物を置くことによる過剰な席取り（およそ20分以上）はご遠慮ください。
+・過剰な席取り行為が確認された場合、スタッフの判断により荷物などを会場外へ移動させていただく場合があります。
+・リストバンドの転売、譲渡⾏為を固く禁じます。
+・開演10分前までにお席にお越しください。
+【その他注意事項】
+・リストバンドは先着数に到達次第、配布を終了いたします。
+・晴天時のイベント観覧方式は『芝生上での立見席』となります。芝生エリアの最前列はお子様優先とさせていただいております。
+・芝生内へベビーカー等大型荷物のお持ち込みはできませんので、本部テント隣接のベビーカー置き場をご利用ください。
+・場所によってはステージが見えにくい、また混雑状況によっては入場を制限させていただくなど、確実にご観覧いただけるとは限りませんので、あらかじめご了承ください。
+・スタッフが記録用に写真撮影を行う場合がございます。あらかじめご了承ください。
+・諸般の事情により、時間・内容が変更・中止となる場合がございます。あらかじめ了承ください。
+・皆様に気持ちよくご参加いただけるよう、ご理解とご協力をお願いいたします。</v>
+      </c>
+      <c r="G14" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H14" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I14">
+        <v>0.5694444444444444</v>
+      </c>
+      <c r="J14">
+        <v>0.5902777777777778</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="str">
+        <v>ポムポムプリンステージ.png</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>14</v>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>46159</v>
+      </c>
+      <c r="D15" t="str">
+        <v>海洋大生トークショー ②（受験・実習編）</v>
+      </c>
+      <c r="F15" t="str">
+        <v>2回目のトークショーは、入試対策と海洋大ならではの「乗船実習」がテーマ。受験を控える高校生・中学生はぜひお越しください！</v>
+      </c>
+      <c r="G15" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H15" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I15">
+        <v>0.6180555555555556</v>
+      </c>
+      <c r="J15">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="L15" t="str">
+        <v>トークショーステージ.png</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>15</v>
+      </c>
+      <c r="B16" t="b">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>46159</v>
+      </c>
+      <c r="D16" t="str">
+        <v>ポムポムプリンスペシャルステージ「ぱぴぷぺ Pom!」 ショー②</v>
+      </c>
+      <c r="F16" t="str" xml:space="preserve">
+        <v xml:space="preserve">晴天時：整理券不要。どなたでもご観覧いただけます。
+雨天時：整理券による先着案内となります。
+POMPOMPURIN 30th ANNIVERSARY スペシャルステージ「ぱぴぷぺ Pom!」が、海王祭にやってくる！
+こげ茶色のベレー帽がトレードマークの、ゴールデンレトリバーの男のコ・ポムポムプリンと一緒に、楽しいひとときをお過ごしください。
+※ショーは1日2回公演（11:30 / 16:10）。公演内容は同じです。
+※キャラクターの衣装は予告なく変更になる可能性がございます。
+■注意事項：
+【雨天時のリストバンドの配布について】
+・イベント当日朝10:30より、「越中島会館 NYKgroupラウンジ」にて全ての回の「入場用リストバンド」を配布いたします。ご希望の回をお選びください。
+・当日列の混雑状況によりリストバンド配布時間が前後する場合がございます。あらかじめご了承ください。
+・ショーとグリーティング共通の配布列となります。
+・リストバンドの配布は1グループにつき5枚までの配布となります。代表者様のみお並びすることも可能です。列に割って入る横入り行為はご遠慮ください。お連れ様との途中合流もお控えください。
+・一度に両方のショーのリストバンドを受け取ることはできません。あらかじめご了承ください。
+・リストバンドは1枚につき1名までのご入場とさせていただきます。
+【ショー・グリーティングの観覧について】
+・ショー・グリーティングは両方とも「越中島会館 2階 講堂」にて開催されます。
+・開演前に、リストバンドを着用されていないお客様には退場していただきます。
+・開演前にリストバンドをスタッフが確認いたします。確認できない場合観覧をお断り致します。リストバンドの再発行は致しかねますので、リストバンドは慎重に保管をお願いいたします。
+・座席は全席ブロック制の自由席です。リストバンドの表示と同じエリア内の座席に自由に座ることが出来ます。
+・他のブロックではご観覧できませんのでご了承ください。
+・ブロック内は自由席となります。空席を作らないよう、詰めてご利用ください。
+・荷物を置くことによる過剰な席取り（およそ20分以上）はご遠慮ください。
+・過剰な席取り行為が確認された場合、スタッフの判断により荷物などを会場外へ移動させていただく場合があります。
+・リストバンドの転売、譲渡⾏為を固く禁じます。
+・開演10分前までにお席にお越しください。
+【その他注意事項】
+・リストバンドは先着数に到達次第、配布を終了いたします。
+・晴天時のイベント観覧方式は『芝生上での立見席』となります。芝生エリアの最前列はお子様優先とさせていただいております。
+・芝生内へベビーカー等大型荷物のお持ち込みはできませんので、本部テント隣接のベビーカー置き場をご利用ください。
+・場所によってはステージが見えにくい、また混雑状況によっては入場を制限させていただくなど、確実にご観覧いただけるとは限りませんので、あらかじめご了承ください。
+・スタッフが記録用に写真撮影を行う場合がございます。あらかじめご了承ください。
+・諸般の事情により、時間・内容が変更・中止となる場合がございます。あらかじめ了承ください。
+・皆様に気持ちよくご参加いただけるよう、ご理解とご協力をお願いいたします。</v>
+      </c>
+      <c r="G16" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H16" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I16">
         <v>0.6736111111111112</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>0.6944444444444444</v>
       </c>
-      <c r="I16" t="b">
+      <c r="K16" t="b">
         <v>1</v>
       </c>
-      <c r="J16" t="str">
+      <c r="L16" t="str">
         <v>ポムポムプリンステージ.png</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2-08</v>
+        <v>16</v>
       </c>
       <c r="B17" t="b">
         <v>1</v>
@@ -36233,19 +37097,504 @@
       <c r="F17" t="str">
         <v>海王祭フィナーレを飾るビンゴ大会。両日参加できますので、1日目で当たらなかった方も、ぜひもう一度挑戦してください！</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="str">
+        <v>ステージ</v>
+      </c>
+      <c r="H17" t="str">
+        <v>越中島会館2F講堂</v>
+      </c>
+      <c r="I17">
         <v>0.7083333333333334</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>0.75</v>
       </c>
-      <c r="J17" t="str">
+      <c r="L17" t="str">
         <v>実行委員会.png</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>17</v>
+      </c>
+      <c r="B18" t="b">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>46158</v>
+      </c>
+      <c r="D18" t="str">
+        <v>プラネタリウム 【子供向けプログラム※子供優先】</v>
+      </c>
+      <c r="E18" t="str">
+        <v>海事普及会</v>
+      </c>
+      <c r="F18" t="str" xml:space="preserve">
+        <v xml:space="preserve">【詳細はこちら→】https://www.kaioufes.com/event/planetarium
+海王祭では毎年、海事普及会によるプラネタリウムの上映を行っています。
+国産現役最古のプラネタリウムが映し出す星空を東京海洋大学ならではの見方でぜひご覧ください。
+※当日、上映時間外でもプラネタリウムをご見学いただけます。
+詳しくは、海事普及会の模擬店までお越しいただくか「プラネタリウム」と書かれた腕章をつけている海事普及会部員までお声がけください。
+【受付方法】
+各回上映開始時刻の1時間前より「先着順」にて受け付けます。
+なお、定員を満たし次第、締め切らせていただきます。
+上映開始10分前には受付場所にお集まりください。</v>
+      </c>
+      <c r="G18" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="H18" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="I18">
+        <v>0.4375</v>
+      </c>
+      <c r="J18">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="L18" t="str">
+        <v>プラネタリウム.png</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>18</v>
+      </c>
+      <c r="B19" t="b">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>46158</v>
+      </c>
+      <c r="D19" t="str">
+        <v>プラネタリウム 【子供向けプログラム※子供優先】</v>
+      </c>
+      <c r="E19" t="str">
+        <v>海事普及会</v>
+      </c>
+      <c r="F19" t="str" xml:space="preserve">
+        <v xml:space="preserve">【詳細はこちら→】https://www.kaioufes.com/event/planetarium
+海王祭では毎年、海事普及会によるプラネタリウムの上映を行っています。
+国産現役最古のプラネタリウムが映し出す星空を東京海洋大学ならではの見方でぜひご覧ください。
+※当日、上映時間外でもプラネタリウムをご見学いただけます。
+詳しくは、海事普及会の模擬店までお越しいただくか「プラネタリウム」と書かれた腕章をつけている海事普及会部員までお声がけください。
+【受付方法】
+各回上映開始時刻の1時間前より「先着順」にて受け付けます。
+なお、定員を満たし次第、締め切らせていただきます。
+上映開始10分前には受付場所にお集まりください。</v>
+      </c>
+      <c r="G19" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="H19" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="I19">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="J19">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="L19" t="str">
+        <v>プラネタリウム.png</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>19</v>
+      </c>
+      <c r="B20" t="b">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>46159</v>
+      </c>
+      <c r="D20" t="str">
+        <v>プラネタリウム 【子供向けプログラム※子供優先】</v>
+      </c>
+      <c r="E20" t="str">
+        <v>海事普及会</v>
+      </c>
+      <c r="F20" t="str" xml:space="preserve">
+        <v xml:space="preserve">【詳細はこちら→】https://www.kaioufes.com/event/planetarium
+海王祭では毎年、海事普及会によるプラネタリウムの上映を行っています。
+国産現役最古のプラネタリウムが映し出す星空を東京海洋大学ならではの見方でぜひご覧ください。
+※当日、上映時間外でもプラネタリウムをご見学いただけます。
+詳しくは、海事普及会の模擬店までお越しいただくか「プラネタリウム」と書かれた腕章をつけている海事普及会部員までお声がけください。
+【受付方法】
+各回上映開始時刻の1時間前より「先着順」にて受け付けます。
+なお、定員を満たし次第、締め切らせていただきます。
+上映開始10分前には受付場所にお集まりください。</v>
+      </c>
+      <c r="G20" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="H20" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="I20">
+        <v>0.4375</v>
+      </c>
+      <c r="J20">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="L20" t="str">
+        <v>プラネタリウム.png</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>20</v>
+      </c>
+      <c r="B21" t="b">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>46159</v>
+      </c>
+      <c r="D21" t="str">
+        <v>プラネタリウム 【子供向けプログラム※子供優先】</v>
+      </c>
+      <c r="E21" t="str">
+        <v>海事普及会</v>
+      </c>
+      <c r="F21" t="str" xml:space="preserve">
+        <v xml:space="preserve">【詳細はこちら→】https://www.kaioufes.com/event/planetarium
+海王祭では毎年、海事普及会によるプラネタリウムの上映を行っています。
+国産現役最古のプラネタリウムが映し出す星空を東京海洋大学ならではの見方でぜひご覧ください。
+※当日、上映時間外でもプラネタリウムをご見学いただけます。
+詳しくは、海事普及会の模擬店までお越しいただくか「プラネタリウム」と書かれた腕章をつけている海事普及会部員までお声がけください。
+【受付方法】
+各回上映開始時刻の1時間前より「先着順」にて受け付けます。
+なお、定員を満たし次第、締め切らせていただきます。
+上映開始10分前には受付場所にお集まりください。</v>
+      </c>
+      <c r="G21" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="H21" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="I21">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="J21">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="L21" t="str">
+        <v>プラネタリウム.png</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>21</v>
+      </c>
+      <c r="B22" t="b">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>46158</v>
+      </c>
+      <c r="D22" t="str">
+        <v>プラネタリウム 【通常版】</v>
+      </c>
+      <c r="E22" t="str">
+        <v>海事普及会</v>
+      </c>
+      <c r="F22" t="str" xml:space="preserve">
+        <v xml:space="preserve">【詳細はこちら→】https://www.kaioufes.com/event/planetarium
+海王祭では毎年、海事普及会によるプラネタリウムの上映を行っています。
+国産現役最古のプラネタリウムが映し出す星空を東京海洋大学ならではの見方でぜひご覧ください。
+※当日、上映時間外でもプラネタリウムをご見学いただけます。
+詳しくは、海事普及会の模擬店までお越しいただくか「プラネタリウム」と書かれた腕章をつけている海事普及会部員までお声がけください。
+【受付方法】
+各回上映開始時刻の1時間前より「先着順」にて受け付けます。
+なお、定員を満たし次第、締め切らせていただきます。
+上映開始10分前には受付場所にお集まりください。</v>
+      </c>
+      <c r="G22" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="H22" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="I22">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="J22">
+        <v>0.5</v>
+      </c>
+      <c r="L22" t="str">
+        <v>プラネタリウム.png</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>22</v>
+      </c>
+      <c r="B23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>46158</v>
+      </c>
+      <c r="D23" t="str">
+        <v>プラネタリウム 【通常版】</v>
+      </c>
+      <c r="E23" t="str">
+        <v>海事普及会</v>
+      </c>
+      <c r="F23" t="str" xml:space="preserve">
+        <v xml:space="preserve">【詳細はこちら→】https://www.kaioufes.com/event/planetarium
+海王祭では毎年、海事普及会によるプラネタリウムの上映を行っています。
+国産現役最古のプラネタリウムが映し出す星空を東京海洋大学ならではの見方でぜひご覧ください。
+※当日、上映時間外でもプラネタリウムをご見学いただけます。
+詳しくは、海事普及会の模擬店までお越しいただくか「プラネタリウム」と書かれた腕章をつけている海事普及会部員までお声がけください。
+【受付方法】
+各回上映開始時刻の1時間前より「先着順」にて受け付けます。
+なお、定員を満たし次第、締め切らせていただきます。
+上映開始10分前には受付場所にお集まりください。</v>
+      </c>
+      <c r="G23" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="H23" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="I23">
+        <v>0.625</v>
+      </c>
+      <c r="J23">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="L23" t="str">
+        <v>プラネタリウム.png</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>23</v>
+      </c>
+      <c r="B24" t="b">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>46159</v>
+      </c>
+      <c r="D24" t="str">
+        <v>プラネタリウム 【通常版】</v>
+      </c>
+      <c r="E24" t="str">
+        <v>海事普及会</v>
+      </c>
+      <c r="F24" t="str" xml:space="preserve">
+        <v xml:space="preserve">【詳細はこちら→】https://www.kaioufes.com/event/planetarium
+海王祭では毎年、海事普及会によるプラネタリウムの上映を行っています。
+国産現役最古のプラネタリウムが映し出す星空を東京海洋大学ならではの見方でぜひご覧ください。
+※当日、上映時間外でもプラネタリウムをご見学いただけます。
+詳しくは、海事普及会の模擬店までお越しいただくか「プラネタリウム」と書かれた腕章をつけている海事普及会部員までお声がけください。
+【受付方法】
+各回上映開始時刻の1時間前より「先着順」にて受け付けます。
+なお、定員を満たし次第、締め切らせていただきます。
+上映開始10分前には受付場所にお集まりください。</v>
+      </c>
+      <c r="G24" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="H24" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="I24">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="J24">
+        <v>0.5</v>
+      </c>
+      <c r="L24" t="str">
+        <v>プラネタリウム.png</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>24</v>
+      </c>
+      <c r="B25" t="b">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>46159</v>
+      </c>
+      <c r="D25" t="str">
+        <v>プラネタリウム 【通常版】</v>
+      </c>
+      <c r="E25" t="str">
+        <v>海事普及会</v>
+      </c>
+      <c r="F25" t="str" xml:space="preserve">
+        <v xml:space="preserve">【詳細はこちら→】https://www.kaioufes.com/event/planetarium
+海王祭では毎年、海事普及会によるプラネタリウムの上映を行っています。
+国産現役最古のプラネタリウムが映し出す星空を東京海洋大学ならではの見方でぜひご覧ください。
+※当日、上映時間外でもプラネタリウムをご見学いただけます。
+詳しくは、海事普及会の模擬店までお越しいただくか「プラネタリウム」と書かれた腕章をつけている海事普及会部員までお声がけください。
+【受付方法】
+各回上映開始時刻の1時間前より「先着順」にて受け付けます。
+なお、定員を満たし次第、締め切らせていただきます。
+上映開始10分前には受付場所にお集まりください。</v>
+      </c>
+      <c r="G25" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="H25" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="I25">
+        <v>0.625</v>
+      </c>
+      <c r="J25">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="L25" t="str">
+        <v>プラネタリウム.png</v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>25</v>
+      </c>
+      <c r="B26" t="b">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>46158</v>
+      </c>
+      <c r="D26" t="str">
+        <v>プラネタリウム 【特別解説会】</v>
+      </c>
+      <c r="E26" t="str">
+        <v>海事普及会</v>
+      </c>
+      <c r="F26" t="str" xml:space="preserve">
+        <v xml:space="preserve">【詳細はこちら→】https://www.kaioufes.com/event/planetarium
+海王祭では毎年、海事普及会によるプラネタリウムの上映を行っています。
+国産現役最古のプラネタリウムが映し出す星空を東京海洋大学ならではの見方でぜひご覧ください。
+※当日、上映時間外でもプラネタリウムをご見学いただけます。
+詳しくは、海事普及会の模擬店までお越しいただくか「プラネタリウム」と書かれた腕章をつけている海事普及会部員までお声がけください。
+【受付方法】
+各回上映開始時刻の1時間前より「先着順」にて受け付けます。
+なお、定員を満たし次第、締め切らせていただきます。
+上映開始10分前には受付場所にお集まりください。</v>
+      </c>
+      <c r="G26" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="H26" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="I26">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J26">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="L26" t="str">
+        <v>プラネタリウム.png</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>26</v>
+      </c>
+      <c r="B27" t="b">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>46159</v>
+      </c>
+      <c r="D27" t="str">
+        <v>プラネタリウム 【特別解説会】</v>
+      </c>
+      <c r="E27" t="str">
+        <v>海事普及会</v>
+      </c>
+      <c r="F27" t="str" xml:space="preserve">
+        <v xml:space="preserve">【詳細はこちら→】https://www.kaioufes.com/event/planetarium
+海王祭では毎年、海事普及会によるプラネタリウムの上映を行っています。
+国産現役最古のプラネタリウムが映し出す星空を東京海洋大学ならではの見方でぜひご覧ください。
+※当日、上映時間外でもプラネタリウムをご見学いただけます。
+詳しくは、海事普及会の模擬店までお越しいただくか「プラネタリウム」と書かれた腕章をつけている海事普及会部員までお声がけください。
+【受付方法】
+各回上映開始時刻の1時間前より「先着順」にて受け付けます。
+なお、定員を満たし次第、締め切らせていただきます。
+上映開始10分前には受付場所にお集まりください。</v>
+      </c>
+      <c r="G27" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="H27" t="str">
+        <v>プラネタリウム</v>
+      </c>
+      <c r="I27">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J27">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="L27" t="str">
+        <v>プラネタリウム.png</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>27</v>
+      </c>
+      <c r="B28" t="b">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>46158</v>
+      </c>
+      <c r="D28" t="str">
+        <v>志馬なにがし先生トークショー</v>
+      </c>
+      <c r="I28">
+        <v>0.625</v>
+      </c>
+      <c r="J28">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="L28" t="str">
+        <v>志馬なにがし先生.png</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>28</v>
+      </c>
+      <c r="B29" t="b">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>46158</v>
+      </c>
+      <c r="D29" t="str">
+        <v>志馬なにがし先生サイン会</v>
+      </c>
+      <c r="F29" t="str">
+        <v>本イベントの参加には海王祭実行委員会模擬店にて書籍の購入が必要です。</v>
+      </c>
+      <c r="I29">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="J29">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L29" t="str">
+        <v>志馬なにがし先生.png</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J1000"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L1000"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/sources/海王祭アプリ2026マスターデータ.xlsx
+++ b/scripts/sources/海王祭アプリ2026マスターデータ.xlsx
@@ -1995,11 +1995,11 @@
       <c r="F18" t="str">
         <v>いつもは大会等があり、参加を見送ることが多かった我々水泳部ですが、今回の海王祭では満を持して出店させていただきます。水泳部が一丸となって作った油そば食べてみたくなりませんか！？</v>
       </c>
-      <c r="G18">
-        <v>35.6671822</v>
-      </c>
-      <c r="H18">
-        <v>139.7914767</v>
+      <c r="G18" t="str">
+        <v>35.6671809</v>
+      </c>
+      <c r="H18" t="str">
+        <v>139.7914797</v>
       </c>
       <c r="I18" t="str">
         <v/>

--- a/scripts/sources/海王祭アプリ2026マスターデータ.xlsx
+++ b/scripts/sources/海王祭アプリ2026マスターデータ.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="549">
   <si>
     <t>id</t>
   </si>
@@ -229,7 +229,7 @@
     <t>02</t>
   </si>
   <si>
-    <t>先端科学技術研究センター(非公開)</t>
+    <t>守衛所</t>
   </si>
   <si>
     <t>1号館</t>
@@ -428,6 +428,9 @@
     <t>139.7910838</t>
   </si>
   <si>
+    <t>看護師常駐場所</t>
+  </si>
+  <si>
     <t>organization</t>
   </si>
   <si>
@@ -773,7 +776,7 @@
     <t>mogi_23</t>
   </si>
   <si>
-    <t>魚介ラーメン</t>
+    <t>あら汁など</t>
   </si>
   <si>
     <t>あさり会</t>
@@ -1750,12 +1753,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color theme="1"/>
@@ -1777,12 +1784,20 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -3387,14 +3402,14 @@
       <c r="B10" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="1">
-        <v>35.6683382</v>
-      </c>
-      <c r="E10" s="1">
-        <v>139.7905755</v>
+      <c r="D10" s="2">
+        <v>35.6685506</v>
+      </c>
+      <c r="E10" s="2">
+        <v>139.7904179</v>
       </c>
       <c r="G10" s="1" t="b">
         <v>1</v>
@@ -3495,6 +3510,12 @@
       </c>
       <c r="E15" s="1">
         <v>139.7917852</v>
+      </c>
+      <c r="F15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4650,7 +4671,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -4682,6 +4703,7 @@
       <c r="B2" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="C2" s="5"/>
       <c r="D2" s="1" t="s">
         <v>57</v>
       </c>
@@ -4705,6 +4727,7 @@
       <c r="B3" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="C3" s="5"/>
       <c r="D3" s="1" t="s">
         <v>100</v>
       </c>
@@ -4728,6 +4751,7 @@
       <c r="B4" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>103</v>
       </c>
@@ -4751,6 +4775,7 @@
       <c r="B5" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="C5" s="5"/>
       <c r="D5" s="1" t="s">
         <v>61</v>
       </c>
@@ -4774,6 +4799,7 @@
       <c r="B6" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="C6" s="5"/>
       <c r="D6" s="1" t="s">
         <v>107</v>
       </c>
@@ -4797,6 +4823,7 @@
       <c r="B7" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="C7" s="5"/>
       <c r="D7" s="1" t="s">
         <v>112</v>
       </c>
@@ -4817,6 +4844,7 @@
       <c r="B8" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="C8" s="5"/>
       <c r="D8" s="1" t="s">
         <v>112</v>
       </c>
@@ -4837,6 +4865,7 @@
       <c r="B9" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="C9" s="5"/>
       <c r="D9" s="1" t="s">
         <v>112</v>
       </c>
@@ -4857,6 +4886,7 @@
       <c r="B10" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="C10" s="5"/>
       <c r="D10" s="1" t="s">
         <v>112</v>
       </c>
@@ -4877,6 +4907,7 @@
       <c r="B11" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="C11" s="5"/>
       <c r="D11" s="1" t="s">
         <v>124</v>
       </c>
@@ -4897,6 +4928,7 @@
       <c r="B12" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="C12" s="5"/>
       <c r="D12" s="1" t="s">
         <v>128</v>
       </c>
@@ -4917,6 +4949,7 @@
       <c r="B13" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="C13" s="5"/>
       <c r="D13" s="1" t="s">
         <v>132</v>
       </c>
@@ -4930,986 +4963,2987 @@
         <v>98</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="5"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="5"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="5"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="5"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="C21" s="5"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="C24" s="5"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="C27" s="5"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="C29" s="5"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="C30" s="5"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="C31" s="5"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="C32" s="5"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="C33" s="5"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="C34" s="5"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="C35" s="5"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="C36" s="5"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="C37" s="5"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="C38" s="5"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="C39" s="5"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="C40" s="5"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="C41" s="5"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="C42" s="5"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="C43" s="5"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="C44" s="5"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="C45" s="5"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="C46" s="5"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="C47" s="5"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="C48" s="5"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="C49" s="5"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="C50" s="5"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="C51" s="5"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="C52" s="5"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="C53" s="5"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="C54" s="5"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="C55" s="5"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="C56" s="5"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="C57" s="5"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="C58" s="5"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="C59" s="5"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="C60" s="5"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="C61" s="5"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="C62" s="5"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="C63" s="5"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="C64" s="5"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="C65" s="5"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="C66" s="5"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="C67" s="5"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="C68" s="5"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="C69" s="5"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="C70" s="5"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="C71" s="5"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="C72" s="5"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="C73" s="5"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="C74" s="5"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="C75" s="5"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="C76" s="5"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="C77" s="5"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="C78" s="5"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="C79" s="5"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="C80" s="5"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="C81" s="5"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="C82" s="5"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="C83" s="5"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="C84" s="5"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="C85" s="5"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="C86" s="5"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="C87" s="5"/>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="C88" s="5"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="C89" s="5"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="C90" s="5"/>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="C91" s="5"/>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="C92" s="5"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="C93" s="5"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="C94" s="5"/>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="C95" s="5"/>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="C96" s="5"/>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="C97" s="5"/>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="C98" s="5"/>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="C99" s="5"/>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="C100" s="5"/>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="C101" s="5"/>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="C102" s="5"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="C103" s="5"/>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="C104" s="5"/>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="C105" s="5"/>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="C106" s="5"/>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="C107" s="5"/>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="C108" s="5"/>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="C109" s="5"/>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="C110" s="5"/>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="C111" s="5"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="C112" s="5"/>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="C113" s="5"/>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="C114" s="5"/>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="C115" s="5"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="C116" s="5"/>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="C117" s="5"/>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="C118" s="5"/>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="C119" s="5"/>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="C120" s="5"/>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="C121" s="5"/>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="C122" s="5"/>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="C123" s="5"/>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="C124" s="5"/>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="C125" s="5"/>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="C126" s="5"/>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="C127" s="5"/>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="C128" s="5"/>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="C129" s="5"/>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="C130" s="5"/>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="C131" s="5"/>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="C132" s="5"/>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="C133" s="5"/>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="C134" s="5"/>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="C135" s="5"/>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="C136" s="5"/>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="C137" s="5"/>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="C138" s="5"/>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="C139" s="5"/>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="C140" s="5"/>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="C141" s="5"/>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="C142" s="5"/>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="C143" s="5"/>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="C144" s="5"/>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="C145" s="5"/>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="C146" s="5"/>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="C147" s="5"/>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="C148" s="5"/>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="C149" s="5"/>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="C150" s="5"/>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="C151" s="5"/>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="C152" s="5"/>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="C153" s="5"/>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="C154" s="5"/>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="C155" s="5"/>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="C156" s="5"/>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="C157" s="5"/>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="C158" s="5"/>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="C159" s="5"/>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="C160" s="5"/>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="C161" s="5"/>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="C162" s="5"/>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="C163" s="5"/>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="C164" s="5"/>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="C165" s="5"/>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="C166" s="5"/>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="C167" s="5"/>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="C168" s="5"/>
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
+      <c r="C169" s="5"/>
+    </row>
+    <row r="170" ht="15.75" customHeight="1">
+      <c r="C170" s="5"/>
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
+      <c r="C171" s="5"/>
+    </row>
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="C172" s="5"/>
+    </row>
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="C173" s="5"/>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="C174" s="5"/>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="C175" s="5"/>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="C176" s="5"/>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="C177" s="5"/>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="C178" s="5"/>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="C179" s="5"/>
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
+      <c r="C180" s="5"/>
+    </row>
+    <row r="181" ht="15.75" customHeight="1">
+      <c r="C181" s="5"/>
+    </row>
+    <row r="182" ht="15.75" customHeight="1">
+      <c r="C182" s="5"/>
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
+      <c r="C183" s="5"/>
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="C184" s="5"/>
+    </row>
+    <row r="185" ht="15.75" customHeight="1">
+      <c r="C185" s="5"/>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="C186" s="5"/>
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="C187" s="5"/>
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
+      <c r="C188" s="5"/>
+    </row>
+    <row r="189" ht="15.75" customHeight="1">
+      <c r="C189" s="5"/>
+    </row>
+    <row r="190" ht="15.75" customHeight="1">
+      <c r="C190" s="5"/>
+    </row>
+    <row r="191" ht="15.75" customHeight="1">
+      <c r="C191" s="5"/>
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
+      <c r="C192" s="5"/>
+    </row>
+    <row r="193" ht="15.75" customHeight="1">
+      <c r="C193" s="5"/>
+    </row>
+    <row r="194" ht="15.75" customHeight="1">
+      <c r="C194" s="5"/>
+    </row>
+    <row r="195" ht="15.75" customHeight="1">
+      <c r="C195" s="5"/>
+    </row>
+    <row r="196" ht="15.75" customHeight="1">
+      <c r="C196" s="5"/>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
+      <c r="C197" s="5"/>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
+      <c r="C198" s="5"/>
+    </row>
+    <row r="199" ht="15.75" customHeight="1">
+      <c r="C199" s="5"/>
+    </row>
+    <row r="200" ht="15.75" customHeight="1">
+      <c r="C200" s="5"/>
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
+      <c r="C201" s="5"/>
+    </row>
+    <row r="202" ht="15.75" customHeight="1">
+      <c r="C202" s="5"/>
+    </row>
+    <row r="203" ht="15.75" customHeight="1">
+      <c r="C203" s="5"/>
+    </row>
+    <row r="204" ht="15.75" customHeight="1">
+      <c r="C204" s="5"/>
+    </row>
+    <row r="205" ht="15.75" customHeight="1">
+      <c r="C205" s="5"/>
+    </row>
+    <row r="206" ht="15.75" customHeight="1">
+      <c r="C206" s="5"/>
+    </row>
+    <row r="207" ht="15.75" customHeight="1">
+      <c r="C207" s="5"/>
+    </row>
+    <row r="208" ht="15.75" customHeight="1">
+      <c r="C208" s="5"/>
+    </row>
+    <row r="209" ht="15.75" customHeight="1">
+      <c r="C209" s="5"/>
+    </row>
+    <row r="210" ht="15.75" customHeight="1">
+      <c r="C210" s="5"/>
+    </row>
+    <row r="211" ht="15.75" customHeight="1">
+      <c r="C211" s="5"/>
+    </row>
+    <row r="212" ht="15.75" customHeight="1">
+      <c r="C212" s="5"/>
+    </row>
+    <row r="213" ht="15.75" customHeight="1">
+      <c r="C213" s="5"/>
+    </row>
+    <row r="214" ht="15.75" customHeight="1">
+      <c r="C214" s="5"/>
+    </row>
+    <row r="215" ht="15.75" customHeight="1">
+      <c r="C215" s="5"/>
+    </row>
+    <row r="216" ht="15.75" customHeight="1">
+      <c r="C216" s="5"/>
+    </row>
+    <row r="217" ht="15.75" customHeight="1">
+      <c r="C217" s="5"/>
+    </row>
+    <row r="218" ht="15.75" customHeight="1">
+      <c r="C218" s="5"/>
+    </row>
+    <row r="219" ht="15.75" customHeight="1">
+      <c r="C219" s="5"/>
+    </row>
+    <row r="220" ht="15.75" customHeight="1">
+      <c r="C220" s="5"/>
+    </row>
+    <row r="221" ht="15.75" customHeight="1">
+      <c r="C221" s="5"/>
+    </row>
+    <row r="222" ht="15.75" customHeight="1">
+      <c r="C222" s="5"/>
+    </row>
+    <row r="223" ht="15.75" customHeight="1">
+      <c r="C223" s="5"/>
+    </row>
+    <row r="224" ht="15.75" customHeight="1">
+      <c r="C224" s="5"/>
+    </row>
+    <row r="225" ht="15.75" customHeight="1">
+      <c r="C225" s="5"/>
+    </row>
+    <row r="226" ht="15.75" customHeight="1">
+      <c r="C226" s="5"/>
+    </row>
+    <row r="227" ht="15.75" customHeight="1">
+      <c r="C227" s="5"/>
+    </row>
+    <row r="228" ht="15.75" customHeight="1">
+      <c r="C228" s="5"/>
+    </row>
+    <row r="229" ht="15.75" customHeight="1">
+      <c r="C229" s="5"/>
+    </row>
+    <row r="230" ht="15.75" customHeight="1">
+      <c r="C230" s="5"/>
+    </row>
+    <row r="231" ht="15.75" customHeight="1">
+      <c r="C231" s="5"/>
+    </row>
+    <row r="232" ht="15.75" customHeight="1">
+      <c r="C232" s="5"/>
+    </row>
+    <row r="233" ht="15.75" customHeight="1">
+      <c r="C233" s="5"/>
+    </row>
+    <row r="234" ht="15.75" customHeight="1">
+      <c r="C234" s="5"/>
+    </row>
+    <row r="235" ht="15.75" customHeight="1">
+      <c r="C235" s="5"/>
+    </row>
+    <row r="236" ht="15.75" customHeight="1">
+      <c r="C236" s="5"/>
+    </row>
+    <row r="237" ht="15.75" customHeight="1">
+      <c r="C237" s="5"/>
+    </row>
+    <row r="238" ht="15.75" customHeight="1">
+      <c r="C238" s="5"/>
+    </row>
+    <row r="239" ht="15.75" customHeight="1">
+      <c r="C239" s="5"/>
+    </row>
+    <row r="240" ht="15.75" customHeight="1">
+      <c r="C240" s="5"/>
+    </row>
+    <row r="241" ht="15.75" customHeight="1">
+      <c r="C241" s="5"/>
+    </row>
+    <row r="242" ht="15.75" customHeight="1">
+      <c r="C242" s="5"/>
+    </row>
+    <row r="243" ht="15.75" customHeight="1">
+      <c r="C243" s="5"/>
+    </row>
+    <row r="244" ht="15.75" customHeight="1">
+      <c r="C244" s="5"/>
+    </row>
+    <row r="245" ht="15.75" customHeight="1">
+      <c r="C245" s="5"/>
+    </row>
+    <row r="246" ht="15.75" customHeight="1">
+      <c r="C246" s="5"/>
+    </row>
+    <row r="247" ht="15.75" customHeight="1">
+      <c r="C247" s="5"/>
+    </row>
+    <row r="248" ht="15.75" customHeight="1">
+      <c r="C248" s="5"/>
+    </row>
+    <row r="249" ht="15.75" customHeight="1">
+      <c r="C249" s="5"/>
+    </row>
+    <row r="250" ht="15.75" customHeight="1">
+      <c r="C250" s="5"/>
+    </row>
+    <row r="251" ht="15.75" customHeight="1">
+      <c r="C251" s="5"/>
+    </row>
+    <row r="252" ht="15.75" customHeight="1">
+      <c r="C252" s="5"/>
+    </row>
+    <row r="253" ht="15.75" customHeight="1">
+      <c r="C253" s="5"/>
+    </row>
+    <row r="254" ht="15.75" customHeight="1">
+      <c r="C254" s="5"/>
+    </row>
+    <row r="255" ht="15.75" customHeight="1">
+      <c r="C255" s="5"/>
+    </row>
+    <row r="256" ht="15.75" customHeight="1">
+      <c r="C256" s="5"/>
+    </row>
+    <row r="257" ht="15.75" customHeight="1">
+      <c r="C257" s="5"/>
+    </row>
+    <row r="258" ht="15.75" customHeight="1">
+      <c r="C258" s="5"/>
+    </row>
+    <row r="259" ht="15.75" customHeight="1">
+      <c r="C259" s="5"/>
+    </row>
+    <row r="260" ht="15.75" customHeight="1">
+      <c r="C260" s="5"/>
+    </row>
+    <row r="261" ht="15.75" customHeight="1">
+      <c r="C261" s="5"/>
+    </row>
+    <row r="262" ht="15.75" customHeight="1">
+      <c r="C262" s="5"/>
+    </row>
+    <row r="263" ht="15.75" customHeight="1">
+      <c r="C263" s="5"/>
+    </row>
+    <row r="264" ht="15.75" customHeight="1">
+      <c r="C264" s="5"/>
+    </row>
+    <row r="265" ht="15.75" customHeight="1">
+      <c r="C265" s="5"/>
+    </row>
+    <row r="266" ht="15.75" customHeight="1">
+      <c r="C266" s="5"/>
+    </row>
+    <row r="267" ht="15.75" customHeight="1">
+      <c r="C267" s="5"/>
+    </row>
+    <row r="268" ht="15.75" customHeight="1">
+      <c r="C268" s="5"/>
+    </row>
+    <row r="269" ht="15.75" customHeight="1">
+      <c r="C269" s="5"/>
+    </row>
+    <row r="270" ht="15.75" customHeight="1">
+      <c r="C270" s="5"/>
+    </row>
+    <row r="271" ht="15.75" customHeight="1">
+      <c r="C271" s="5"/>
+    </row>
+    <row r="272" ht="15.75" customHeight="1">
+      <c r="C272" s="5"/>
+    </row>
+    <row r="273" ht="15.75" customHeight="1">
+      <c r="C273" s="5"/>
+    </row>
+    <row r="274" ht="15.75" customHeight="1">
+      <c r="C274" s="5"/>
+    </row>
+    <row r="275" ht="15.75" customHeight="1">
+      <c r="C275" s="5"/>
+    </row>
+    <row r="276" ht="15.75" customHeight="1">
+      <c r="C276" s="5"/>
+    </row>
+    <row r="277" ht="15.75" customHeight="1">
+      <c r="C277" s="5"/>
+    </row>
+    <row r="278" ht="15.75" customHeight="1">
+      <c r="C278" s="5"/>
+    </row>
+    <row r="279" ht="15.75" customHeight="1">
+      <c r="C279" s="5"/>
+    </row>
+    <row r="280" ht="15.75" customHeight="1">
+      <c r="C280" s="5"/>
+    </row>
+    <row r="281" ht="15.75" customHeight="1">
+      <c r="C281" s="5"/>
+    </row>
+    <row r="282" ht="15.75" customHeight="1">
+      <c r="C282" s="5"/>
+    </row>
+    <row r="283" ht="15.75" customHeight="1">
+      <c r="C283" s="5"/>
+    </row>
+    <row r="284" ht="15.75" customHeight="1">
+      <c r="C284" s="5"/>
+    </row>
+    <row r="285" ht="15.75" customHeight="1">
+      <c r="C285" s="5"/>
+    </row>
+    <row r="286" ht="15.75" customHeight="1">
+      <c r="C286" s="5"/>
+    </row>
+    <row r="287" ht="15.75" customHeight="1">
+      <c r="C287" s="5"/>
+    </row>
+    <row r="288" ht="15.75" customHeight="1">
+      <c r="C288" s="5"/>
+    </row>
+    <row r="289" ht="15.75" customHeight="1">
+      <c r="C289" s="5"/>
+    </row>
+    <row r="290" ht="15.75" customHeight="1">
+      <c r="C290" s="5"/>
+    </row>
+    <row r="291" ht="15.75" customHeight="1">
+      <c r="C291" s="5"/>
+    </row>
+    <row r="292" ht="15.75" customHeight="1">
+      <c r="C292" s="5"/>
+    </row>
+    <row r="293" ht="15.75" customHeight="1">
+      <c r="C293" s="5"/>
+    </row>
+    <row r="294" ht="15.75" customHeight="1">
+      <c r="C294" s="5"/>
+    </row>
+    <row r="295" ht="15.75" customHeight="1">
+      <c r="C295" s="5"/>
+    </row>
+    <row r="296" ht="15.75" customHeight="1">
+      <c r="C296" s="5"/>
+    </row>
+    <row r="297" ht="15.75" customHeight="1">
+      <c r="C297" s="5"/>
+    </row>
+    <row r="298" ht="15.75" customHeight="1">
+      <c r="C298" s="5"/>
+    </row>
+    <row r="299" ht="15.75" customHeight="1">
+      <c r="C299" s="5"/>
+    </row>
+    <row r="300" ht="15.75" customHeight="1">
+      <c r="C300" s="5"/>
+    </row>
+    <row r="301" ht="15.75" customHeight="1">
+      <c r="C301" s="5"/>
+    </row>
+    <row r="302" ht="15.75" customHeight="1">
+      <c r="C302" s="5"/>
+    </row>
+    <row r="303" ht="15.75" customHeight="1">
+      <c r="C303" s="5"/>
+    </row>
+    <row r="304" ht="15.75" customHeight="1">
+      <c r="C304" s="5"/>
+    </row>
+    <row r="305" ht="15.75" customHeight="1">
+      <c r="C305" s="5"/>
+    </row>
+    <row r="306" ht="15.75" customHeight="1">
+      <c r="C306" s="5"/>
+    </row>
+    <row r="307" ht="15.75" customHeight="1">
+      <c r="C307" s="5"/>
+    </row>
+    <row r="308" ht="15.75" customHeight="1">
+      <c r="C308" s="5"/>
+    </row>
+    <row r="309" ht="15.75" customHeight="1">
+      <c r="C309" s="5"/>
+    </row>
+    <row r="310" ht="15.75" customHeight="1">
+      <c r="C310" s="5"/>
+    </row>
+    <row r="311" ht="15.75" customHeight="1">
+      <c r="C311" s="5"/>
+    </row>
+    <row r="312" ht="15.75" customHeight="1">
+      <c r="C312" s="5"/>
+    </row>
+    <row r="313" ht="15.75" customHeight="1">
+      <c r="C313" s="5"/>
+    </row>
+    <row r="314" ht="15.75" customHeight="1">
+      <c r="C314" s="5"/>
+    </row>
+    <row r="315" ht="15.75" customHeight="1">
+      <c r="C315" s="5"/>
+    </row>
+    <row r="316" ht="15.75" customHeight="1">
+      <c r="C316" s="5"/>
+    </row>
+    <row r="317" ht="15.75" customHeight="1">
+      <c r="C317" s="5"/>
+    </row>
+    <row r="318" ht="15.75" customHeight="1">
+      <c r="C318" s="5"/>
+    </row>
+    <row r="319" ht="15.75" customHeight="1">
+      <c r="C319" s="5"/>
+    </row>
+    <row r="320" ht="15.75" customHeight="1">
+      <c r="C320" s="5"/>
+    </row>
+    <row r="321" ht="15.75" customHeight="1">
+      <c r="C321" s="5"/>
+    </row>
+    <row r="322" ht="15.75" customHeight="1">
+      <c r="C322" s="5"/>
+    </row>
+    <row r="323" ht="15.75" customHeight="1">
+      <c r="C323" s="5"/>
+    </row>
+    <row r="324" ht="15.75" customHeight="1">
+      <c r="C324" s="5"/>
+    </row>
+    <row r="325" ht="15.75" customHeight="1">
+      <c r="C325" s="5"/>
+    </row>
+    <row r="326" ht="15.75" customHeight="1">
+      <c r="C326" s="5"/>
+    </row>
+    <row r="327" ht="15.75" customHeight="1">
+      <c r="C327" s="5"/>
+    </row>
+    <row r="328" ht="15.75" customHeight="1">
+      <c r="C328" s="5"/>
+    </row>
+    <row r="329" ht="15.75" customHeight="1">
+      <c r="C329" s="5"/>
+    </row>
+    <row r="330" ht="15.75" customHeight="1">
+      <c r="C330" s="5"/>
+    </row>
+    <row r="331" ht="15.75" customHeight="1">
+      <c r="C331" s="5"/>
+    </row>
+    <row r="332" ht="15.75" customHeight="1">
+      <c r="C332" s="5"/>
+    </row>
+    <row r="333" ht="15.75" customHeight="1">
+      <c r="C333" s="5"/>
+    </row>
+    <row r="334" ht="15.75" customHeight="1">
+      <c r="C334" s="5"/>
+    </row>
+    <row r="335" ht="15.75" customHeight="1">
+      <c r="C335" s="5"/>
+    </row>
+    <row r="336" ht="15.75" customHeight="1">
+      <c r="C336" s="5"/>
+    </row>
+    <row r="337" ht="15.75" customHeight="1">
+      <c r="C337" s="5"/>
+    </row>
+    <row r="338" ht="15.75" customHeight="1">
+      <c r="C338" s="5"/>
+    </row>
+    <row r="339" ht="15.75" customHeight="1">
+      <c r="C339" s="5"/>
+    </row>
+    <row r="340" ht="15.75" customHeight="1">
+      <c r="C340" s="5"/>
+    </row>
+    <row r="341" ht="15.75" customHeight="1">
+      <c r="C341" s="5"/>
+    </row>
+    <row r="342" ht="15.75" customHeight="1">
+      <c r="C342" s="5"/>
+    </row>
+    <row r="343" ht="15.75" customHeight="1">
+      <c r="C343" s="5"/>
+    </row>
+    <row r="344" ht="15.75" customHeight="1">
+      <c r="C344" s="5"/>
+    </row>
+    <row r="345" ht="15.75" customHeight="1">
+      <c r="C345" s="5"/>
+    </row>
+    <row r="346" ht="15.75" customHeight="1">
+      <c r="C346" s="5"/>
+    </row>
+    <row r="347" ht="15.75" customHeight="1">
+      <c r="C347" s="5"/>
+    </row>
+    <row r="348" ht="15.75" customHeight="1">
+      <c r="C348" s="5"/>
+    </row>
+    <row r="349" ht="15.75" customHeight="1">
+      <c r="C349" s="5"/>
+    </row>
+    <row r="350" ht="15.75" customHeight="1">
+      <c r="C350" s="5"/>
+    </row>
+    <row r="351" ht="15.75" customHeight="1">
+      <c r="C351" s="5"/>
+    </row>
+    <row r="352" ht="15.75" customHeight="1">
+      <c r="C352" s="5"/>
+    </row>
+    <row r="353" ht="15.75" customHeight="1">
+      <c r="C353" s="5"/>
+    </row>
+    <row r="354" ht="15.75" customHeight="1">
+      <c r="C354" s="5"/>
+    </row>
+    <row r="355" ht="15.75" customHeight="1">
+      <c r="C355" s="5"/>
+    </row>
+    <row r="356" ht="15.75" customHeight="1">
+      <c r="C356" s="5"/>
+    </row>
+    <row r="357" ht="15.75" customHeight="1">
+      <c r="C357" s="5"/>
+    </row>
+    <row r="358" ht="15.75" customHeight="1">
+      <c r="C358" s="5"/>
+    </row>
+    <row r="359" ht="15.75" customHeight="1">
+      <c r="C359" s="5"/>
+    </row>
+    <row r="360" ht="15.75" customHeight="1">
+      <c r="C360" s="5"/>
+    </row>
+    <row r="361" ht="15.75" customHeight="1">
+      <c r="C361" s="5"/>
+    </row>
+    <row r="362" ht="15.75" customHeight="1">
+      <c r="C362" s="5"/>
+    </row>
+    <row r="363" ht="15.75" customHeight="1">
+      <c r="C363" s="5"/>
+    </row>
+    <row r="364" ht="15.75" customHeight="1">
+      <c r="C364" s="5"/>
+    </row>
+    <row r="365" ht="15.75" customHeight="1">
+      <c r="C365" s="5"/>
+    </row>
+    <row r="366" ht="15.75" customHeight="1">
+      <c r="C366" s="5"/>
+    </row>
+    <row r="367" ht="15.75" customHeight="1">
+      <c r="C367" s="5"/>
+    </row>
+    <row r="368" ht="15.75" customHeight="1">
+      <c r="C368" s="5"/>
+    </row>
+    <row r="369" ht="15.75" customHeight="1">
+      <c r="C369" s="5"/>
+    </row>
+    <row r="370" ht="15.75" customHeight="1">
+      <c r="C370" s="5"/>
+    </row>
+    <row r="371" ht="15.75" customHeight="1">
+      <c r="C371" s="5"/>
+    </row>
+    <row r="372" ht="15.75" customHeight="1">
+      <c r="C372" s="5"/>
+    </row>
+    <row r="373" ht="15.75" customHeight="1">
+      <c r="C373" s="5"/>
+    </row>
+    <row r="374" ht="15.75" customHeight="1">
+      <c r="C374" s="5"/>
+    </row>
+    <row r="375" ht="15.75" customHeight="1">
+      <c r="C375" s="5"/>
+    </row>
+    <row r="376" ht="15.75" customHeight="1">
+      <c r="C376" s="5"/>
+    </row>
+    <row r="377" ht="15.75" customHeight="1">
+      <c r="C377" s="5"/>
+    </row>
+    <row r="378" ht="15.75" customHeight="1">
+      <c r="C378" s="5"/>
+    </row>
+    <row r="379" ht="15.75" customHeight="1">
+      <c r="C379" s="5"/>
+    </row>
+    <row r="380" ht="15.75" customHeight="1">
+      <c r="C380" s="5"/>
+    </row>
+    <row r="381" ht="15.75" customHeight="1">
+      <c r="C381" s="5"/>
+    </row>
+    <row r="382" ht="15.75" customHeight="1">
+      <c r="C382" s="5"/>
+    </row>
+    <row r="383" ht="15.75" customHeight="1">
+      <c r="C383" s="5"/>
+    </row>
+    <row r="384" ht="15.75" customHeight="1">
+      <c r="C384" s="5"/>
+    </row>
+    <row r="385" ht="15.75" customHeight="1">
+      <c r="C385" s="5"/>
+    </row>
+    <row r="386" ht="15.75" customHeight="1">
+      <c r="C386" s="5"/>
+    </row>
+    <row r="387" ht="15.75" customHeight="1">
+      <c r="C387" s="5"/>
+    </row>
+    <row r="388" ht="15.75" customHeight="1">
+      <c r="C388" s="5"/>
+    </row>
+    <row r="389" ht="15.75" customHeight="1">
+      <c r="C389" s="5"/>
+    </row>
+    <row r="390" ht="15.75" customHeight="1">
+      <c r="C390" s="5"/>
+    </row>
+    <row r="391" ht="15.75" customHeight="1">
+      <c r="C391" s="5"/>
+    </row>
+    <row r="392" ht="15.75" customHeight="1">
+      <c r="C392" s="5"/>
+    </row>
+    <row r="393" ht="15.75" customHeight="1">
+      <c r="C393" s="5"/>
+    </row>
+    <row r="394" ht="15.75" customHeight="1">
+      <c r="C394" s="5"/>
+    </row>
+    <row r="395" ht="15.75" customHeight="1">
+      <c r="C395" s="5"/>
+    </row>
+    <row r="396" ht="15.75" customHeight="1">
+      <c r="C396" s="5"/>
+    </row>
+    <row r="397" ht="15.75" customHeight="1">
+      <c r="C397" s="5"/>
+    </row>
+    <row r="398" ht="15.75" customHeight="1">
+      <c r="C398" s="5"/>
+    </row>
+    <row r="399" ht="15.75" customHeight="1">
+      <c r="C399" s="5"/>
+    </row>
+    <row r="400" ht="15.75" customHeight="1">
+      <c r="C400" s="5"/>
+    </row>
+    <row r="401" ht="15.75" customHeight="1">
+      <c r="C401" s="5"/>
+    </row>
+    <row r="402" ht="15.75" customHeight="1">
+      <c r="C402" s="5"/>
+    </row>
+    <row r="403" ht="15.75" customHeight="1">
+      <c r="C403" s="5"/>
+    </row>
+    <row r="404" ht="15.75" customHeight="1">
+      <c r="C404" s="5"/>
+    </row>
+    <row r="405" ht="15.75" customHeight="1">
+      <c r="C405" s="5"/>
+    </row>
+    <row r="406" ht="15.75" customHeight="1">
+      <c r="C406" s="5"/>
+    </row>
+    <row r="407" ht="15.75" customHeight="1">
+      <c r="C407" s="5"/>
+    </row>
+    <row r="408" ht="15.75" customHeight="1">
+      <c r="C408" s="5"/>
+    </row>
+    <row r="409" ht="15.75" customHeight="1">
+      <c r="C409" s="5"/>
+    </row>
+    <row r="410" ht="15.75" customHeight="1">
+      <c r="C410" s="5"/>
+    </row>
+    <row r="411" ht="15.75" customHeight="1">
+      <c r="C411" s="5"/>
+    </row>
+    <row r="412" ht="15.75" customHeight="1">
+      <c r="C412" s="5"/>
+    </row>
+    <row r="413" ht="15.75" customHeight="1">
+      <c r="C413" s="5"/>
+    </row>
+    <row r="414" ht="15.75" customHeight="1">
+      <c r="C414" s="5"/>
+    </row>
+    <row r="415" ht="15.75" customHeight="1">
+      <c r="C415" s="5"/>
+    </row>
+    <row r="416" ht="15.75" customHeight="1">
+      <c r="C416" s="5"/>
+    </row>
+    <row r="417" ht="15.75" customHeight="1">
+      <c r="C417" s="5"/>
+    </row>
+    <row r="418" ht="15.75" customHeight="1">
+      <c r="C418" s="5"/>
+    </row>
+    <row r="419" ht="15.75" customHeight="1">
+      <c r="C419" s="5"/>
+    </row>
+    <row r="420" ht="15.75" customHeight="1">
+      <c r="C420" s="5"/>
+    </row>
+    <row r="421" ht="15.75" customHeight="1">
+      <c r="C421" s="5"/>
+    </row>
+    <row r="422" ht="15.75" customHeight="1">
+      <c r="C422" s="5"/>
+    </row>
+    <row r="423" ht="15.75" customHeight="1">
+      <c r="C423" s="5"/>
+    </row>
+    <row r="424" ht="15.75" customHeight="1">
+      <c r="C424" s="5"/>
+    </row>
+    <row r="425" ht="15.75" customHeight="1">
+      <c r="C425" s="5"/>
+    </row>
+    <row r="426" ht="15.75" customHeight="1">
+      <c r="C426" s="5"/>
+    </row>
+    <row r="427" ht="15.75" customHeight="1">
+      <c r="C427" s="5"/>
+    </row>
+    <row r="428" ht="15.75" customHeight="1">
+      <c r="C428" s="5"/>
+    </row>
+    <row r="429" ht="15.75" customHeight="1">
+      <c r="C429" s="5"/>
+    </row>
+    <row r="430" ht="15.75" customHeight="1">
+      <c r="C430" s="5"/>
+    </row>
+    <row r="431" ht="15.75" customHeight="1">
+      <c r="C431" s="5"/>
+    </row>
+    <row r="432" ht="15.75" customHeight="1">
+      <c r="C432" s="5"/>
+    </row>
+    <row r="433" ht="15.75" customHeight="1">
+      <c r="C433" s="5"/>
+    </row>
+    <row r="434" ht="15.75" customHeight="1">
+      <c r="C434" s="5"/>
+    </row>
+    <row r="435" ht="15.75" customHeight="1">
+      <c r="C435" s="5"/>
+    </row>
+    <row r="436" ht="15.75" customHeight="1">
+      <c r="C436" s="5"/>
+    </row>
+    <row r="437" ht="15.75" customHeight="1">
+      <c r="C437" s="5"/>
+    </row>
+    <row r="438" ht="15.75" customHeight="1">
+      <c r="C438" s="5"/>
+    </row>
+    <row r="439" ht="15.75" customHeight="1">
+      <c r="C439" s="5"/>
+    </row>
+    <row r="440" ht="15.75" customHeight="1">
+      <c r="C440" s="5"/>
+    </row>
+    <row r="441" ht="15.75" customHeight="1">
+      <c r="C441" s="5"/>
+    </row>
+    <row r="442" ht="15.75" customHeight="1">
+      <c r="C442" s="5"/>
+    </row>
+    <row r="443" ht="15.75" customHeight="1">
+      <c r="C443" s="5"/>
+    </row>
+    <row r="444" ht="15.75" customHeight="1">
+      <c r="C444" s="5"/>
+    </row>
+    <row r="445" ht="15.75" customHeight="1">
+      <c r="C445" s="5"/>
+    </row>
+    <row r="446" ht="15.75" customHeight="1">
+      <c r="C446" s="5"/>
+    </row>
+    <row r="447" ht="15.75" customHeight="1">
+      <c r="C447" s="5"/>
+    </row>
+    <row r="448" ht="15.75" customHeight="1">
+      <c r="C448" s="5"/>
+    </row>
+    <row r="449" ht="15.75" customHeight="1">
+      <c r="C449" s="5"/>
+    </row>
+    <row r="450" ht="15.75" customHeight="1">
+      <c r="C450" s="5"/>
+    </row>
+    <row r="451" ht="15.75" customHeight="1">
+      <c r="C451" s="5"/>
+    </row>
+    <row r="452" ht="15.75" customHeight="1">
+      <c r="C452" s="5"/>
+    </row>
+    <row r="453" ht="15.75" customHeight="1">
+      <c r="C453" s="5"/>
+    </row>
+    <row r="454" ht="15.75" customHeight="1">
+      <c r="C454" s="5"/>
+    </row>
+    <row r="455" ht="15.75" customHeight="1">
+      <c r="C455" s="5"/>
+    </row>
+    <row r="456" ht="15.75" customHeight="1">
+      <c r="C456" s="5"/>
+    </row>
+    <row r="457" ht="15.75" customHeight="1">
+      <c r="C457" s="5"/>
+    </row>
+    <row r="458" ht="15.75" customHeight="1">
+      <c r="C458" s="5"/>
+    </row>
+    <row r="459" ht="15.75" customHeight="1">
+      <c r="C459" s="5"/>
+    </row>
+    <row r="460" ht="15.75" customHeight="1">
+      <c r="C460" s="5"/>
+    </row>
+    <row r="461" ht="15.75" customHeight="1">
+      <c r="C461" s="5"/>
+    </row>
+    <row r="462" ht="15.75" customHeight="1">
+      <c r="C462" s="5"/>
+    </row>
+    <row r="463" ht="15.75" customHeight="1">
+      <c r="C463" s="5"/>
+    </row>
+    <row r="464" ht="15.75" customHeight="1">
+      <c r="C464" s="5"/>
+    </row>
+    <row r="465" ht="15.75" customHeight="1">
+      <c r="C465" s="5"/>
+    </row>
+    <row r="466" ht="15.75" customHeight="1">
+      <c r="C466" s="5"/>
+    </row>
+    <row r="467" ht="15.75" customHeight="1">
+      <c r="C467" s="5"/>
+    </row>
+    <row r="468" ht="15.75" customHeight="1">
+      <c r="C468" s="5"/>
+    </row>
+    <row r="469" ht="15.75" customHeight="1">
+      <c r="C469" s="5"/>
+    </row>
+    <row r="470" ht="15.75" customHeight="1">
+      <c r="C470" s="5"/>
+    </row>
+    <row r="471" ht="15.75" customHeight="1">
+      <c r="C471" s="5"/>
+    </row>
+    <row r="472" ht="15.75" customHeight="1">
+      <c r="C472" s="5"/>
+    </row>
+    <row r="473" ht="15.75" customHeight="1">
+      <c r="C473" s="5"/>
+    </row>
+    <row r="474" ht="15.75" customHeight="1">
+      <c r="C474" s="5"/>
+    </row>
+    <row r="475" ht="15.75" customHeight="1">
+      <c r="C475" s="5"/>
+    </row>
+    <row r="476" ht="15.75" customHeight="1">
+      <c r="C476" s="5"/>
+    </row>
+    <row r="477" ht="15.75" customHeight="1">
+      <c r="C477" s="5"/>
+    </row>
+    <row r="478" ht="15.75" customHeight="1">
+      <c r="C478" s="5"/>
+    </row>
+    <row r="479" ht="15.75" customHeight="1">
+      <c r="C479" s="5"/>
+    </row>
+    <row r="480" ht="15.75" customHeight="1">
+      <c r="C480" s="5"/>
+    </row>
+    <row r="481" ht="15.75" customHeight="1">
+      <c r="C481" s="5"/>
+    </row>
+    <row r="482" ht="15.75" customHeight="1">
+      <c r="C482" s="5"/>
+    </row>
+    <row r="483" ht="15.75" customHeight="1">
+      <c r="C483" s="5"/>
+    </row>
+    <row r="484" ht="15.75" customHeight="1">
+      <c r="C484" s="5"/>
+    </row>
+    <row r="485" ht="15.75" customHeight="1">
+      <c r="C485" s="5"/>
+    </row>
+    <row r="486" ht="15.75" customHeight="1">
+      <c r="C486" s="5"/>
+    </row>
+    <row r="487" ht="15.75" customHeight="1">
+      <c r="C487" s="5"/>
+    </row>
+    <row r="488" ht="15.75" customHeight="1">
+      <c r="C488" s="5"/>
+    </row>
+    <row r="489" ht="15.75" customHeight="1">
+      <c r="C489" s="5"/>
+    </row>
+    <row r="490" ht="15.75" customHeight="1">
+      <c r="C490" s="5"/>
+    </row>
+    <row r="491" ht="15.75" customHeight="1">
+      <c r="C491" s="5"/>
+    </row>
+    <row r="492" ht="15.75" customHeight="1">
+      <c r="C492" s="5"/>
+    </row>
+    <row r="493" ht="15.75" customHeight="1">
+      <c r="C493" s="5"/>
+    </row>
+    <row r="494" ht="15.75" customHeight="1">
+      <c r="C494" s="5"/>
+    </row>
+    <row r="495" ht="15.75" customHeight="1">
+      <c r="C495" s="5"/>
+    </row>
+    <row r="496" ht="15.75" customHeight="1">
+      <c r="C496" s="5"/>
+    </row>
+    <row r="497" ht="15.75" customHeight="1">
+      <c r="C497" s="5"/>
+    </row>
+    <row r="498" ht="15.75" customHeight="1">
+      <c r="C498" s="5"/>
+    </row>
+    <row r="499" ht="15.75" customHeight="1">
+      <c r="C499" s="5"/>
+    </row>
+    <row r="500" ht="15.75" customHeight="1">
+      <c r="C500" s="5"/>
+    </row>
+    <row r="501" ht="15.75" customHeight="1">
+      <c r="C501" s="5"/>
+    </row>
+    <row r="502" ht="15.75" customHeight="1">
+      <c r="C502" s="5"/>
+    </row>
+    <row r="503" ht="15.75" customHeight="1">
+      <c r="C503" s="5"/>
+    </row>
+    <row r="504" ht="15.75" customHeight="1">
+      <c r="C504" s="5"/>
+    </row>
+    <row r="505" ht="15.75" customHeight="1">
+      <c r="C505" s="5"/>
+    </row>
+    <row r="506" ht="15.75" customHeight="1">
+      <c r="C506" s="5"/>
+    </row>
+    <row r="507" ht="15.75" customHeight="1">
+      <c r="C507" s="5"/>
+    </row>
+    <row r="508" ht="15.75" customHeight="1">
+      <c r="C508" s="5"/>
+    </row>
+    <row r="509" ht="15.75" customHeight="1">
+      <c r="C509" s="5"/>
+    </row>
+    <row r="510" ht="15.75" customHeight="1">
+      <c r="C510" s="5"/>
+    </row>
+    <row r="511" ht="15.75" customHeight="1">
+      <c r="C511" s="5"/>
+    </row>
+    <row r="512" ht="15.75" customHeight="1">
+      <c r="C512" s="5"/>
+    </row>
+    <row r="513" ht="15.75" customHeight="1">
+      <c r="C513" s="5"/>
+    </row>
+    <row r="514" ht="15.75" customHeight="1">
+      <c r="C514" s="5"/>
+    </row>
+    <row r="515" ht="15.75" customHeight="1">
+      <c r="C515" s="5"/>
+    </row>
+    <row r="516" ht="15.75" customHeight="1">
+      <c r="C516" s="5"/>
+    </row>
+    <row r="517" ht="15.75" customHeight="1">
+      <c r="C517" s="5"/>
+    </row>
+    <row r="518" ht="15.75" customHeight="1">
+      <c r="C518" s="5"/>
+    </row>
+    <row r="519" ht="15.75" customHeight="1">
+      <c r="C519" s="5"/>
+    </row>
+    <row r="520" ht="15.75" customHeight="1">
+      <c r="C520" s="5"/>
+    </row>
+    <row r="521" ht="15.75" customHeight="1">
+      <c r="C521" s="5"/>
+    </row>
+    <row r="522" ht="15.75" customHeight="1">
+      <c r="C522" s="5"/>
+    </row>
+    <row r="523" ht="15.75" customHeight="1">
+      <c r="C523" s="5"/>
+    </row>
+    <row r="524" ht="15.75" customHeight="1">
+      <c r="C524" s="5"/>
+    </row>
+    <row r="525" ht="15.75" customHeight="1">
+      <c r="C525" s="5"/>
+    </row>
+    <row r="526" ht="15.75" customHeight="1">
+      <c r="C526" s="5"/>
+    </row>
+    <row r="527" ht="15.75" customHeight="1">
+      <c r="C527" s="5"/>
+    </row>
+    <row r="528" ht="15.75" customHeight="1">
+      <c r="C528" s="5"/>
+    </row>
+    <row r="529" ht="15.75" customHeight="1">
+      <c r="C529" s="5"/>
+    </row>
+    <row r="530" ht="15.75" customHeight="1">
+      <c r="C530" s="5"/>
+    </row>
+    <row r="531" ht="15.75" customHeight="1">
+      <c r="C531" s="5"/>
+    </row>
+    <row r="532" ht="15.75" customHeight="1">
+      <c r="C532" s="5"/>
+    </row>
+    <row r="533" ht="15.75" customHeight="1">
+      <c r="C533" s="5"/>
+    </row>
+    <row r="534" ht="15.75" customHeight="1">
+      <c r="C534" s="5"/>
+    </row>
+    <row r="535" ht="15.75" customHeight="1">
+      <c r="C535" s="5"/>
+    </row>
+    <row r="536" ht="15.75" customHeight="1">
+      <c r="C536" s="5"/>
+    </row>
+    <row r="537" ht="15.75" customHeight="1">
+      <c r="C537" s="5"/>
+    </row>
+    <row r="538" ht="15.75" customHeight="1">
+      <c r="C538" s="5"/>
+    </row>
+    <row r="539" ht="15.75" customHeight="1">
+      <c r="C539" s="5"/>
+    </row>
+    <row r="540" ht="15.75" customHeight="1">
+      <c r="C540" s="5"/>
+    </row>
+    <row r="541" ht="15.75" customHeight="1">
+      <c r="C541" s="5"/>
+    </row>
+    <row r="542" ht="15.75" customHeight="1">
+      <c r="C542" s="5"/>
+    </row>
+    <row r="543" ht="15.75" customHeight="1">
+      <c r="C543" s="5"/>
+    </row>
+    <row r="544" ht="15.75" customHeight="1">
+      <c r="C544" s="5"/>
+    </row>
+    <row r="545" ht="15.75" customHeight="1">
+      <c r="C545" s="5"/>
+    </row>
+    <row r="546" ht="15.75" customHeight="1">
+      <c r="C546" s="5"/>
+    </row>
+    <row r="547" ht="15.75" customHeight="1">
+      <c r="C547" s="5"/>
+    </row>
+    <row r="548" ht="15.75" customHeight="1">
+      <c r="C548" s="5"/>
+    </row>
+    <row r="549" ht="15.75" customHeight="1">
+      <c r="C549" s="5"/>
+    </row>
+    <row r="550" ht="15.75" customHeight="1">
+      <c r="C550" s="5"/>
+    </row>
+    <row r="551" ht="15.75" customHeight="1">
+      <c r="C551" s="5"/>
+    </row>
+    <row r="552" ht="15.75" customHeight="1">
+      <c r="C552" s="5"/>
+    </row>
+    <row r="553" ht="15.75" customHeight="1">
+      <c r="C553" s="5"/>
+    </row>
+    <row r="554" ht="15.75" customHeight="1">
+      <c r="C554" s="5"/>
+    </row>
+    <row r="555" ht="15.75" customHeight="1">
+      <c r="C555" s="5"/>
+    </row>
+    <row r="556" ht="15.75" customHeight="1">
+      <c r="C556" s="5"/>
+    </row>
+    <row r="557" ht="15.75" customHeight="1">
+      <c r="C557" s="5"/>
+    </row>
+    <row r="558" ht="15.75" customHeight="1">
+      <c r="C558" s="5"/>
+    </row>
+    <row r="559" ht="15.75" customHeight="1">
+      <c r="C559" s="5"/>
+    </row>
+    <row r="560" ht="15.75" customHeight="1">
+      <c r="C560" s="5"/>
+    </row>
+    <row r="561" ht="15.75" customHeight="1">
+      <c r="C561" s="5"/>
+    </row>
+    <row r="562" ht="15.75" customHeight="1">
+      <c r="C562" s="5"/>
+    </row>
+    <row r="563" ht="15.75" customHeight="1">
+      <c r="C563" s="5"/>
+    </row>
+    <row r="564" ht="15.75" customHeight="1">
+      <c r="C564" s="5"/>
+    </row>
+    <row r="565" ht="15.75" customHeight="1">
+      <c r="C565" s="5"/>
+    </row>
+    <row r="566" ht="15.75" customHeight="1">
+      <c r="C566" s="5"/>
+    </row>
+    <row r="567" ht="15.75" customHeight="1">
+      <c r="C567" s="5"/>
+    </row>
+    <row r="568" ht="15.75" customHeight="1">
+      <c r="C568" s="5"/>
+    </row>
+    <row r="569" ht="15.75" customHeight="1">
+      <c r="C569" s="5"/>
+    </row>
+    <row r="570" ht="15.75" customHeight="1">
+      <c r="C570" s="5"/>
+    </row>
+    <row r="571" ht="15.75" customHeight="1">
+      <c r="C571" s="5"/>
+    </row>
+    <row r="572" ht="15.75" customHeight="1">
+      <c r="C572" s="5"/>
+    </row>
+    <row r="573" ht="15.75" customHeight="1">
+      <c r="C573" s="5"/>
+    </row>
+    <row r="574" ht="15.75" customHeight="1">
+      <c r="C574" s="5"/>
+    </row>
+    <row r="575" ht="15.75" customHeight="1">
+      <c r="C575" s="5"/>
+    </row>
+    <row r="576" ht="15.75" customHeight="1">
+      <c r="C576" s="5"/>
+    </row>
+    <row r="577" ht="15.75" customHeight="1">
+      <c r="C577" s="5"/>
+    </row>
+    <row r="578" ht="15.75" customHeight="1">
+      <c r="C578" s="5"/>
+    </row>
+    <row r="579" ht="15.75" customHeight="1">
+      <c r="C579" s="5"/>
+    </row>
+    <row r="580" ht="15.75" customHeight="1">
+      <c r="C580" s="5"/>
+    </row>
+    <row r="581" ht="15.75" customHeight="1">
+      <c r="C581" s="5"/>
+    </row>
+    <row r="582" ht="15.75" customHeight="1">
+      <c r="C582" s="5"/>
+    </row>
+    <row r="583" ht="15.75" customHeight="1">
+      <c r="C583" s="5"/>
+    </row>
+    <row r="584" ht="15.75" customHeight="1">
+      <c r="C584" s="5"/>
+    </row>
+    <row r="585" ht="15.75" customHeight="1">
+      <c r="C585" s="5"/>
+    </row>
+    <row r="586" ht="15.75" customHeight="1">
+      <c r="C586" s="5"/>
+    </row>
+    <row r="587" ht="15.75" customHeight="1">
+      <c r="C587" s="5"/>
+    </row>
+    <row r="588" ht="15.75" customHeight="1">
+      <c r="C588" s="5"/>
+    </row>
+    <row r="589" ht="15.75" customHeight="1">
+      <c r="C589" s="5"/>
+    </row>
+    <row r="590" ht="15.75" customHeight="1">
+      <c r="C590" s="5"/>
+    </row>
+    <row r="591" ht="15.75" customHeight="1">
+      <c r="C591" s="5"/>
+    </row>
+    <row r="592" ht="15.75" customHeight="1">
+      <c r="C592" s="5"/>
+    </row>
+    <row r="593" ht="15.75" customHeight="1">
+      <c r="C593" s="5"/>
+    </row>
+    <row r="594" ht="15.75" customHeight="1">
+      <c r="C594" s="5"/>
+    </row>
+    <row r="595" ht="15.75" customHeight="1">
+      <c r="C595" s="5"/>
+    </row>
+    <row r="596" ht="15.75" customHeight="1">
+      <c r="C596" s="5"/>
+    </row>
+    <row r="597" ht="15.75" customHeight="1">
+      <c r="C597" s="5"/>
+    </row>
+    <row r="598" ht="15.75" customHeight="1">
+      <c r="C598" s="5"/>
+    </row>
+    <row r="599" ht="15.75" customHeight="1">
+      <c r="C599" s="5"/>
+    </row>
+    <row r="600" ht="15.75" customHeight="1">
+      <c r="C600" s="5"/>
+    </row>
+    <row r="601" ht="15.75" customHeight="1">
+      <c r="C601" s="5"/>
+    </row>
+    <row r="602" ht="15.75" customHeight="1">
+      <c r="C602" s="5"/>
+    </row>
+    <row r="603" ht="15.75" customHeight="1">
+      <c r="C603" s="5"/>
+    </row>
+    <row r="604" ht="15.75" customHeight="1">
+      <c r="C604" s="5"/>
+    </row>
+    <row r="605" ht="15.75" customHeight="1">
+      <c r="C605" s="5"/>
+    </row>
+    <row r="606" ht="15.75" customHeight="1">
+      <c r="C606" s="5"/>
+    </row>
+    <row r="607" ht="15.75" customHeight="1">
+      <c r="C607" s="5"/>
+    </row>
+    <row r="608" ht="15.75" customHeight="1">
+      <c r="C608" s="5"/>
+    </row>
+    <row r="609" ht="15.75" customHeight="1">
+      <c r="C609" s="5"/>
+    </row>
+    <row r="610" ht="15.75" customHeight="1">
+      <c r="C610" s="5"/>
+    </row>
+    <row r="611" ht="15.75" customHeight="1">
+      <c r="C611" s="5"/>
+    </row>
+    <row r="612" ht="15.75" customHeight="1">
+      <c r="C612" s="5"/>
+    </row>
+    <row r="613" ht="15.75" customHeight="1">
+      <c r="C613" s="5"/>
+    </row>
+    <row r="614" ht="15.75" customHeight="1">
+      <c r="C614" s="5"/>
+    </row>
+    <row r="615" ht="15.75" customHeight="1">
+      <c r="C615" s="5"/>
+    </row>
+    <row r="616" ht="15.75" customHeight="1">
+      <c r="C616" s="5"/>
+    </row>
+    <row r="617" ht="15.75" customHeight="1">
+      <c r="C617" s="5"/>
+    </row>
+    <row r="618" ht="15.75" customHeight="1">
+      <c r="C618" s="5"/>
+    </row>
+    <row r="619" ht="15.75" customHeight="1">
+      <c r="C619" s="5"/>
+    </row>
+    <row r="620" ht="15.75" customHeight="1">
+      <c r="C620" s="5"/>
+    </row>
+    <row r="621" ht="15.75" customHeight="1">
+      <c r="C621" s="5"/>
+    </row>
+    <row r="622" ht="15.75" customHeight="1">
+      <c r="C622" s="5"/>
+    </row>
+    <row r="623" ht="15.75" customHeight="1">
+      <c r="C623" s="5"/>
+    </row>
+    <row r="624" ht="15.75" customHeight="1">
+      <c r="C624" s="5"/>
+    </row>
+    <row r="625" ht="15.75" customHeight="1">
+      <c r="C625" s="5"/>
+    </row>
+    <row r="626" ht="15.75" customHeight="1">
+      <c r="C626" s="5"/>
+    </row>
+    <row r="627" ht="15.75" customHeight="1">
+      <c r="C627" s="5"/>
+    </row>
+    <row r="628" ht="15.75" customHeight="1">
+      <c r="C628" s="5"/>
+    </row>
+    <row r="629" ht="15.75" customHeight="1">
+      <c r="C629" s="5"/>
+    </row>
+    <row r="630" ht="15.75" customHeight="1">
+      <c r="C630" s="5"/>
+    </row>
+    <row r="631" ht="15.75" customHeight="1">
+      <c r="C631" s="5"/>
+    </row>
+    <row r="632" ht="15.75" customHeight="1">
+      <c r="C632" s="5"/>
+    </row>
+    <row r="633" ht="15.75" customHeight="1">
+      <c r="C633" s="5"/>
+    </row>
+    <row r="634" ht="15.75" customHeight="1">
+      <c r="C634" s="5"/>
+    </row>
+    <row r="635" ht="15.75" customHeight="1">
+      <c r="C635" s="5"/>
+    </row>
+    <row r="636" ht="15.75" customHeight="1">
+      <c r="C636" s="5"/>
+    </row>
+    <row r="637" ht="15.75" customHeight="1">
+      <c r="C637" s="5"/>
+    </row>
+    <row r="638" ht="15.75" customHeight="1">
+      <c r="C638" s="5"/>
+    </row>
+    <row r="639" ht="15.75" customHeight="1">
+      <c r="C639" s="5"/>
+    </row>
+    <row r="640" ht="15.75" customHeight="1">
+      <c r="C640" s="5"/>
+    </row>
+    <row r="641" ht="15.75" customHeight="1">
+      <c r="C641" s="5"/>
+    </row>
+    <row r="642" ht="15.75" customHeight="1">
+      <c r="C642" s="5"/>
+    </row>
+    <row r="643" ht="15.75" customHeight="1">
+      <c r="C643" s="5"/>
+    </row>
+    <row r="644" ht="15.75" customHeight="1">
+      <c r="C644" s="5"/>
+    </row>
+    <row r="645" ht="15.75" customHeight="1">
+      <c r="C645" s="5"/>
+    </row>
+    <row r="646" ht="15.75" customHeight="1">
+      <c r="C646" s="5"/>
+    </row>
+    <row r="647" ht="15.75" customHeight="1">
+      <c r="C647" s="5"/>
+    </row>
+    <row r="648" ht="15.75" customHeight="1">
+      <c r="C648" s="5"/>
+    </row>
+    <row r="649" ht="15.75" customHeight="1">
+      <c r="C649" s="5"/>
+    </row>
+    <row r="650" ht="15.75" customHeight="1">
+      <c r="C650" s="5"/>
+    </row>
+    <row r="651" ht="15.75" customHeight="1">
+      <c r="C651" s="5"/>
+    </row>
+    <row r="652" ht="15.75" customHeight="1">
+      <c r="C652" s="5"/>
+    </row>
+    <row r="653" ht="15.75" customHeight="1">
+      <c r="C653" s="5"/>
+    </row>
+    <row r="654" ht="15.75" customHeight="1">
+      <c r="C654" s="5"/>
+    </row>
+    <row r="655" ht="15.75" customHeight="1">
+      <c r="C655" s="5"/>
+    </row>
+    <row r="656" ht="15.75" customHeight="1">
+      <c r="C656" s="5"/>
+    </row>
+    <row r="657" ht="15.75" customHeight="1">
+      <c r="C657" s="5"/>
+    </row>
+    <row r="658" ht="15.75" customHeight="1">
+      <c r="C658" s="5"/>
+    </row>
+    <row r="659" ht="15.75" customHeight="1">
+      <c r="C659" s="5"/>
+    </row>
+    <row r="660" ht="15.75" customHeight="1">
+      <c r="C660" s="5"/>
+    </row>
+    <row r="661" ht="15.75" customHeight="1">
+      <c r="C661" s="5"/>
+    </row>
+    <row r="662" ht="15.75" customHeight="1">
+      <c r="C662" s="5"/>
+    </row>
+    <row r="663" ht="15.75" customHeight="1">
+      <c r="C663" s="5"/>
+    </row>
+    <row r="664" ht="15.75" customHeight="1">
+      <c r="C664" s="5"/>
+    </row>
+    <row r="665" ht="15.75" customHeight="1">
+      <c r="C665" s="5"/>
+    </row>
+    <row r="666" ht="15.75" customHeight="1">
+      <c r="C666" s="5"/>
+    </row>
+    <row r="667" ht="15.75" customHeight="1">
+      <c r="C667" s="5"/>
+    </row>
+    <row r="668" ht="15.75" customHeight="1">
+      <c r="C668" s="5"/>
+    </row>
+    <row r="669" ht="15.75" customHeight="1">
+      <c r="C669" s="5"/>
+    </row>
+    <row r="670" ht="15.75" customHeight="1">
+      <c r="C670" s="5"/>
+    </row>
+    <row r="671" ht="15.75" customHeight="1">
+      <c r="C671" s="5"/>
+    </row>
+    <row r="672" ht="15.75" customHeight="1">
+      <c r="C672" s="5"/>
+    </row>
+    <row r="673" ht="15.75" customHeight="1">
+      <c r="C673" s="5"/>
+    </row>
+    <row r="674" ht="15.75" customHeight="1">
+      <c r="C674" s="5"/>
+    </row>
+    <row r="675" ht="15.75" customHeight="1">
+      <c r="C675" s="5"/>
+    </row>
+    <row r="676" ht="15.75" customHeight="1">
+      <c r="C676" s="5"/>
+    </row>
+    <row r="677" ht="15.75" customHeight="1">
+      <c r="C677" s="5"/>
+    </row>
+    <row r="678" ht="15.75" customHeight="1">
+      <c r="C678" s="5"/>
+    </row>
+    <row r="679" ht="15.75" customHeight="1">
+      <c r="C679" s="5"/>
+    </row>
+    <row r="680" ht="15.75" customHeight="1">
+      <c r="C680" s="5"/>
+    </row>
+    <row r="681" ht="15.75" customHeight="1">
+      <c r="C681" s="5"/>
+    </row>
+    <row r="682" ht="15.75" customHeight="1">
+      <c r="C682" s="5"/>
+    </row>
+    <row r="683" ht="15.75" customHeight="1">
+      <c r="C683" s="5"/>
+    </row>
+    <row r="684" ht="15.75" customHeight="1">
+      <c r="C684" s="5"/>
+    </row>
+    <row r="685" ht="15.75" customHeight="1">
+      <c r="C685" s="5"/>
+    </row>
+    <row r="686" ht="15.75" customHeight="1">
+      <c r="C686" s="5"/>
+    </row>
+    <row r="687" ht="15.75" customHeight="1">
+      <c r="C687" s="5"/>
+    </row>
+    <row r="688" ht="15.75" customHeight="1">
+      <c r="C688" s="5"/>
+    </row>
+    <row r="689" ht="15.75" customHeight="1">
+      <c r="C689" s="5"/>
+    </row>
+    <row r="690" ht="15.75" customHeight="1">
+      <c r="C690" s="5"/>
+    </row>
+    <row r="691" ht="15.75" customHeight="1">
+      <c r="C691" s="5"/>
+    </row>
+    <row r="692" ht="15.75" customHeight="1">
+      <c r="C692" s="5"/>
+    </row>
+    <row r="693" ht="15.75" customHeight="1">
+      <c r="C693" s="5"/>
+    </row>
+    <row r="694" ht="15.75" customHeight="1">
+      <c r="C694" s="5"/>
+    </row>
+    <row r="695" ht="15.75" customHeight="1">
+      <c r="C695" s="5"/>
+    </row>
+    <row r="696" ht="15.75" customHeight="1">
+      <c r="C696" s="5"/>
+    </row>
+    <row r="697" ht="15.75" customHeight="1">
+      <c r="C697" s="5"/>
+    </row>
+    <row r="698" ht="15.75" customHeight="1">
+      <c r="C698" s="5"/>
+    </row>
+    <row r="699" ht="15.75" customHeight="1">
+      <c r="C699" s="5"/>
+    </row>
+    <row r="700" ht="15.75" customHeight="1">
+      <c r="C700" s="5"/>
+    </row>
+    <row r="701" ht="15.75" customHeight="1">
+      <c r="C701" s="5"/>
+    </row>
+    <row r="702" ht="15.75" customHeight="1">
+      <c r="C702" s="5"/>
+    </row>
+    <row r="703" ht="15.75" customHeight="1">
+      <c r="C703" s="5"/>
+    </row>
+    <row r="704" ht="15.75" customHeight="1">
+      <c r="C704" s="5"/>
+    </row>
+    <row r="705" ht="15.75" customHeight="1">
+      <c r="C705" s="5"/>
+    </row>
+    <row r="706" ht="15.75" customHeight="1">
+      <c r="C706" s="5"/>
+    </row>
+    <row r="707" ht="15.75" customHeight="1">
+      <c r="C707" s="5"/>
+    </row>
+    <row r="708" ht="15.75" customHeight="1">
+      <c r="C708" s="5"/>
+    </row>
+    <row r="709" ht="15.75" customHeight="1">
+      <c r="C709" s="5"/>
+    </row>
+    <row r="710" ht="15.75" customHeight="1">
+      <c r="C710" s="5"/>
+    </row>
+    <row r="711" ht="15.75" customHeight="1">
+      <c r="C711" s="5"/>
+    </row>
+    <row r="712" ht="15.75" customHeight="1">
+      <c r="C712" s="5"/>
+    </row>
+    <row r="713" ht="15.75" customHeight="1">
+      <c r="C713" s="5"/>
+    </row>
+    <row r="714" ht="15.75" customHeight="1">
+      <c r="C714" s="5"/>
+    </row>
+    <row r="715" ht="15.75" customHeight="1">
+      <c r="C715" s="5"/>
+    </row>
+    <row r="716" ht="15.75" customHeight="1">
+      <c r="C716" s="5"/>
+    </row>
+    <row r="717" ht="15.75" customHeight="1">
+      <c r="C717" s="5"/>
+    </row>
+    <row r="718" ht="15.75" customHeight="1">
+      <c r="C718" s="5"/>
+    </row>
+    <row r="719" ht="15.75" customHeight="1">
+      <c r="C719" s="5"/>
+    </row>
+    <row r="720" ht="15.75" customHeight="1">
+      <c r="C720" s="5"/>
+    </row>
+    <row r="721" ht="15.75" customHeight="1">
+      <c r="C721" s="5"/>
+    </row>
+    <row r="722" ht="15.75" customHeight="1">
+      <c r="C722" s="5"/>
+    </row>
+    <row r="723" ht="15.75" customHeight="1">
+      <c r="C723" s="5"/>
+    </row>
+    <row r="724" ht="15.75" customHeight="1">
+      <c r="C724" s="5"/>
+    </row>
+    <row r="725" ht="15.75" customHeight="1">
+      <c r="C725" s="5"/>
+    </row>
+    <row r="726" ht="15.75" customHeight="1">
+      <c r="C726" s="5"/>
+    </row>
+    <row r="727" ht="15.75" customHeight="1">
+      <c r="C727" s="5"/>
+    </row>
+    <row r="728" ht="15.75" customHeight="1">
+      <c r="C728" s="5"/>
+    </row>
+    <row r="729" ht="15.75" customHeight="1">
+      <c r="C729" s="5"/>
+    </row>
+    <row r="730" ht="15.75" customHeight="1">
+      <c r="C730" s="5"/>
+    </row>
+    <row r="731" ht="15.75" customHeight="1">
+      <c r="C731" s="5"/>
+    </row>
+    <row r="732" ht="15.75" customHeight="1">
+      <c r="C732" s="5"/>
+    </row>
+    <row r="733" ht="15.75" customHeight="1">
+      <c r="C733" s="5"/>
+    </row>
+    <row r="734" ht="15.75" customHeight="1">
+      <c r="C734" s="5"/>
+    </row>
+    <row r="735" ht="15.75" customHeight="1">
+      <c r="C735" s="5"/>
+    </row>
+    <row r="736" ht="15.75" customHeight="1">
+      <c r="C736" s="5"/>
+    </row>
+    <row r="737" ht="15.75" customHeight="1">
+      <c r="C737" s="5"/>
+    </row>
+    <row r="738" ht="15.75" customHeight="1">
+      <c r="C738" s="5"/>
+    </row>
+    <row r="739" ht="15.75" customHeight="1">
+      <c r="C739" s="5"/>
+    </row>
+    <row r="740" ht="15.75" customHeight="1">
+      <c r="C740" s="5"/>
+    </row>
+    <row r="741" ht="15.75" customHeight="1">
+      <c r="C741" s="5"/>
+    </row>
+    <row r="742" ht="15.75" customHeight="1">
+      <c r="C742" s="5"/>
+    </row>
+    <row r="743" ht="15.75" customHeight="1">
+      <c r="C743" s="5"/>
+    </row>
+    <row r="744" ht="15.75" customHeight="1">
+      <c r="C744" s="5"/>
+    </row>
+    <row r="745" ht="15.75" customHeight="1">
+      <c r="C745" s="5"/>
+    </row>
+    <row r="746" ht="15.75" customHeight="1">
+      <c r="C746" s="5"/>
+    </row>
+    <row r="747" ht="15.75" customHeight="1">
+      <c r="C747" s="5"/>
+    </row>
+    <row r="748" ht="15.75" customHeight="1">
+      <c r="C748" s="5"/>
+    </row>
+    <row r="749" ht="15.75" customHeight="1">
+      <c r="C749" s="5"/>
+    </row>
+    <row r="750" ht="15.75" customHeight="1">
+      <c r="C750" s="5"/>
+    </row>
+    <row r="751" ht="15.75" customHeight="1">
+      <c r="C751" s="5"/>
+    </row>
+    <row r="752" ht="15.75" customHeight="1">
+      <c r="C752" s="5"/>
+    </row>
+    <row r="753" ht="15.75" customHeight="1">
+      <c r="C753" s="5"/>
+    </row>
+    <row r="754" ht="15.75" customHeight="1">
+      <c r="C754" s="5"/>
+    </row>
+    <row r="755" ht="15.75" customHeight="1">
+      <c r="C755" s="5"/>
+    </row>
+    <row r="756" ht="15.75" customHeight="1">
+      <c r="C756" s="5"/>
+    </row>
+    <row r="757" ht="15.75" customHeight="1">
+      <c r="C757" s="5"/>
+    </row>
+    <row r="758" ht="15.75" customHeight="1">
+      <c r="C758" s="5"/>
+    </row>
+    <row r="759" ht="15.75" customHeight="1">
+      <c r="C759" s="5"/>
+    </row>
+    <row r="760" ht="15.75" customHeight="1">
+      <c r="C760" s="5"/>
+    </row>
+    <row r="761" ht="15.75" customHeight="1">
+      <c r="C761" s="5"/>
+    </row>
+    <row r="762" ht="15.75" customHeight="1">
+      <c r="C762" s="5"/>
+    </row>
+    <row r="763" ht="15.75" customHeight="1">
+      <c r="C763" s="5"/>
+    </row>
+    <row r="764" ht="15.75" customHeight="1">
+      <c r="C764" s="5"/>
+    </row>
+    <row r="765" ht="15.75" customHeight="1">
+      <c r="C765" s="5"/>
+    </row>
+    <row r="766" ht="15.75" customHeight="1">
+      <c r="C766" s="5"/>
+    </row>
+    <row r="767" ht="15.75" customHeight="1">
+      <c r="C767" s="5"/>
+    </row>
+    <row r="768" ht="15.75" customHeight="1">
+      <c r="C768" s="5"/>
+    </row>
+    <row r="769" ht="15.75" customHeight="1">
+      <c r="C769" s="5"/>
+    </row>
+    <row r="770" ht="15.75" customHeight="1">
+      <c r="C770" s="5"/>
+    </row>
+    <row r="771" ht="15.75" customHeight="1">
+      <c r="C771" s="5"/>
+    </row>
+    <row r="772" ht="15.75" customHeight="1">
+      <c r="C772" s="5"/>
+    </row>
+    <row r="773" ht="15.75" customHeight="1">
+      <c r="C773" s="5"/>
+    </row>
+    <row r="774" ht="15.75" customHeight="1">
+      <c r="C774" s="5"/>
+    </row>
+    <row r="775" ht="15.75" customHeight="1">
+      <c r="C775" s="5"/>
+    </row>
+    <row r="776" ht="15.75" customHeight="1">
+      <c r="C776" s="5"/>
+    </row>
+    <row r="777" ht="15.75" customHeight="1">
+      <c r="C777" s="5"/>
+    </row>
+    <row r="778" ht="15.75" customHeight="1">
+      <c r="C778" s="5"/>
+    </row>
+    <row r="779" ht="15.75" customHeight="1">
+      <c r="C779" s="5"/>
+    </row>
+    <row r="780" ht="15.75" customHeight="1">
+      <c r="C780" s="5"/>
+    </row>
+    <row r="781" ht="15.75" customHeight="1">
+      <c r="C781" s="5"/>
+    </row>
+    <row r="782" ht="15.75" customHeight="1">
+      <c r="C782" s="5"/>
+    </row>
+    <row r="783" ht="15.75" customHeight="1">
+      <c r="C783" s="5"/>
+    </row>
+    <row r="784" ht="15.75" customHeight="1">
+      <c r="C784" s="5"/>
+    </row>
+    <row r="785" ht="15.75" customHeight="1">
+      <c r="C785" s="5"/>
+    </row>
+    <row r="786" ht="15.75" customHeight="1">
+      <c r="C786" s="5"/>
+    </row>
+    <row r="787" ht="15.75" customHeight="1">
+      <c r="C787" s="5"/>
+    </row>
+    <row r="788" ht="15.75" customHeight="1">
+      <c r="C788" s="5"/>
+    </row>
+    <row r="789" ht="15.75" customHeight="1">
+      <c r="C789" s="5"/>
+    </row>
+    <row r="790" ht="15.75" customHeight="1">
+      <c r="C790" s="5"/>
+    </row>
+    <row r="791" ht="15.75" customHeight="1">
+      <c r="C791" s="5"/>
+    </row>
+    <row r="792" ht="15.75" customHeight="1">
+      <c r="C792" s="5"/>
+    </row>
+    <row r="793" ht="15.75" customHeight="1">
+      <c r="C793" s="5"/>
+    </row>
+    <row r="794" ht="15.75" customHeight="1">
+      <c r="C794" s="5"/>
+    </row>
+    <row r="795" ht="15.75" customHeight="1">
+      <c r="C795" s="5"/>
+    </row>
+    <row r="796" ht="15.75" customHeight="1">
+      <c r="C796" s="5"/>
+    </row>
+    <row r="797" ht="15.75" customHeight="1">
+      <c r="C797" s="5"/>
+    </row>
+    <row r="798" ht="15.75" customHeight="1">
+      <c r="C798" s="5"/>
+    </row>
+    <row r="799" ht="15.75" customHeight="1">
+      <c r="C799" s="5"/>
+    </row>
+    <row r="800" ht="15.75" customHeight="1">
+      <c r="C800" s="5"/>
+    </row>
+    <row r="801" ht="15.75" customHeight="1">
+      <c r="C801" s="5"/>
+    </row>
+    <row r="802" ht="15.75" customHeight="1">
+      <c r="C802" s="5"/>
+    </row>
+    <row r="803" ht="15.75" customHeight="1">
+      <c r="C803" s="5"/>
+    </row>
+    <row r="804" ht="15.75" customHeight="1">
+      <c r="C804" s="5"/>
+    </row>
+    <row r="805" ht="15.75" customHeight="1">
+      <c r="C805" s="5"/>
+    </row>
+    <row r="806" ht="15.75" customHeight="1">
+      <c r="C806" s="5"/>
+    </row>
+    <row r="807" ht="15.75" customHeight="1">
+      <c r="C807" s="5"/>
+    </row>
+    <row r="808" ht="15.75" customHeight="1">
+      <c r="C808" s="5"/>
+    </row>
+    <row r="809" ht="15.75" customHeight="1">
+      <c r="C809" s="5"/>
+    </row>
+    <row r="810" ht="15.75" customHeight="1">
+      <c r="C810" s="5"/>
+    </row>
+    <row r="811" ht="15.75" customHeight="1">
+      <c r="C811" s="5"/>
+    </row>
+    <row r="812" ht="15.75" customHeight="1">
+      <c r="C812" s="5"/>
+    </row>
+    <row r="813" ht="15.75" customHeight="1">
+      <c r="C813" s="5"/>
+    </row>
+    <row r="814" ht="15.75" customHeight="1">
+      <c r="C814" s="5"/>
+    </row>
+    <row r="815" ht="15.75" customHeight="1">
+      <c r="C815" s="5"/>
+    </row>
+    <row r="816" ht="15.75" customHeight="1">
+      <c r="C816" s="5"/>
+    </row>
+    <row r="817" ht="15.75" customHeight="1">
+      <c r="C817" s="5"/>
+    </row>
+    <row r="818" ht="15.75" customHeight="1">
+      <c r="C818" s="5"/>
+    </row>
+    <row r="819" ht="15.75" customHeight="1">
+      <c r="C819" s="5"/>
+    </row>
+    <row r="820" ht="15.75" customHeight="1">
+      <c r="C820" s="5"/>
+    </row>
+    <row r="821" ht="15.75" customHeight="1">
+      <c r="C821" s="5"/>
+    </row>
+    <row r="822" ht="15.75" customHeight="1">
+      <c r="C822" s="5"/>
+    </row>
+    <row r="823" ht="15.75" customHeight="1">
+      <c r="C823" s="5"/>
+    </row>
+    <row r="824" ht="15.75" customHeight="1">
+      <c r="C824" s="5"/>
+    </row>
+    <row r="825" ht="15.75" customHeight="1">
+      <c r="C825" s="5"/>
+    </row>
+    <row r="826" ht="15.75" customHeight="1">
+      <c r="C826" s="5"/>
+    </row>
+    <row r="827" ht="15.75" customHeight="1">
+      <c r="C827" s="5"/>
+    </row>
+    <row r="828" ht="15.75" customHeight="1">
+      <c r="C828" s="5"/>
+    </row>
+    <row r="829" ht="15.75" customHeight="1">
+      <c r="C829" s="5"/>
+    </row>
+    <row r="830" ht="15.75" customHeight="1">
+      <c r="C830" s="5"/>
+    </row>
+    <row r="831" ht="15.75" customHeight="1">
+      <c r="C831" s="5"/>
+    </row>
+    <row r="832" ht="15.75" customHeight="1">
+      <c r="C832" s="5"/>
+    </row>
+    <row r="833" ht="15.75" customHeight="1">
+      <c r="C833" s="5"/>
+    </row>
+    <row r="834" ht="15.75" customHeight="1">
+      <c r="C834" s="5"/>
+    </row>
+    <row r="835" ht="15.75" customHeight="1">
+      <c r="C835" s="5"/>
+    </row>
+    <row r="836" ht="15.75" customHeight="1">
+      <c r="C836" s="5"/>
+    </row>
+    <row r="837" ht="15.75" customHeight="1">
+      <c r="C837" s="5"/>
+    </row>
+    <row r="838" ht="15.75" customHeight="1">
+      <c r="C838" s="5"/>
+    </row>
+    <row r="839" ht="15.75" customHeight="1">
+      <c r="C839" s="5"/>
+    </row>
+    <row r="840" ht="15.75" customHeight="1">
+      <c r="C840" s="5"/>
+    </row>
+    <row r="841" ht="15.75" customHeight="1">
+      <c r="C841" s="5"/>
+    </row>
+    <row r="842" ht="15.75" customHeight="1">
+      <c r="C842" s="5"/>
+    </row>
+    <row r="843" ht="15.75" customHeight="1">
+      <c r="C843" s="5"/>
+    </row>
+    <row r="844" ht="15.75" customHeight="1">
+      <c r="C844" s="5"/>
+    </row>
+    <row r="845" ht="15.75" customHeight="1">
+      <c r="C845" s="5"/>
+    </row>
+    <row r="846" ht="15.75" customHeight="1">
+      <c r="C846" s="5"/>
+    </row>
+    <row r="847" ht="15.75" customHeight="1">
+      <c r="C847" s="5"/>
+    </row>
+    <row r="848" ht="15.75" customHeight="1">
+      <c r="C848" s="5"/>
+    </row>
+    <row r="849" ht="15.75" customHeight="1">
+      <c r="C849" s="5"/>
+    </row>
+    <row r="850" ht="15.75" customHeight="1">
+      <c r="C850" s="5"/>
+    </row>
+    <row r="851" ht="15.75" customHeight="1">
+      <c r="C851" s="5"/>
+    </row>
+    <row r="852" ht="15.75" customHeight="1">
+      <c r="C852" s="5"/>
+    </row>
+    <row r="853" ht="15.75" customHeight="1">
+      <c r="C853" s="5"/>
+    </row>
+    <row r="854" ht="15.75" customHeight="1">
+      <c r="C854" s="5"/>
+    </row>
+    <row r="855" ht="15.75" customHeight="1">
+      <c r="C855" s="5"/>
+    </row>
+    <row r="856" ht="15.75" customHeight="1">
+      <c r="C856" s="5"/>
+    </row>
+    <row r="857" ht="15.75" customHeight="1">
+      <c r="C857" s="5"/>
+    </row>
+    <row r="858" ht="15.75" customHeight="1">
+      <c r="C858" s="5"/>
+    </row>
+    <row r="859" ht="15.75" customHeight="1">
+      <c r="C859" s="5"/>
+    </row>
+    <row r="860" ht="15.75" customHeight="1">
+      <c r="C860" s="5"/>
+    </row>
+    <row r="861" ht="15.75" customHeight="1">
+      <c r="C861" s="5"/>
+    </row>
+    <row r="862" ht="15.75" customHeight="1">
+      <c r="C862" s="5"/>
+    </row>
+    <row r="863" ht="15.75" customHeight="1">
+      <c r="C863" s="5"/>
+    </row>
+    <row r="864" ht="15.75" customHeight="1">
+      <c r="C864" s="5"/>
+    </row>
+    <row r="865" ht="15.75" customHeight="1">
+      <c r="C865" s="5"/>
+    </row>
+    <row r="866" ht="15.75" customHeight="1">
+      <c r="C866" s="5"/>
+    </row>
+    <row r="867" ht="15.75" customHeight="1">
+      <c r="C867" s="5"/>
+    </row>
+    <row r="868" ht="15.75" customHeight="1">
+      <c r="C868" s="5"/>
+    </row>
+    <row r="869" ht="15.75" customHeight="1">
+      <c r="C869" s="5"/>
+    </row>
+    <row r="870" ht="15.75" customHeight="1">
+      <c r="C870" s="5"/>
+    </row>
+    <row r="871" ht="15.75" customHeight="1">
+      <c r="C871" s="5"/>
+    </row>
+    <row r="872" ht="15.75" customHeight="1">
+      <c r="C872" s="5"/>
+    </row>
+    <row r="873" ht="15.75" customHeight="1">
+      <c r="C873" s="5"/>
+    </row>
+    <row r="874" ht="15.75" customHeight="1">
+      <c r="C874" s="5"/>
+    </row>
+    <row r="875" ht="15.75" customHeight="1">
+      <c r="C875" s="5"/>
+    </row>
+    <row r="876" ht="15.75" customHeight="1">
+      <c r="C876" s="5"/>
+    </row>
+    <row r="877" ht="15.75" customHeight="1">
+      <c r="C877" s="5"/>
+    </row>
+    <row r="878" ht="15.75" customHeight="1">
+      <c r="C878" s="5"/>
+    </row>
+    <row r="879" ht="15.75" customHeight="1">
+      <c r="C879" s="5"/>
+    </row>
+    <row r="880" ht="15.75" customHeight="1">
+      <c r="C880" s="5"/>
+    </row>
+    <row r="881" ht="15.75" customHeight="1">
+      <c r="C881" s="5"/>
+    </row>
+    <row r="882" ht="15.75" customHeight="1">
+      <c r="C882" s="5"/>
+    </row>
+    <row r="883" ht="15.75" customHeight="1">
+      <c r="C883" s="5"/>
+    </row>
+    <row r="884" ht="15.75" customHeight="1">
+      <c r="C884" s="5"/>
+    </row>
+    <row r="885" ht="15.75" customHeight="1">
+      <c r="C885" s="5"/>
+    </row>
+    <row r="886" ht="15.75" customHeight="1">
+      <c r="C886" s="5"/>
+    </row>
+    <row r="887" ht="15.75" customHeight="1">
+      <c r="C887" s="5"/>
+    </row>
+    <row r="888" ht="15.75" customHeight="1">
+      <c r="C888" s="5"/>
+    </row>
+    <row r="889" ht="15.75" customHeight="1">
+      <c r="C889" s="5"/>
+    </row>
+    <row r="890" ht="15.75" customHeight="1">
+      <c r="C890" s="5"/>
+    </row>
+    <row r="891" ht="15.75" customHeight="1">
+      <c r="C891" s="5"/>
+    </row>
+    <row r="892" ht="15.75" customHeight="1">
+      <c r="C892" s="5"/>
+    </row>
+    <row r="893" ht="15.75" customHeight="1">
+      <c r="C893" s="5"/>
+    </row>
+    <row r="894" ht="15.75" customHeight="1">
+      <c r="C894" s="5"/>
+    </row>
+    <row r="895" ht="15.75" customHeight="1">
+      <c r="C895" s="5"/>
+    </row>
+    <row r="896" ht="15.75" customHeight="1">
+      <c r="C896" s="5"/>
+    </row>
+    <row r="897" ht="15.75" customHeight="1">
+      <c r="C897" s="5"/>
+    </row>
+    <row r="898" ht="15.75" customHeight="1">
+      <c r="C898" s="5"/>
+    </row>
+    <row r="899" ht="15.75" customHeight="1">
+      <c r="C899" s="5"/>
+    </row>
+    <row r="900" ht="15.75" customHeight="1">
+      <c r="C900" s="5"/>
+    </row>
+    <row r="901" ht="15.75" customHeight="1">
+      <c r="C901" s="5"/>
+    </row>
+    <row r="902" ht="15.75" customHeight="1">
+      <c r="C902" s="5"/>
+    </row>
+    <row r="903" ht="15.75" customHeight="1">
+      <c r="C903" s="5"/>
+    </row>
+    <row r="904" ht="15.75" customHeight="1">
+      <c r="C904" s="5"/>
+    </row>
+    <row r="905" ht="15.75" customHeight="1">
+      <c r="C905" s="5"/>
+    </row>
+    <row r="906" ht="15.75" customHeight="1">
+      <c r="C906" s="5"/>
+    </row>
+    <row r="907" ht="15.75" customHeight="1">
+      <c r="C907" s="5"/>
+    </row>
+    <row r="908" ht="15.75" customHeight="1">
+      <c r="C908" s="5"/>
+    </row>
+    <row r="909" ht="15.75" customHeight="1">
+      <c r="C909" s="5"/>
+    </row>
+    <row r="910" ht="15.75" customHeight="1">
+      <c r="C910" s="5"/>
+    </row>
+    <row r="911" ht="15.75" customHeight="1">
+      <c r="C911" s="5"/>
+    </row>
+    <row r="912" ht="15.75" customHeight="1">
+      <c r="C912" s="5"/>
+    </row>
+    <row r="913" ht="15.75" customHeight="1">
+      <c r="C913" s="5"/>
+    </row>
+    <row r="914" ht="15.75" customHeight="1">
+      <c r="C914" s="5"/>
+    </row>
+    <row r="915" ht="15.75" customHeight="1">
+      <c r="C915" s="5"/>
+    </row>
+    <row r="916" ht="15.75" customHeight="1">
+      <c r="C916" s="5"/>
+    </row>
+    <row r="917" ht="15.75" customHeight="1">
+      <c r="C917" s="5"/>
+    </row>
+    <row r="918" ht="15.75" customHeight="1">
+      <c r="C918" s="5"/>
+    </row>
+    <row r="919" ht="15.75" customHeight="1">
+      <c r="C919" s="5"/>
+    </row>
+    <row r="920" ht="15.75" customHeight="1">
+      <c r="C920" s="5"/>
+    </row>
+    <row r="921" ht="15.75" customHeight="1">
+      <c r="C921" s="5"/>
+    </row>
+    <row r="922" ht="15.75" customHeight="1">
+      <c r="C922" s="5"/>
+    </row>
+    <row r="923" ht="15.75" customHeight="1">
+      <c r="C923" s="5"/>
+    </row>
+    <row r="924" ht="15.75" customHeight="1">
+      <c r="C924" s="5"/>
+    </row>
+    <row r="925" ht="15.75" customHeight="1">
+      <c r="C925" s="5"/>
+    </row>
+    <row r="926" ht="15.75" customHeight="1">
+      <c r="C926" s="5"/>
+    </row>
+    <row r="927" ht="15.75" customHeight="1">
+      <c r="C927" s="5"/>
+    </row>
+    <row r="928" ht="15.75" customHeight="1">
+      <c r="C928" s="5"/>
+    </row>
+    <row r="929" ht="15.75" customHeight="1">
+      <c r="C929" s="5"/>
+    </row>
+    <row r="930" ht="15.75" customHeight="1">
+      <c r="C930" s="5"/>
+    </row>
+    <row r="931" ht="15.75" customHeight="1">
+      <c r="C931" s="5"/>
+    </row>
+    <row r="932" ht="15.75" customHeight="1">
+      <c r="C932" s="5"/>
+    </row>
+    <row r="933" ht="15.75" customHeight="1">
+      <c r="C933" s="5"/>
+    </row>
+    <row r="934" ht="15.75" customHeight="1">
+      <c r="C934" s="5"/>
+    </row>
+    <row r="935" ht="15.75" customHeight="1">
+      <c r="C935" s="5"/>
+    </row>
+    <row r="936" ht="15.75" customHeight="1">
+      <c r="C936" s="5"/>
+    </row>
+    <row r="937" ht="15.75" customHeight="1">
+      <c r="C937" s="5"/>
+    </row>
+    <row r="938" ht="15.75" customHeight="1">
+      <c r="C938" s="5"/>
+    </row>
+    <row r="939" ht="15.75" customHeight="1">
+      <c r="C939" s="5"/>
+    </row>
+    <row r="940" ht="15.75" customHeight="1">
+      <c r="C940" s="5"/>
+    </row>
+    <row r="941" ht="15.75" customHeight="1">
+      <c r="C941" s="5"/>
+    </row>
+    <row r="942" ht="15.75" customHeight="1">
+      <c r="C942" s="5"/>
+    </row>
+    <row r="943" ht="15.75" customHeight="1">
+      <c r="C943" s="5"/>
+    </row>
+    <row r="944" ht="15.75" customHeight="1">
+      <c r="C944" s="5"/>
+    </row>
+    <row r="945" ht="15.75" customHeight="1">
+      <c r="C945" s="5"/>
+    </row>
+    <row r="946" ht="15.75" customHeight="1">
+      <c r="C946" s="5"/>
+    </row>
+    <row r="947" ht="15.75" customHeight="1">
+      <c r="C947" s="5"/>
+    </row>
+    <row r="948" ht="15.75" customHeight="1">
+      <c r="C948" s="5"/>
+    </row>
+    <row r="949" ht="15.75" customHeight="1">
+      <c r="C949" s="5"/>
+    </row>
+    <row r="950" ht="15.75" customHeight="1">
+      <c r="C950" s="5"/>
+    </row>
+    <row r="951" ht="15.75" customHeight="1">
+      <c r="C951" s="5"/>
+    </row>
+    <row r="952" ht="15.75" customHeight="1">
+      <c r="C952" s="5"/>
+    </row>
+    <row r="953" ht="15.75" customHeight="1">
+      <c r="C953" s="5"/>
+    </row>
+    <row r="954" ht="15.75" customHeight="1">
+      <c r="C954" s="5"/>
+    </row>
+    <row r="955" ht="15.75" customHeight="1">
+      <c r="C955" s="5"/>
+    </row>
+    <row r="956" ht="15.75" customHeight="1">
+      <c r="C956" s="5"/>
+    </row>
+    <row r="957" ht="15.75" customHeight="1">
+      <c r="C957" s="5"/>
+    </row>
+    <row r="958" ht="15.75" customHeight="1">
+      <c r="C958" s="5"/>
+    </row>
+    <row r="959" ht="15.75" customHeight="1">
+      <c r="C959" s="5"/>
+    </row>
+    <row r="960" ht="15.75" customHeight="1">
+      <c r="C960" s="5"/>
+    </row>
+    <row r="961" ht="15.75" customHeight="1">
+      <c r="C961" s="5"/>
+    </row>
+    <row r="962" ht="15.75" customHeight="1">
+      <c r="C962" s="5"/>
+    </row>
+    <row r="963" ht="15.75" customHeight="1">
+      <c r="C963" s="5"/>
+    </row>
+    <row r="964" ht="15.75" customHeight="1">
+      <c r="C964" s="5"/>
+    </row>
+    <row r="965" ht="15.75" customHeight="1">
+      <c r="C965" s="5"/>
+    </row>
+    <row r="966" ht="15.75" customHeight="1">
+      <c r="C966" s="5"/>
+    </row>
+    <row r="967" ht="15.75" customHeight="1">
+      <c r="C967" s="5"/>
+    </row>
+    <row r="968" ht="15.75" customHeight="1">
+      <c r="C968" s="5"/>
+    </row>
+    <row r="969" ht="15.75" customHeight="1">
+      <c r="C969" s="5"/>
+    </row>
+    <row r="970" ht="15.75" customHeight="1">
+      <c r="C970" s="5"/>
+    </row>
+    <row r="971" ht="15.75" customHeight="1">
+      <c r="C971" s="5"/>
+    </row>
+    <row r="972" ht="15.75" customHeight="1">
+      <c r="C972" s="5"/>
+    </row>
+    <row r="973" ht="15.75" customHeight="1">
+      <c r="C973" s="5"/>
+    </row>
+    <row r="974" ht="15.75" customHeight="1">
+      <c r="C974" s="5"/>
+    </row>
+    <row r="975" ht="15.75" customHeight="1">
+      <c r="C975" s="5"/>
+    </row>
+    <row r="976" ht="15.75" customHeight="1">
+      <c r="C976" s="5"/>
+    </row>
+    <row r="977" ht="15.75" customHeight="1">
+      <c r="C977" s="5"/>
+    </row>
+    <row r="978" ht="15.75" customHeight="1">
+      <c r="C978" s="5"/>
+    </row>
+    <row r="979" ht="15.75" customHeight="1">
+      <c r="C979" s="5"/>
+    </row>
+    <row r="980" ht="15.75" customHeight="1">
+      <c r="C980" s="5"/>
+    </row>
+    <row r="981" ht="15.75" customHeight="1">
+      <c r="C981" s="5"/>
+    </row>
+    <row r="982" ht="15.75" customHeight="1">
+      <c r="C982" s="5"/>
+    </row>
+    <row r="983" ht="15.75" customHeight="1">
+      <c r="C983" s="5"/>
+    </row>
+    <row r="984" ht="15.75" customHeight="1">
+      <c r="C984" s="5"/>
+    </row>
+    <row r="985" ht="15.75" customHeight="1">
+      <c r="C985" s="5"/>
+    </row>
+    <row r="986" ht="15.75" customHeight="1">
+      <c r="C986" s="5"/>
+    </row>
+    <row r="987" ht="15.75" customHeight="1">
+      <c r="C987" s="5"/>
+    </row>
+    <row r="988" ht="15.75" customHeight="1">
+      <c r="C988" s="5"/>
+    </row>
+    <row r="989" ht="15.75" customHeight="1">
+      <c r="C989" s="5"/>
+    </row>
+    <row r="990" ht="15.75" customHeight="1">
+      <c r="C990" s="5"/>
+    </row>
+    <row r="991" ht="15.75" customHeight="1">
+      <c r="C991" s="5"/>
+    </row>
+    <row r="992" ht="15.75" customHeight="1">
+      <c r="C992" s="5"/>
+    </row>
+    <row r="993" ht="15.75" customHeight="1">
+      <c r="C993" s="5"/>
+    </row>
+    <row r="994" ht="15.75" customHeight="1">
+      <c r="C994" s="5"/>
+    </row>
+    <row r="995" ht="15.75" customHeight="1">
+      <c r="C995" s="5"/>
+    </row>
+    <row r="996" ht="15.75" customHeight="1">
+      <c r="C996" s="5"/>
+    </row>
+    <row r="997" ht="15.75" customHeight="1">
+      <c r="C997" s="5"/>
+    </row>
+    <row r="998" ht="15.75" customHeight="1">
+      <c r="C998" s="5"/>
+    </row>
+    <row r="999" ht="15.75" customHeight="1">
+      <c r="C999" s="5"/>
+    </row>
+    <row r="1000" ht="15.75" customHeight="1">
+      <c r="C1000" s="5"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5933,7 +7967,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>93</v>
@@ -5954,21 +7988,21 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B2" s="1" t="b">
         <v>1</v>
@@ -5977,13 +8011,13 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G2" s="1">
         <v>35.66776362</v>
@@ -5992,7 +8026,7 @@
         <v>139.7909335</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L2" s="1" t="b">
         <v>0</v>
@@ -6009,7 +8043,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B3" s="1" t="b">
         <v>1</v>
@@ -6018,13 +8052,13 @@
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G3" s="1">
         <v>35.6677205</v>
@@ -6033,7 +8067,7 @@
         <v>139.7909872</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L3" s="1" t="b">
         <v>0</v>
@@ -6050,7 +8084,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B4" s="1" t="b">
         <v>1</v>
@@ -6059,13 +8093,13 @@
         <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G4" s="1">
         <v>35.667776</v>
@@ -6074,7 +8108,7 @@
         <v>139.7907338</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L4" s="1" t="b">
         <v>0</v>
@@ -6082,16 +8116,16 @@
       <c r="M4" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2" t="b">
+      <c r="N4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B5" s="1" t="b">
         <v>1</v>
@@ -6100,13 +8134,13 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G5" s="1">
         <v>35.6677303</v>
@@ -6115,9 +8149,9 @@
         <v>139.7906747</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="L5" s="2" t="b">
+        <v>156</v>
+      </c>
+      <c r="L5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="M5" s="1" t="b">
@@ -6132,7 +8166,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B6" s="1" t="b">
         <v>1</v>
@@ -6141,13 +8175,13 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G6" s="1">
         <v>35.6676801</v>
@@ -6156,7 +8190,7 @@
         <v>139.7906077</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L6" s="1" t="b">
         <v>0</v>
@@ -6164,16 +8198,16 @@
       <c r="M6" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2" t="b">
+      <c r="N6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B7" s="1" t="b">
         <v>1</v>
@@ -6182,30 +8216,30 @@
         <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="L7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N7" s="2" t="b">
+        <v>167</v>
+      </c>
+      <c r="L7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O7" s="1" t="b">
@@ -6214,7 +8248,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B8" s="1" t="b">
         <v>1</v>
@@ -6223,13 +8257,13 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G8" s="1">
         <v>35.6676327</v>
@@ -6238,7 +8272,7 @@
         <v>139.7910938</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L8" s="1" t="b">
         <v>0</v>
@@ -6255,7 +8289,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B9" s="1" t="b">
         <v>1</v>
@@ -6264,13 +8298,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G9" s="1">
         <v>35.6675843</v>
@@ -6279,7 +8313,7 @@
         <v>139.7911495</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L9" s="1" t="b">
         <v>1</v>
@@ -6296,7 +8330,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B10" s="1" t="b">
         <v>1</v>
@@ -6305,13 +8339,13 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G10" s="1">
         <v>35.6675385</v>
@@ -6320,7 +8354,7 @@
         <v>139.7912031</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L10" s="1" t="b">
         <v>1</v>
@@ -6337,7 +8371,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B11" s="1" t="b">
         <v>1</v>
@@ -6346,13 +8380,13 @@
         <v>5</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G11" s="1">
         <v>35.6674927</v>
@@ -6361,7 +8395,7 @@
         <v>139.7912581</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L11" s="1" t="b">
         <v>1</v>
@@ -6378,7 +8412,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B12" s="1" t="b">
         <v>1</v>
@@ -6387,13 +8421,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G12" s="1">
         <v>35.6673587</v>
@@ -6402,7 +8436,7 @@
         <v>139.7912568</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L12" s="1" t="b">
         <v>1</v>
@@ -6419,7 +8453,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B13" s="1" t="b">
         <v>1</v>
@@ -6428,13 +8462,13 @@
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G13" s="1">
         <v>35.6673293</v>
@@ -6443,7 +8477,7 @@
         <v>139.7912923</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L13" s="1" t="b">
         <v>1</v>
@@ -6460,7 +8494,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B14" s="1" t="b">
         <v>1</v>
@@ -6469,13 +8503,13 @@
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G14" s="1">
         <v>35.6673015</v>
@@ -6484,7 +8518,7 @@
         <v>139.7913285</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L14" s="1" t="b">
         <v>1</v>
@@ -6501,7 +8535,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B15" s="1" t="b">
         <v>1</v>
@@ -6510,13 +8544,13 @@
         <v>5</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G15" s="1">
         <v>35.6672748</v>
@@ -6525,7 +8559,7 @@
         <v>139.791358</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L15" s="1" t="b">
         <v>1</v>
@@ -6542,7 +8576,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B16" s="1" t="b">
         <v>1</v>
@@ -6551,13 +8585,13 @@
         <v>5</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G16" s="1">
         <v>35.6672481</v>
@@ -6566,7 +8600,7 @@
         <v>139.7913929</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L16" s="1" t="b">
         <v>1</v>
@@ -6583,7 +8617,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B17" s="1" t="b">
         <v>1</v>
@@ -6592,13 +8626,13 @@
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G17" s="1">
         <v>35.6672182</v>
@@ -6607,7 +8641,7 @@
         <v>139.7914325</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L17" s="1" t="b">
         <v>1</v>
@@ -6624,7 +8658,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B18" s="1" t="b">
         <v>1</v>
@@ -6633,22 +8667,22 @@
         <v>5</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L18" s="1" t="b">
         <v>1</v>
@@ -6665,7 +8699,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B19" s="1" t="b">
         <v>1</v>
@@ -6674,13 +8708,13 @@
         <v>5</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G19" s="1">
         <v>35.6671501</v>
@@ -6689,7 +8723,7 @@
         <v>139.7915176</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L19" s="1" t="b">
         <v>0</v>
@@ -6706,7 +8740,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B20" s="1" t="b">
         <v>1</v>
@@ -6715,22 +8749,22 @@
         <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L20" s="1" t="b">
         <v>1</v>
@@ -6747,7 +8781,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B21" s="1" t="b">
         <v>1</v>
@@ -6756,22 +8790,22 @@
         <v>5</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L21" s="1" t="b">
         <v>1</v>
@@ -6788,7 +8822,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B22" s="1" t="b">
         <v>1</v>
@@ -6797,22 +8831,22 @@
         <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L22" s="1" t="b">
         <v>0</v>
@@ -6829,7 +8863,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B23" s="1" t="b">
         <v>1</v>
@@ -6837,23 +8871,23 @@
       <c r="C23" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>250</v>
+      <c r="D23" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L23" s="1" t="b">
         <v>1</v>
@@ -6870,7 +8904,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B24" s="1" t="b">
         <v>1</v>
@@ -6879,30 +8913,30 @@
         <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="L24" s="2" t="b">
+        <v>262</v>
+      </c>
+      <c r="L24" s="1" t="b">
         <v>1</v>
       </c>
       <c r="M24" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N24" s="2" t="b">
+      <c r="N24" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O24" s="1" t="b">
@@ -6911,7 +8945,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B25" s="1" t="b">
         <v>1</v>
@@ -6920,13 +8954,13 @@
         <v>5</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G25" s="1">
         <v>35.6669469</v>
@@ -6935,7 +8969,7 @@
         <v>139.7917631</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L25" s="1" t="b">
         <v>1</v>
@@ -6952,7 +8986,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B26" s="1" t="b">
         <v>1</v>
@@ -6961,13 +8995,13 @@
         <v>5</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G26" s="1">
         <v>35.6669082</v>
@@ -6976,7 +9010,7 @@
         <v>139.7918093</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L26" s="1" t="b">
         <v>0</v>
@@ -6993,7 +9027,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B27" s="1" t="b">
         <v>1</v>
@@ -7002,13 +9036,13 @@
         <v>5</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G27" s="1">
         <v>35.666875</v>
@@ -7017,7 +9051,7 @@
         <v>139.7918502</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L27" s="1" t="b">
         <v>1</v>
@@ -7034,7 +9068,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B28" s="1" t="b">
         <v>1</v>
@@ -7043,13 +9077,13 @@
         <v>5</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G28" s="1">
         <v>35.6668396</v>
@@ -7058,24 +9092,24 @@
         <v>139.7918925</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L28" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M28" s="2" t="b">
+      <c r="M28" s="1" t="b">
         <v>1</v>
       </c>
       <c r="N28" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O28" s="2" t="b">
+      <c r="O28" s="1" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B29" s="1" t="b">
         <v>1</v>
@@ -7084,13 +9118,13 @@
         <v>5</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G29" s="1">
         <v>35.6669616</v>
@@ -7099,7 +9133,7 @@
         <v>139.7918931</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L29" s="1" t="b">
         <v>0</v>
@@ -7116,7 +9150,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B30" s="1" t="b">
         <v>1</v>
@@ -7125,22 +9159,22 @@
         <v>5</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L30" s="1" t="b">
         <v>1</v>
@@ -7157,7 +9191,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B31" s="1" t="b">
         <v>1</v>
@@ -7166,22 +9200,22 @@
         <v>5</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L31" s="1" t="b">
         <v>0</v>
@@ -7192,13 +9226,13 @@
       <c r="N31" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="O31" s="2" t="b">
+      <c r="O31" s="1" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B32" s="1" t="b">
         <v>1</v>
@@ -7207,22 +9241,22 @@
         <v>8</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L32" s="1" t="b">
         <v>0</v>
@@ -7239,7 +9273,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B33" s="1" t="b">
         <v>1</v>
@@ -7248,22 +9282,22 @@
         <v>8</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L33" s="1" t="b">
         <v>0</v>
@@ -7280,7 +9314,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B34" s="1" t="b">
         <v>1</v>
@@ -7289,22 +9323,22 @@
         <v>8</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L34" s="1" t="b">
         <v>0</v>
@@ -7321,7 +9355,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B35" s="1" t="b">
         <v>1</v>
@@ -7330,22 +9364,22 @@
         <v>8</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L35" s="1" t="b">
         <v>0</v>
@@ -7362,7 +9396,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B36" s="1" t="b">
         <v>1</v>
@@ -7371,22 +9405,22 @@
         <v>8</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L36" s="1" t="b">
         <v>0</v>
@@ -7403,7 +9437,7 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B37" s="1" t="b">
         <v>1</v>
@@ -7412,22 +9446,22 @@
         <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L37" s="1" t="b">
         <v>0</v>
@@ -7444,7 +9478,7 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B38" s="1" t="b">
         <v>1</v>
@@ -7453,22 +9487,22 @@
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L38" s="1" t="b">
         <v>0</v>
@@ -7485,7 +9519,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B39" s="1" t="b">
         <v>1</v>
@@ -7494,27 +9528,27 @@
         <v>15</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L39" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M39" s="2" t="b">
+      <c r="M39" s="1" t="b">
         <v>1</v>
       </c>
       <c r="N39" s="1" t="b">
@@ -7526,7 +9560,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B40" s="1" t="b">
         <v>1</v>
@@ -7535,22 +9569,22 @@
         <v>15</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L40" s="1" t="b">
         <v>0</v>
@@ -7558,16 +9592,16 @@
       <c r="M40" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N40" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="O40" s="1" t="b">
-        <v>1</v>
+      <c r="N40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B41" s="1" t="b">
         <v>1</v>
@@ -7576,22 +9610,22 @@
         <v>15</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L41" s="1" t="b">
         <v>0</v>
@@ -7608,7 +9642,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B42" s="1" t="b">
         <v>1</v>
@@ -7617,22 +9651,22 @@
         <v>15</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L42" s="1" t="b">
         <v>0</v>
@@ -7649,7 +9683,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B43" s="1" t="b">
         <v>1</v>
@@ -7658,22 +9692,22 @@
         <v>15</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L43" s="1" t="b">
         <v>0</v>
@@ -7690,7 +9724,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B44" s="1" t="b">
         <v>1</v>
@@ -7699,22 +9733,22 @@
         <v>19</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L44" s="1" t="b">
         <v>0</v>
@@ -7731,7 +9765,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B45" s="1" t="b">
         <v>1</v>
@@ -7740,22 +9774,22 @@
         <v>19</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L45" s="1" t="b">
         <v>0</v>
@@ -7772,7 +9806,7 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B46" s="1" t="b">
         <v>1</v>
@@ -7781,22 +9815,22 @@
         <v>19</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L46" s="1" t="b">
         <v>0</v>
@@ -7807,13 +9841,13 @@
       <c r="N46" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="O46" s="2" t="b">
+      <c r="O46" s="1" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B47" s="1" t="b">
         <v>1</v>
@@ -7822,22 +9856,22 @@
         <v>22</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L47" s="1" t="b">
         <v>0</v>
@@ -7845,7 +9879,7 @@
       <c r="M47" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N47" s="2" t="b">
+      <c r="N47" s="1" t="b">
         <v>1</v>
       </c>
       <c r="O47" s="1" t="b">
@@ -7854,7 +9888,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B48" s="1" t="b">
         <v>1</v>
@@ -7863,22 +9897,22 @@
         <v>22</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L48" s="1" t="b">
         <v>0</v>
@@ -7895,7 +9929,7 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B49" s="1" t="b">
         <v>1</v>
@@ -7904,22 +9938,22 @@
         <v>22</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L49" s="1" t="b">
         <v>0</v>
@@ -7936,7 +9970,7 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B50" s="1" t="b">
         <v>1</v>
@@ -7945,22 +9979,22 @@
         <v>22</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L50" s="1" t="b">
         <v>0</v>
@@ -7977,7 +10011,7 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B51" s="1" t="b">
         <v>1</v>
@@ -7986,22 +10020,22 @@
         <v>5</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L51" s="1" t="b">
         <v>0</v>
@@ -8018,7 +10052,7 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B52" s="1" t="b">
         <v>1</v>
@@ -8027,22 +10061,22 @@
         <v>5</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L52" s="1" t="b">
         <v>0</v>
@@ -8059,7 +10093,7 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B53" s="1" t="b">
         <v>1</v>
@@ -8068,16 +10102,16 @@
         <v>5</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>111</v>
@@ -8097,7 +10131,7 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B54" s="1" t="b">
         <v>1</v>
@@ -8106,22 +10140,22 @@
         <v>22</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L54" s="1" t="b">
         <v>0</v>
@@ -8138,7 +10172,7 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B55" s="1" t="b">
         <v>1</v>
@@ -8147,19 +10181,19 @@
         <v>36</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L55" s="1" t="b">
         <v>0</v>
@@ -8176,7 +10210,7 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B56" s="1" t="b">
         <v>1</v>
@@ -8185,22 +10219,22 @@
         <v>33</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L56" s="1" t="b">
         <v>0</v>
@@ -8217,7 +10251,7 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B57" s="1" t="b">
         <v>1</v>
@@ -8226,22 +10260,22 @@
         <v>43</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L57" s="1" t="b">
         <v>0</v>
@@ -8258,7 +10292,7 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B58" s="1" t="b">
         <v>1</v>
@@ -8267,19 +10301,19 @@
         <v>29</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L58" s="1" t="b">
         <v>0</v>
@@ -8296,7 +10330,7 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B59" s="1" t="b">
         <v>1</v>
@@ -8305,22 +10339,22 @@
         <v>40</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L59" s="1" t="b">
         <v>0</v>
@@ -9293,31 +11327,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>4</v>
@@ -9334,16 +11368,16 @@
         <v>46158.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I2" s="1">
         <v>0.3645833333333333</v>
@@ -9352,7 +11386,7 @@
         <v>0.375</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3">
@@ -9366,19 +11400,19 @@
         <v>46158.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I3" s="1">
         <v>0.375</v>
@@ -9387,7 +11421,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4">
@@ -9401,19 +11435,19 @@
         <v>46158.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I4" s="1">
         <v>0.4305555555555556</v>
@@ -9422,7 +11456,7 @@
         <v>0.4722222222222222</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5">
@@ -9436,19 +11470,19 @@
         <v>46158.0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I5" s="1">
         <v>0.4930555555555556</v>
@@ -9457,7 +11491,7 @@
         <v>0.5625</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6">
@@ -9471,13 +11505,13 @@
         <v>46158.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I6" s="1">
         <v>0.5625</v>
@@ -9497,19 +11531,19 @@
         <v>46158.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I7" s="1">
         <v>0.5833333333333334</v>
@@ -9521,7 +11555,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8">
@@ -9535,19 +11569,19 @@
         <v>46158.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I8" s="1">
         <v>0.6180555555555556</v>
@@ -9556,7 +11590,7 @@
         <v>0.7013888888888888</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9">
@@ -9570,19 +11604,19 @@
         <v>46158.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I9" s="1">
         <v>0.7083333333333334</v>
@@ -9591,7 +11625,7 @@
         <v>0.75</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10">
@@ -9605,19 +11639,19 @@
         <v>46159.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I10" s="1">
         <v>0.4027777777777778</v>
@@ -9626,7 +11660,7 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="11">
@@ -9640,19 +11674,19 @@
         <v>46159.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I11" s="1">
         <v>0.4375</v>
@@ -9661,7 +11695,7 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12">
@@ -9675,16 +11709,16 @@
         <v>46159.0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I12" s="1">
         <v>0.4791666666666667</v>
@@ -9696,7 +11730,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="13">
@@ -9710,19 +11744,19 @@
         <v>46159.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I13" s="1">
         <v>0.5138888888888888</v>
@@ -9731,7 +11765,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="14">
@@ -9745,16 +11779,16 @@
         <v>46159.0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I14" s="1">
         <v>0.5694444444444444</v>
@@ -9766,7 +11800,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="15">
@@ -9780,16 +11814,16 @@
         <v>46159.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I15" s="1">
         <v>0.6180555555555556</v>
@@ -9798,7 +11832,7 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16">
@@ -9812,16 +11846,16 @@
         <v>46159.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I16" s="1">
         <v>0.6736111111111112</v>
@@ -9833,7 +11867,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="17">
@@ -9847,19 +11881,19 @@
         <v>46159.0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I17" s="1">
         <v>0.7083333333333334</v>
@@ -9868,12 +11902,12 @@
         <v>0.75</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B18" s="1" t="b">
         <v>1</v>
@@ -9882,19 +11916,19 @@
         <v>46158.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I18" s="1">
         <v>0.4375</v>
@@ -9903,12 +11937,12 @@
         <v>0.4513888888888889</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B19" s="1" t="b">
         <v>1</v>
@@ -9917,19 +11951,19 @@
         <v>46158.0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I19" s="1">
         <v>0.5416666666666666</v>
@@ -9938,7 +11972,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="20">
@@ -9952,19 +11986,19 @@
         <v>46159.0</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I20" s="1">
         <v>0.4375</v>
@@ -9973,12 +12007,12 @@
         <v>0.4513888888888889</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B21" s="1" t="b">
         <v>1</v>
@@ -9987,19 +12021,19 @@
         <v>46159.0</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I21" s="1">
         <v>0.5416666666666666</v>
@@ -10008,12 +12042,12 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B22" s="1" t="b">
         <v>1</v>
@@ -10022,19 +12056,19 @@
         <v>46158.0</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I22" s="1">
         <v>0.4791666666666667</v>
@@ -10043,7 +12077,7 @@
         <v>0.5</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -10057,19 +12091,19 @@
         <v>46158.0</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I23" s="1">
         <v>0.625</v>
@@ -10078,12 +12112,12 @@
         <v>0.6458333333333334</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B24" s="1" t="b">
         <v>1</v>
@@ -10092,19 +12126,19 @@
         <v>46159.0</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I24" s="1">
         <v>0.4791666666666667</v>
@@ -10113,12 +12147,12 @@
         <v>0.5</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B25" s="1" t="b">
         <v>1</v>
@@ -10127,19 +12161,19 @@
         <v>46159.0</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I25" s="1">
         <v>0.625</v>
@@ -10148,12 +12182,12 @@
         <v>0.6458333333333334</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B26" s="1" t="b">
         <v>1</v>
@@ -10162,19 +12196,19 @@
         <v>46158.0</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I26" s="1">
         <v>0.6666666666666666</v>
@@ -10183,7 +12217,7 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -10197,19 +12231,19 @@
         <v>46159.0</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I27" s="1">
         <v>0.6666666666666666</v>
@@ -10218,12 +12252,12 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B28" s="1" t="b">
         <v>1</v>
@@ -10232,13 +12266,13 @@
         <v>46158.0</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I28" s="1">
         <v>0.625</v>
@@ -10247,12 +12281,12 @@
         <v>0.6458333333333334</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B29" s="1" t="b">
         <v>1</v>
@@ -10261,16 +12295,16 @@
         <v>46158.0</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I29" s="1">
         <v>0.6458333333333334</v>
@@ -10279,7 +12313,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>
